--- a/Copia Envases/ListaEntrada.xlsx
+++ b/Copia Envases/ListaEntrada.xlsx
@@ -166,23 +166,6 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -387,10 +370,10 @@
         <v>190810</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>1963101</v>
+        <v>1963170</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -398,10 +381,10 @@
         <v>190810</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>1963102</v>
+        <v>1963171</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -409,537 +392,9 @@
         <v>190810</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>1963104</v>
+        <v>1963172</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B5" s="1" t="n">
-        <v>1963107</v>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B6" s="1" t="n">
-        <v>1963108</v>
-      </c>
-      <c r="C6" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B7" s="1" t="n">
-        <v>1963109</v>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B8" s="1" t="n">
-        <v>1963110</v>
-      </c>
-      <c r="C8" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B9" s="1" t="n">
-        <v>1963111</v>
-      </c>
-      <c r="C9" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B10" s="1" t="n">
-        <v>1963112</v>
-      </c>
-      <c r="C10" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B11" s="1" t="n">
-        <v>1963113</v>
-      </c>
-      <c r="C11" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B12" s="1" t="n">
-        <v>1963114</v>
-      </c>
-      <c r="C12" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B13" s="1" t="n">
-        <v>1963115</v>
-      </c>
-      <c r="C13" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B14" s="1" t="n">
-        <v>1963116</v>
-      </c>
-      <c r="C14" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B15" s="1" t="n">
-        <v>1963117</v>
-      </c>
-      <c r="C15" s="1" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B16" s="1" t="n">
-        <v>1963118</v>
-      </c>
-      <c r="C16" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B17" s="1" t="n">
-        <v>1963119</v>
-      </c>
-      <c r="C17" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B18" s="1" t="n">
-        <v>1963120</v>
-      </c>
-      <c r="C18" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B19" s="1" t="n">
-        <v>1963121</v>
-      </c>
-      <c r="C19" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B20" s="1" t="n">
-        <v>1963122</v>
-      </c>
-      <c r="C20" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B21" s="1" t="n">
-        <v>1963123</v>
-      </c>
-      <c r="C21" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B22" s="1" t="n">
-        <v>1963125</v>
-      </c>
-      <c r="C22" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B23" s="1" t="n">
-        <v>1963127</v>
-      </c>
-      <c r="C23" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B24" s="1" t="n">
-        <v>1963129</v>
-      </c>
-      <c r="C24" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B25" s="1" t="n">
-        <v>1963130</v>
-      </c>
-      <c r="C25" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B26" s="1" t="n">
-        <v>1963131</v>
-      </c>
-      <c r="C26" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B27" s="1" t="n">
-        <v>1963132</v>
-      </c>
-      <c r="C27" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B28" s="1" t="n">
-        <v>1963133</v>
-      </c>
-      <c r="C28" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B29" s="1" t="n">
-        <v>1963135</v>
-      </c>
-      <c r="C29" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B30" s="1" t="n">
-        <v>1963138</v>
-      </c>
-      <c r="C30" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B31" s="1" t="n">
-        <v>1963139</v>
-      </c>
-      <c r="C31" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B32" s="1" t="n">
-        <v>1963140</v>
-      </c>
-      <c r="C32" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B33" s="1" t="n">
-        <v>1963141</v>
-      </c>
-      <c r="C33" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B34" s="1" t="n">
-        <v>1963142</v>
-      </c>
-      <c r="C34" s="1" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B35" s="1" t="n">
-        <v>1963143</v>
-      </c>
-      <c r="C35" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B36" s="1" t="n">
-        <v>1963144</v>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B37" s="1" t="n">
-        <v>1963145</v>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B38" s="1" t="n">
-        <v>1963146</v>
-      </c>
-      <c r="C38" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B39" s="1" t="n">
-        <v>1963147</v>
-      </c>
-      <c r="C39" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B40" s="1" t="n">
-        <v>1963150</v>
-      </c>
-      <c r="C40" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B41" s="1" t="n">
-        <v>1963152</v>
-      </c>
-      <c r="C41" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B42" s="1" t="n">
-        <v>1963153</v>
-      </c>
-      <c r="C42" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B43" s="1" t="n">
-        <v>1963155</v>
-      </c>
-      <c r="C43" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B44" s="1" t="n">
-        <v>1963156</v>
-      </c>
-      <c r="C44" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B45" s="1" t="n">
-        <v>1963159</v>
-      </c>
-      <c r="C45" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B46" s="1" t="n">
-        <v>1963161</v>
-      </c>
-      <c r="C46" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B47" s="1" t="n">
-        <v>1963162</v>
-      </c>
-      <c r="C47" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B48" s="1" t="n">
-        <v>1963165</v>
-      </c>
-      <c r="C48" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B49" s="1" t="n">
-        <v>1963166</v>
-      </c>
-      <c r="C49" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B50" s="1" t="n">
-        <v>1963170</v>
-      </c>
-      <c r="C50" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B51" s="1" t="n">
-        <v>1963171</v>
-      </c>
-      <c r="C51" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="1" t="n">
-        <v>190810</v>
-      </c>
-      <c r="B52" s="1" t="n">
-        <v>1963172</v>
-      </c>
-      <c r="C52" s="1" t="n">
         <v>1</v>
       </c>
     </row>

--- a/Copia Envases/ListaEntrada.xlsx
+++ b/Copia Envases/ListaEntrada.xlsx
@@ -149,7 +149,7 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -358,7 +358,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E584"/>
+  <dimension ref="A1:E1048576"/>
   <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.57"/>
@@ -382,7 +382,7 @@
         <v>171794</v>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1744416</v>
+        <v>1917303</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>1</v>
@@ -390,4691 +390,1447 @@
     </row>
     <row r="3" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="n">
-        <v>171794</v>
+        <v>171795</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1744420</v>
+        <v>1744437</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>1</v>
       </c>
+      <c r="E3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="n">
-        <v>171794</v>
+        <v>171795</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1744433</v>
+        <v>2332131</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="n">
-        <v>171794</v>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>1744435</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="n">
-        <v>171794</v>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>1917303</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="n">
-        <v>171795</v>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>1744437</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="4"/>
-    </row>
-    <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="n">
-        <v>171795</v>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>1744439</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="n">
-        <v>171795</v>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>1744443</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="n">
-        <v>171795</v>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>1744444</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="n">
-        <v>171795</v>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>1744445</v>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="n">
-        <v>171795</v>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>1744446</v>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="n">
-        <v>171795</v>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>1744449</v>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="n">
-        <v>171795</v>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>1744450</v>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="n">
-        <v>171795</v>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>1849822</v>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="n">
-        <v>171795</v>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>1766247</v>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="n">
-        <v>171798</v>
-      </c>
-      <c r="B17" s="3" t="n">
-        <v>1744452</v>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="n">
-        <v>171798</v>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>1744453</v>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="n">
-        <v>171800</v>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>1744474</v>
-      </c>
-      <c r="C19" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="n">
-        <v>171800</v>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>1744476</v>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="n">
-        <v>171800</v>
-      </c>
-      <c r="B21" s="3" t="n">
-        <v>1744477</v>
-      </c>
-      <c r="C21" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="n">
-        <v>171800</v>
-      </c>
-      <c r="B22" s="3" t="n">
-        <v>1744478</v>
-      </c>
-      <c r="C22" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="n">
-        <v>171800</v>
-      </c>
-      <c r="B23" s="3" t="n">
-        <v>1744482</v>
-      </c>
-      <c r="C23" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A23" s="5"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="n">
-        <v>171800</v>
-      </c>
-      <c r="B24" s="3" t="n">
-        <v>1744483</v>
-      </c>
-      <c r="C24" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A24" s="5"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="n">
-        <v>171800</v>
-      </c>
-      <c r="B25" s="3" t="n">
-        <v>1744484</v>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A25" s="5"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="n">
-        <v>171800</v>
-      </c>
-      <c r="B26" s="3" t="n">
-        <v>1766863</v>
-      </c>
-      <c r="C26" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A26" s="5"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="n">
-        <v>171800</v>
-      </c>
-      <c r="B27" s="3" t="n">
-        <v>1972170</v>
-      </c>
-      <c r="C27" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A27" s="5"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="n">
-        <v>171800</v>
-      </c>
-      <c r="B28" s="3" t="n">
-        <v>2074284</v>
-      </c>
-      <c r="C28" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A28" s="5"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="n">
-        <v>171800</v>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>2230921</v>
-      </c>
-      <c r="C29" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A29" s="5"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="n">
-        <v>171800</v>
-      </c>
-      <c r="B30" s="3" t="n">
-        <v>2230922</v>
-      </c>
-      <c r="C30" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A30" s="5"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3" t="n">
-        <v>171800</v>
-      </c>
-      <c r="B31" s="3" t="n">
-        <v>2230923</v>
-      </c>
-      <c r="C31" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A31" s="5"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="3" t="n">
-        <v>171800</v>
-      </c>
-      <c r="B32" s="3" t="n">
-        <v>2230924</v>
-      </c>
-      <c r="C32" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A32" s="5"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="5"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="3" t="n">
-        <v>171800</v>
-      </c>
-      <c r="B33" s="3" t="n">
-        <v>2230925</v>
-      </c>
-      <c r="C33" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A33" s="5"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="5"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3" t="n">
-        <v>171800</v>
-      </c>
-      <c r="B34" s="3" t="n">
-        <v>2230926</v>
-      </c>
-      <c r="C34" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A34" s="5"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="5"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="3" t="n">
-        <v>171800</v>
-      </c>
-      <c r="B35" s="3" t="n">
-        <v>2230927</v>
-      </c>
-      <c r="C35" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A35" s="5"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="5"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="3" t="n">
-        <v>171801</v>
-      </c>
-      <c r="B36" s="3" t="n">
-        <v>1744487</v>
-      </c>
-      <c r="C36" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A36" s="5"/>
+      <c r="B36" s="5"/>
+      <c r="C36" s="5"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="3" t="n">
-        <v>171801</v>
-      </c>
-      <c r="B37" s="3" t="n">
-        <v>1744489</v>
-      </c>
-      <c r="C37" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A37" s="5"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="5"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="3" t="n">
-        <v>171801</v>
-      </c>
-      <c r="B38" s="3" t="n">
-        <v>1744494</v>
-      </c>
-      <c r="C38" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A38" s="5"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="3" t="n">
-        <v>171801</v>
-      </c>
-      <c r="B39" s="3" t="n">
-        <v>1744496</v>
-      </c>
-      <c r="C39" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A39" s="5"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="3" t="n">
-        <v>171802</v>
-      </c>
-      <c r="B40" s="3" t="n">
-        <v>1744510</v>
-      </c>
-      <c r="C40" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A40" s="5"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="3" t="n">
-        <v>171802</v>
-      </c>
-      <c r="B41" s="3" t="n">
-        <v>1744511</v>
-      </c>
-      <c r="C41" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A41" s="5"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="3" t="n">
-        <v>171802</v>
-      </c>
-      <c r="B42" s="3" t="n">
-        <v>2169719</v>
-      </c>
-      <c r="C42" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A42" s="5"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="5"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="3" t="n">
-        <v>171802</v>
-      </c>
-      <c r="B43" s="3" t="n">
-        <v>1766852</v>
-      </c>
-      <c r="C43" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A43" s="5"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="5"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="3" t="n">
-        <v>171804</v>
-      </c>
-      <c r="B44" s="3" t="n">
-        <v>1744516</v>
-      </c>
-      <c r="C44" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A44" s="5"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="5"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="3" t="n">
-        <v>171804</v>
-      </c>
-      <c r="B45" s="3" t="n">
-        <v>1744517</v>
-      </c>
-      <c r="C45" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A45" s="5"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="5"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="3" t="n">
-        <v>171804</v>
-      </c>
-      <c r="B46" s="3" t="n">
-        <v>1744518</v>
-      </c>
-      <c r="C46" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A46" s="5"/>
+      <c r="B46" s="5"/>
+      <c r="C46" s="5"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="3" t="n">
-        <v>171804</v>
-      </c>
-      <c r="B47" s="3" t="n">
-        <v>1744521</v>
-      </c>
-      <c r="C47" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A47" s="5"/>
+      <c r="B47" s="5"/>
+      <c r="C47" s="5"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="3" t="n">
-        <v>171806</v>
-      </c>
-      <c r="B48" s="3" t="n">
-        <v>1968396</v>
-      </c>
-      <c r="C48" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A48" s="5"/>
+      <c r="B48" s="5"/>
+      <c r="C48" s="5"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="3" t="n">
-        <v>171806</v>
-      </c>
-      <c r="B49" s="3" t="n">
-        <v>1954520</v>
-      </c>
-      <c r="C49" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A49" s="5"/>
+      <c r="B49" s="5"/>
+      <c r="C49" s="5"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="3" t="n">
-        <v>171806</v>
-      </c>
-      <c r="B50" s="3" t="n">
-        <v>1765954</v>
-      </c>
-      <c r="C50" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A50" s="5"/>
+      <c r="B50" s="5"/>
+      <c r="C50" s="5"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="3" t="n">
-        <v>171807</v>
-      </c>
-      <c r="B51" s="3" t="n">
-        <v>1744525</v>
-      </c>
-      <c r="C51" s="3" t="n">
-        <v>4</v>
-      </c>
+      <c r="A51" s="5"/>
+      <c r="B51" s="5"/>
+      <c r="C51" s="5"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="3" t="n">
-        <v>171808</v>
-      </c>
-      <c r="B52" s="3" t="n">
-        <v>1744537</v>
-      </c>
-      <c r="C52" s="3" t="n">
-        <v>2</v>
-      </c>
+      <c r="A52" s="5"/>
+      <c r="B52" s="5"/>
+      <c r="C52" s="5"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="3" t="n">
-        <v>171810</v>
-      </c>
-      <c r="B53" s="3" t="n">
-        <v>1954496</v>
-      </c>
-      <c r="C53" s="3" t="n">
-        <v>3</v>
-      </c>
+      <c r="A53" s="5"/>
+      <c r="B53" s="5"/>
+      <c r="C53" s="5"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="3" t="n">
-        <v>173409</v>
-      </c>
-      <c r="B54" s="3" t="n">
-        <v>1766788</v>
-      </c>
-      <c r="C54" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A54" s="5"/>
+      <c r="B54" s="5"/>
+      <c r="C54" s="5"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="3" t="n">
-        <v>173409</v>
-      </c>
-      <c r="B55" s="3" t="n">
-        <v>1766791</v>
-      </c>
-      <c r="C55" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A55" s="5"/>
+      <c r="B55" s="5"/>
+      <c r="C55" s="5"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="3" t="n">
-        <v>173409</v>
-      </c>
-      <c r="B56" s="3" t="n">
-        <v>1766795</v>
-      </c>
-      <c r="C56" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A56" s="5"/>
+      <c r="B56" s="5"/>
+      <c r="C56" s="5"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="3" t="n">
-        <v>173409</v>
-      </c>
-      <c r="B57" s="3" t="n">
-        <v>1766798</v>
-      </c>
-      <c r="C57" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A57" s="5"/>
+      <c r="B57" s="5"/>
+      <c r="C57" s="5"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="3" t="n">
-        <v>173409</v>
-      </c>
-      <c r="B58" s="3" t="n">
-        <v>1766805</v>
-      </c>
-      <c r="C58" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A58" s="5"/>
+      <c r="B58" s="5"/>
+      <c r="C58" s="5"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="3" t="n">
-        <v>173409</v>
-      </c>
-      <c r="B59" s="3" t="n">
-        <v>1766813</v>
-      </c>
-      <c r="C59" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A59" s="5"/>
+      <c r="B59" s="5"/>
+      <c r="C59" s="5"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="3" t="n">
-        <v>173413</v>
-      </c>
-      <c r="B60" s="3" t="n">
-        <v>1769189</v>
-      </c>
-      <c r="C60" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A60" s="5"/>
+      <c r="B60" s="5"/>
+      <c r="C60" s="5"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="3" t="n">
-        <v>173413</v>
-      </c>
-      <c r="B61" s="3" t="n">
-        <v>1769190</v>
-      </c>
-      <c r="C61" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A61" s="5"/>
+      <c r="B61" s="5"/>
+      <c r="C61" s="5"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="3" t="n">
-        <v>173413</v>
-      </c>
-      <c r="B62" s="3" t="n">
-        <v>1769191</v>
-      </c>
-      <c r="C62" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A62" s="5"/>
+      <c r="B62" s="5"/>
+      <c r="C62" s="5"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="3" t="n">
-        <v>173413</v>
-      </c>
-      <c r="B63" s="3" t="n">
-        <v>1769195</v>
-      </c>
-      <c r="C63" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A63" s="5"/>
+      <c r="B63" s="5"/>
+      <c r="C63" s="5"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="3" t="n">
-        <v>173413</v>
-      </c>
-      <c r="B64" s="3" t="n">
-        <v>1769201</v>
-      </c>
-      <c r="C64" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A64" s="5"/>
+      <c r="B64" s="5"/>
+      <c r="C64" s="5"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="3" t="n">
-        <v>173413</v>
-      </c>
-      <c r="B65" s="3" t="n">
-        <v>1769202</v>
-      </c>
-      <c r="C65" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A65" s="5"/>
+      <c r="B65" s="5"/>
+      <c r="C65" s="5"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="3" t="n">
-        <v>173419</v>
-      </c>
-      <c r="B66" s="3" t="n">
-        <v>2130580</v>
-      </c>
-      <c r="C66" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A66" s="5"/>
+      <c r="B66" s="5"/>
+      <c r="C66" s="5"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="3" t="n">
-        <v>173419</v>
-      </c>
-      <c r="B67" s="3" t="n">
-        <v>2130582</v>
-      </c>
-      <c r="C67" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A67" s="5"/>
+      <c r="B67" s="5"/>
+      <c r="C67" s="5"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="3" t="n">
-        <v>173419</v>
-      </c>
-      <c r="B68" s="3" t="n">
-        <v>2130584</v>
-      </c>
-      <c r="C68" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A68" s="5"/>
+      <c r="B68" s="5"/>
+      <c r="C68" s="5"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="3" t="n">
-        <v>173419</v>
-      </c>
-      <c r="B69" s="3" t="n">
-        <v>2130587</v>
-      </c>
-      <c r="C69" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A69" s="5"/>
+      <c r="B69" s="5"/>
+      <c r="C69" s="5"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="3" t="n">
-        <v>173419</v>
-      </c>
-      <c r="B70" s="3" t="n">
-        <v>2130589</v>
-      </c>
-      <c r="C70" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A70" s="5"/>
+      <c r="B70" s="5"/>
+      <c r="C70" s="5"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="3" t="n">
-        <v>173419</v>
-      </c>
-      <c r="B71" s="3" t="n">
-        <v>2130591</v>
-      </c>
-      <c r="C71" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A71" s="5"/>
+      <c r="B71" s="5"/>
+      <c r="C71" s="5"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="3" t="n">
-        <v>173460</v>
-      </c>
-      <c r="B72" s="3" t="n">
-        <v>2054183</v>
-      </c>
-      <c r="C72" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A72" s="5"/>
+      <c r="B72" s="5"/>
+      <c r="C72" s="5"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="3" t="n">
-        <v>173460</v>
-      </c>
-      <c r="B73" s="3" t="n">
-        <v>2054184</v>
-      </c>
-      <c r="C73" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A73" s="5"/>
+      <c r="B73" s="5"/>
+      <c r="C73" s="5"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="3" t="n">
-        <v>173462</v>
-      </c>
-      <c r="B74" s="3" t="n">
-        <v>1768763</v>
-      </c>
-      <c r="C74" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A74" s="5"/>
+      <c r="B74" s="5"/>
+      <c r="C74" s="5"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="3" t="n">
-        <v>173462</v>
-      </c>
-      <c r="B75" s="3" t="n">
-        <v>1768764</v>
-      </c>
-      <c r="C75" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A75" s="5"/>
+      <c r="B75" s="5"/>
+      <c r="C75" s="5"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="3" t="n">
-        <v>173462</v>
-      </c>
-      <c r="B76" s="3" t="n">
-        <v>1768766</v>
-      </c>
-      <c r="C76" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A76" s="5"/>
+      <c r="B76" s="5"/>
+      <c r="C76" s="5"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="3" t="n">
-        <v>173462</v>
-      </c>
-      <c r="B77" s="3" t="n">
-        <v>1768777</v>
-      </c>
-      <c r="C77" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A77" s="5"/>
+      <c r="B77" s="5"/>
+      <c r="C77" s="5"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="3" t="n">
-        <v>173462</v>
-      </c>
-      <c r="B78" s="3" t="n">
-        <v>1768778</v>
-      </c>
-      <c r="C78" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A78" s="5"/>
+      <c r="B78" s="5"/>
+      <c r="C78" s="5"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="3" t="n">
-        <v>173462</v>
-      </c>
-      <c r="B79" s="3" t="n">
-        <v>1768779</v>
-      </c>
-      <c r="C79" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A79" s="5"/>
+      <c r="B79" s="5"/>
+      <c r="C79" s="5"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="3" t="n">
-        <v>173465</v>
-      </c>
-      <c r="B80" s="3" t="n">
-        <v>1768392</v>
-      </c>
-      <c r="C80" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A80" s="5"/>
+      <c r="B80" s="5"/>
+      <c r="C80" s="5"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="3" t="n">
-        <v>173465</v>
-      </c>
-      <c r="B81" s="3" t="n">
-        <v>1768393</v>
-      </c>
-      <c r="C81" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A81" s="5"/>
+      <c r="B81" s="5"/>
+      <c r="C81" s="5"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="3" t="n">
-        <v>173465</v>
-      </c>
-      <c r="B82" s="3" t="n">
-        <v>1768394</v>
-      </c>
-      <c r="C82" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A82" s="5"/>
+      <c r="B82" s="5"/>
+      <c r="C82" s="5"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="3" t="n">
-        <v>173465</v>
-      </c>
-      <c r="B83" s="3" t="n">
-        <v>1768395</v>
-      </c>
-      <c r="C83" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A83" s="5"/>
+      <c r="B83" s="5"/>
+      <c r="C83" s="5"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="3" t="n">
-        <v>173465</v>
-      </c>
-      <c r="B84" s="3" t="n">
-        <v>1768396</v>
-      </c>
-      <c r="C84" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A84" s="5"/>
+      <c r="B84" s="5"/>
+      <c r="C84" s="5"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="3" t="n">
-        <v>173465</v>
-      </c>
-      <c r="B85" s="3" t="n">
-        <v>1768397</v>
-      </c>
-      <c r="C85" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A85" s="5"/>
+      <c r="B85" s="5"/>
+      <c r="C85" s="5"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="3" t="n">
-        <v>173467</v>
-      </c>
-      <c r="B86" s="3" t="n">
-        <v>2054171</v>
-      </c>
-      <c r="C86" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A86" s="5"/>
+      <c r="B86" s="5"/>
+      <c r="C86" s="5"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="3" t="n">
-        <v>173503</v>
-      </c>
-      <c r="B87" s="3" t="n">
-        <v>2186866</v>
-      </c>
-      <c r="C87" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A87" s="5"/>
+      <c r="B87" s="5"/>
+      <c r="C87" s="5"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="3" t="n">
-        <v>173503</v>
-      </c>
-      <c r="B88" s="3" t="n">
-        <v>2186868</v>
-      </c>
-      <c r="C88" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A88" s="5"/>
+      <c r="B88" s="5"/>
+      <c r="C88" s="5"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="3" t="n">
-        <v>173503</v>
-      </c>
-      <c r="B89" s="3" t="n">
-        <v>2186871</v>
-      </c>
-      <c r="C89" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A89" s="5"/>
+      <c r="B89" s="5"/>
+      <c r="C89" s="5"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="3" t="n">
-        <v>173503</v>
-      </c>
-      <c r="B90" s="3" t="n">
-        <v>2186872</v>
-      </c>
-      <c r="C90" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A90" s="5"/>
+      <c r="B90" s="5"/>
+      <c r="C90" s="5"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="3" t="n">
-        <v>173503</v>
-      </c>
-      <c r="B91" s="3" t="n">
-        <v>2186873</v>
-      </c>
-      <c r="C91" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A91" s="5"/>
+      <c r="B91" s="5"/>
+      <c r="C91" s="5"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="3" t="n">
-        <v>173503</v>
-      </c>
-      <c r="B92" s="3" t="n">
-        <v>2186874</v>
-      </c>
-      <c r="C92" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A92" s="5"/>
+      <c r="B92" s="5"/>
+      <c r="C92" s="5"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="3" t="n">
-        <v>173508</v>
-      </c>
-      <c r="B93" s="3" t="n">
-        <v>1768821</v>
-      </c>
-      <c r="C93" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A93" s="5"/>
+      <c r="B93" s="5"/>
+      <c r="C93" s="5"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="3" t="n">
-        <v>173508</v>
-      </c>
-      <c r="B94" s="3" t="n">
-        <v>1768841</v>
-      </c>
-      <c r="C94" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A94" s="5"/>
+      <c r="B94" s="5"/>
+      <c r="C94" s="5"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="3" t="n">
-        <v>173508</v>
-      </c>
-      <c r="B95" s="3" t="n">
-        <v>1768844</v>
-      </c>
-      <c r="C95" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A95" s="5"/>
+      <c r="B95" s="5"/>
+      <c r="C95" s="5"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="3" t="n">
-        <v>173508</v>
-      </c>
-      <c r="B96" s="3" t="n">
-        <v>1768845</v>
-      </c>
-      <c r="C96" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A96" s="5"/>
+      <c r="B96" s="5"/>
+      <c r="C96" s="5"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="3" t="n">
-        <v>173508</v>
-      </c>
-      <c r="B97" s="3" t="n">
-        <v>1768846</v>
-      </c>
-      <c r="C97" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A97" s="5"/>
+      <c r="B97" s="5"/>
+      <c r="C97" s="5"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="3" t="n">
-        <v>173508</v>
-      </c>
-      <c r="B98" s="3" t="n">
-        <v>1768847</v>
-      </c>
-      <c r="C98" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A98" s="5"/>
+      <c r="B98" s="5"/>
+      <c r="C98" s="5"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="3" t="n">
-        <v>173565</v>
-      </c>
-      <c r="B99" s="3" t="n">
-        <v>1769408</v>
-      </c>
-      <c r="C99" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A99" s="5"/>
+      <c r="B99" s="5"/>
+      <c r="C99" s="5"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="3" t="n">
-        <v>173565</v>
-      </c>
-      <c r="B100" s="3" t="n">
-        <v>1769432</v>
-      </c>
-      <c r="C100" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A100" s="5"/>
+      <c r="B100" s="5"/>
+      <c r="C100" s="5"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="3" t="n">
-        <v>173565</v>
-      </c>
-      <c r="B101" s="3" t="n">
-        <v>1769436</v>
-      </c>
-      <c r="C101" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A101" s="5"/>
+      <c r="B101" s="5"/>
+      <c r="C101" s="5"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="3" t="n">
-        <v>173565</v>
-      </c>
-      <c r="B102" s="3" t="n">
-        <v>1769438</v>
-      </c>
-      <c r="C102" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A102" s="5"/>
+      <c r="B102" s="5"/>
+      <c r="C102" s="5"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="3" t="n">
-        <v>173565</v>
-      </c>
-      <c r="B103" s="3" t="n">
-        <v>1769440</v>
-      </c>
-      <c r="C103" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A103" s="5"/>
+      <c r="B103" s="5"/>
+      <c r="C103" s="5"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="3" t="n">
-        <v>173565</v>
-      </c>
-      <c r="B104" s="3" t="n">
-        <v>1769442</v>
-      </c>
-      <c r="C104" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A104" s="5"/>
+      <c r="B104" s="5"/>
+      <c r="C104" s="5"/>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A105" s="3" t="n">
-        <v>173583</v>
-      </c>
-      <c r="B105" s="3" t="n">
-        <v>2313151</v>
-      </c>
-      <c r="C105" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A105" s="5"/>
+      <c r="B105" s="5"/>
+      <c r="C105" s="5"/>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A106" s="3" t="n">
-        <v>173583</v>
-      </c>
-      <c r="B106" s="3" t="n">
-        <v>2313152</v>
-      </c>
-      <c r="C106" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A106" s="5"/>
+      <c r="B106" s="5"/>
+      <c r="C106" s="5"/>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A107" s="3" t="n">
-        <v>173583</v>
-      </c>
-      <c r="B107" s="3" t="n">
-        <v>2313153</v>
-      </c>
-      <c r="C107" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A107" s="5"/>
+      <c r="B107" s="5"/>
+      <c r="C107" s="5"/>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A108" s="3" t="n">
-        <v>173583</v>
-      </c>
-      <c r="B108" s="3" t="n">
-        <v>2313154</v>
-      </c>
-      <c r="C108" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A108" s="5"/>
+      <c r="B108" s="5"/>
+      <c r="C108" s="5"/>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A109" s="3" t="n">
-        <v>173583</v>
-      </c>
-      <c r="B109" s="3" t="n">
-        <v>2313156</v>
-      </c>
-      <c r="C109" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A109" s="5"/>
+      <c r="B109" s="5"/>
+      <c r="C109" s="5"/>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A110" s="3" t="n">
-        <v>173583</v>
-      </c>
-      <c r="B110" s="3" t="n">
-        <v>2313157</v>
-      </c>
-      <c r="C110" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A110" s="5"/>
+      <c r="B110" s="5"/>
+      <c r="C110" s="5"/>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A111" s="3" t="n">
-        <v>173624</v>
-      </c>
-      <c r="B111" s="3" t="n">
-        <v>2313132</v>
-      </c>
-      <c r="C111" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A111" s="5"/>
+      <c r="B111" s="5"/>
+      <c r="C111" s="5"/>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A112" s="3" t="n">
-        <v>173624</v>
-      </c>
-      <c r="B112" s="3" t="n">
-        <v>2313133</v>
-      </c>
-      <c r="C112" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A112" s="5"/>
+      <c r="B112" s="5"/>
+      <c r="C112" s="5"/>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A113" s="3" t="n">
-        <v>173624</v>
-      </c>
-      <c r="B113" s="3" t="n">
-        <v>2313134</v>
-      </c>
-      <c r="C113" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A113" s="5"/>
+      <c r="B113" s="5"/>
+      <c r="C113" s="5"/>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A114" s="3" t="n">
-        <v>173624</v>
-      </c>
-      <c r="B114" s="3" t="n">
-        <v>2313135</v>
-      </c>
-      <c r="C114" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A114" s="5"/>
+      <c r="B114" s="5"/>
+      <c r="C114" s="5"/>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A115" s="3" t="n">
-        <v>173624</v>
-      </c>
-      <c r="B115" s="3" t="n">
-        <v>2313136</v>
-      </c>
-      <c r="C115" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A115" s="5"/>
+      <c r="B115" s="5"/>
+      <c r="C115" s="5"/>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A116" s="3" t="n">
-        <v>173624</v>
-      </c>
-      <c r="B116" s="3" t="n">
-        <v>2313140</v>
-      </c>
-      <c r="C116" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A116" s="5"/>
+      <c r="B116" s="5"/>
+      <c r="C116" s="5"/>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A117" s="3" t="n">
-        <v>173647</v>
-      </c>
-      <c r="B117" s="3" t="n">
-        <v>2000741</v>
-      </c>
-      <c r="C117" s="3" t="n">
-        <v>2</v>
-      </c>
+      <c r="A117" s="5"/>
+      <c r="B117" s="5"/>
+      <c r="C117" s="5"/>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A118" s="3" t="n">
-        <v>173647</v>
-      </c>
-      <c r="B118" s="3" t="n">
-        <v>2000795</v>
-      </c>
-      <c r="C118" s="3" t="n">
-        <v>2</v>
-      </c>
+      <c r="A118" s="5"/>
+      <c r="B118" s="5"/>
+      <c r="C118" s="5"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A119" s="3" t="n">
-        <v>173647</v>
-      </c>
-      <c r="B119" s="3" t="n">
-        <v>2074278</v>
-      </c>
-      <c r="C119" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A119" s="5"/>
+      <c r="B119" s="5"/>
+      <c r="C119" s="5"/>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A120" s="3" t="n">
-        <v>173654</v>
-      </c>
-      <c r="B120" s="3" t="n">
-        <v>1879822</v>
-      </c>
-      <c r="C120" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A120" s="5"/>
+      <c r="B120" s="5"/>
+      <c r="C120" s="5"/>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A121" s="3" t="n">
-        <v>173654</v>
-      </c>
-      <c r="B121" s="3" t="n">
-        <v>2316023</v>
-      </c>
-      <c r="C121" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A121" s="5"/>
+      <c r="B121" s="5"/>
+      <c r="C121" s="5"/>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A122" s="3" t="n">
-        <v>173654</v>
-      </c>
-      <c r="B122" s="3" t="n">
-        <v>2316024</v>
-      </c>
-      <c r="C122" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A122" s="5"/>
+      <c r="B122" s="5"/>
+      <c r="C122" s="5"/>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A123" s="3" t="n">
-        <v>173659</v>
-      </c>
-      <c r="B123" s="3" t="n">
-        <v>1768987</v>
-      </c>
-      <c r="C123" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A123" s="5"/>
+      <c r="B123" s="5"/>
+      <c r="C123" s="5"/>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A124" s="3" t="n">
-        <v>173659</v>
-      </c>
-      <c r="B124" s="3" t="n">
-        <v>1768988</v>
-      </c>
-      <c r="C124" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A124" s="5"/>
+      <c r="B124" s="5"/>
+      <c r="C124" s="5"/>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A125" s="3" t="n">
-        <v>173659</v>
-      </c>
-      <c r="B125" s="3" t="n">
-        <v>1768991</v>
-      </c>
-      <c r="C125" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A125" s="5"/>
+      <c r="B125" s="5"/>
+      <c r="C125" s="5"/>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A126" s="3" t="n">
-        <v>173659</v>
-      </c>
-      <c r="B126" s="3" t="n">
-        <v>1913468</v>
-      </c>
-      <c r="C126" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A126" s="5"/>
+      <c r="B126" s="5"/>
+      <c r="C126" s="5"/>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A127" s="3" t="n">
-        <v>173662</v>
-      </c>
-      <c r="B127" s="3" t="n">
-        <v>1744274</v>
-      </c>
-      <c r="C127" s="3" t="n">
-        <v>3</v>
-      </c>
+      <c r="A127" s="5"/>
+      <c r="B127" s="5"/>
+      <c r="C127" s="5"/>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A128" s="3" t="n">
-        <v>173662</v>
-      </c>
-      <c r="B128" s="3" t="n">
-        <v>1755812</v>
-      </c>
-      <c r="C128" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A128" s="5"/>
+      <c r="B128" s="5"/>
+      <c r="C128" s="5"/>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A129" s="3" t="n">
-        <v>173662</v>
-      </c>
-      <c r="B129" s="3" t="n">
-        <v>1744286</v>
-      </c>
-      <c r="C129" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A129" s="5"/>
+      <c r="B129" s="5"/>
+      <c r="C129" s="5"/>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A130" s="3" t="n">
-        <v>173664</v>
-      </c>
-      <c r="B130" s="3" t="n">
-        <v>1769018</v>
-      </c>
-      <c r="C130" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A130" s="5"/>
+      <c r="B130" s="5"/>
+      <c r="C130" s="5"/>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A131" s="3" t="n">
-        <v>173664</v>
-      </c>
-      <c r="B131" s="3" t="n">
-        <v>1769019</v>
-      </c>
-      <c r="C131" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A131" s="5"/>
+      <c r="B131" s="5"/>
+      <c r="C131" s="5"/>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A132" s="3" t="n">
-        <v>173669</v>
-      </c>
-      <c r="B132" s="3" t="n">
-        <v>1766223</v>
-      </c>
-      <c r="C132" s="3" t="n">
-        <v>2</v>
-      </c>
+      <c r="A132" s="5"/>
+      <c r="B132" s="5"/>
+      <c r="C132" s="5"/>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A133" s="3" t="n">
-        <v>173669</v>
-      </c>
-      <c r="B133" s="3" t="n">
-        <v>1768992</v>
-      </c>
-      <c r="C133" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A133" s="5"/>
+      <c r="B133" s="5"/>
+      <c r="C133" s="5"/>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A134" s="3" t="n">
-        <v>173669</v>
-      </c>
-      <c r="B134" s="3" t="n">
-        <v>1769017</v>
-      </c>
-      <c r="C134" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A134" s="5"/>
+      <c r="B134" s="5"/>
+      <c r="C134" s="5"/>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A135" s="3" t="n">
-        <v>173669</v>
-      </c>
-      <c r="B135" s="3" t="n">
-        <v>1769020</v>
-      </c>
-      <c r="C135" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A135" s="5"/>
+      <c r="B135" s="5"/>
+      <c r="C135" s="5"/>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A136" s="3" t="n">
-        <v>173669</v>
-      </c>
-      <c r="B136" s="3" t="n">
-        <v>1769025</v>
-      </c>
-      <c r="C136" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A136" s="5"/>
+      <c r="B136" s="5"/>
+      <c r="C136" s="5"/>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A137" s="3" t="n">
-        <v>173669</v>
-      </c>
-      <c r="B137" s="3" t="n">
-        <v>1769026</v>
-      </c>
-      <c r="C137" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A137" s="5"/>
+      <c r="B137" s="5"/>
+      <c r="C137" s="5"/>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A138" s="3" t="n">
-        <v>173669</v>
-      </c>
-      <c r="B138" s="3" t="n">
-        <v>1769029</v>
-      </c>
-      <c r="C138" s="3" t="n">
-        <v>2</v>
-      </c>
+      <c r="A138" s="5"/>
+      <c r="B138" s="5"/>
+      <c r="C138" s="5"/>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A139" s="3" t="n">
-        <v>173669</v>
-      </c>
-      <c r="B139" s="3" t="n">
-        <v>1769033</v>
-      </c>
-      <c r="C139" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A139" s="5"/>
+      <c r="B139" s="5"/>
+      <c r="C139" s="5"/>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A140" s="3" t="n">
-        <v>173669</v>
-      </c>
-      <c r="B140" s="3" t="n">
-        <v>1769035</v>
-      </c>
-      <c r="C140" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A140" s="5"/>
+      <c r="B140" s="5"/>
+      <c r="C140" s="5"/>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A141" s="3" t="n">
-        <v>173669</v>
-      </c>
-      <c r="B141" s="3" t="n">
-        <v>2074285</v>
-      </c>
-      <c r="C141" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A141" s="5"/>
+      <c r="B141" s="5"/>
+      <c r="C141" s="5"/>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A142" s="3" t="n">
-        <v>173669</v>
-      </c>
-      <c r="B142" s="3" t="n">
-        <v>2074287</v>
-      </c>
-      <c r="C142" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A142" s="5"/>
+      <c r="B142" s="5"/>
+      <c r="C142" s="5"/>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A143" s="3" t="n">
-        <v>173671</v>
-      </c>
-      <c r="B143" s="3" t="n">
-        <v>1979801</v>
-      </c>
-      <c r="C143" s="3" t="n">
-        <v>2</v>
-      </c>
+      <c r="A143" s="5"/>
+      <c r="B143" s="5"/>
+      <c r="C143" s="5"/>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A144" s="3" t="n">
-        <v>173671</v>
-      </c>
-      <c r="B144" s="3" t="n">
-        <v>1979804</v>
-      </c>
-      <c r="C144" s="3" t="n">
-        <v>2</v>
-      </c>
+      <c r="A144" s="5"/>
+      <c r="B144" s="5"/>
+      <c r="C144" s="5"/>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A145" s="3" t="n">
-        <v>173671</v>
-      </c>
-      <c r="B145" s="3" t="n">
-        <v>1744163</v>
-      </c>
-      <c r="C145" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A145" s="5"/>
+      <c r="B145" s="5"/>
+      <c r="C145" s="5"/>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A146" s="3" t="n">
-        <v>173671</v>
-      </c>
-      <c r="B146" s="3" t="n">
-        <v>1979805</v>
-      </c>
-      <c r="C146" s="3" t="n">
-        <v>2</v>
-      </c>
+      <c r="A146" s="5"/>
+      <c r="B146" s="5"/>
+      <c r="C146" s="5"/>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A147" s="3" t="n">
-        <v>173671</v>
-      </c>
-      <c r="B147" s="3" t="n">
-        <v>1979806</v>
-      </c>
-      <c r="C147" s="3" t="n">
-        <v>2</v>
-      </c>
+      <c r="A147" s="5"/>
+      <c r="B147" s="5"/>
+      <c r="C147" s="5"/>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A148" s="3" t="n">
-        <v>173671</v>
-      </c>
-      <c r="B148" s="3" t="n">
-        <v>1768710</v>
-      </c>
-      <c r="C148" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A148" s="5"/>
+      <c r="B148" s="5"/>
+      <c r="C148" s="5"/>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A149" s="3" t="n">
-        <v>173671</v>
-      </c>
-      <c r="B149" s="3" t="n">
-        <v>1768716</v>
-      </c>
-      <c r="C149" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A149" s="5"/>
+      <c r="B149" s="5"/>
+      <c r="C149" s="5"/>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A150" s="3" t="n">
-        <v>173671</v>
-      </c>
-      <c r="B150" s="3" t="n">
-        <v>1768727</v>
-      </c>
-      <c r="C150" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A150" s="5"/>
+      <c r="B150" s="5"/>
+      <c r="C150" s="5"/>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A151" s="3" t="n">
-        <v>173672</v>
-      </c>
-      <c r="B151" s="3" t="n">
-        <v>1766815</v>
-      </c>
-      <c r="C151" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A151" s="5"/>
+      <c r="B151" s="5"/>
+      <c r="C151" s="5"/>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A152" s="3" t="n">
-        <v>173672</v>
-      </c>
-      <c r="B152" s="3" t="n">
-        <v>1766818</v>
-      </c>
-      <c r="C152" s="3" t="n">
-        <v>2</v>
-      </c>
+      <c r="A152" s="5"/>
+      <c r="B152" s="5"/>
+      <c r="C152" s="5"/>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A153" s="3" t="n">
-        <v>173673</v>
-      </c>
-      <c r="B153" s="3" t="n">
-        <v>1744330</v>
-      </c>
-      <c r="C153" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A153" s="5"/>
+      <c r="B153" s="5"/>
+      <c r="C153" s="5"/>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A154" s="3" t="n">
-        <v>173673</v>
-      </c>
-      <c r="B154" s="3" t="n">
-        <v>1768540</v>
-      </c>
-      <c r="C154" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A154" s="5"/>
+      <c r="B154" s="5"/>
+      <c r="C154" s="5"/>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A155" s="3" t="n">
-        <v>173673</v>
-      </c>
-      <c r="B155" s="3" t="n">
-        <v>1768544</v>
-      </c>
-      <c r="C155" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A155" s="5"/>
+      <c r="B155" s="5"/>
+      <c r="C155" s="5"/>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A156" s="3" t="n">
-        <v>173673</v>
-      </c>
-      <c r="B156" s="3" t="n">
-        <v>1768545</v>
-      </c>
-      <c r="C156" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A156" s="5"/>
+      <c r="B156" s="5"/>
+      <c r="C156" s="5"/>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A157" s="3" t="n">
-        <v>173674</v>
-      </c>
-      <c r="B157" s="3" t="n">
-        <v>1744455</v>
-      </c>
-      <c r="C157" s="3" t="n">
-        <v>2</v>
-      </c>
+      <c r="A157" s="5"/>
+      <c r="B157" s="5"/>
+      <c r="C157" s="5"/>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A158" s="3" t="n">
-        <v>173674</v>
-      </c>
-      <c r="B158" s="3" t="n">
-        <v>1744456</v>
-      </c>
-      <c r="C158" s="3" t="n">
-        <v>2</v>
-      </c>
+      <c r="A158" s="5"/>
+      <c r="B158" s="5"/>
+      <c r="C158" s="5"/>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A159" s="3" t="n">
-        <v>173674</v>
-      </c>
-      <c r="B159" s="3" t="n">
-        <v>1744458</v>
-      </c>
-      <c r="C159" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A159" s="5"/>
+      <c r="B159" s="5"/>
+      <c r="C159" s="5"/>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A160" s="3" t="n">
-        <v>173674</v>
-      </c>
-      <c r="B160" s="3" t="n">
-        <v>1766877</v>
-      </c>
-      <c r="C160" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A160" s="5"/>
+      <c r="B160" s="5"/>
+      <c r="C160" s="5"/>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A161" s="3" t="n">
-        <v>173674</v>
-      </c>
-      <c r="B161" s="3" t="n">
-        <v>1766879</v>
-      </c>
-      <c r="C161" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A161" s="5"/>
+      <c r="B161" s="5"/>
+      <c r="C161" s="5"/>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A162" s="3" t="n">
-        <v>173674</v>
-      </c>
-      <c r="B162" s="3" t="n">
-        <v>1766881</v>
-      </c>
-      <c r="C162" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A162" s="5"/>
+      <c r="B162" s="5"/>
+      <c r="C162" s="5"/>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A163" s="3" t="n">
-        <v>173674</v>
-      </c>
-      <c r="B163" s="3" t="n">
-        <v>1766882</v>
-      </c>
-      <c r="C163" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A163" s="5"/>
+      <c r="B163" s="5"/>
+      <c r="C163" s="5"/>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A164" s="3" t="n">
-        <v>173674</v>
-      </c>
-      <c r="B164" s="3" t="n">
-        <v>1766883</v>
-      </c>
-      <c r="C164" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A164" s="5"/>
+      <c r="B164" s="5"/>
+      <c r="C164" s="5"/>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A165" s="3" t="n">
-        <v>173675</v>
-      </c>
-      <c r="B165" s="3" t="n">
-        <v>1768879</v>
-      </c>
-      <c r="C165" s="3" t="n">
-        <v>3</v>
-      </c>
+      <c r="A165" s="5"/>
+      <c r="B165" s="5"/>
+      <c r="C165" s="5"/>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A166" s="3" t="n">
-        <v>173675</v>
-      </c>
-      <c r="B166" s="3" t="n">
-        <v>1768883</v>
-      </c>
-      <c r="C166" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A166" s="5"/>
+      <c r="B166" s="5"/>
+      <c r="C166" s="5"/>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A167" s="3" t="n">
-        <v>173675</v>
-      </c>
-      <c r="B167" s="3" t="n">
-        <v>1768886</v>
-      </c>
-      <c r="C167" s="3" t="n">
-        <v>3</v>
-      </c>
+      <c r="A167" s="5"/>
+      <c r="B167" s="5"/>
+      <c r="C167" s="5"/>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A168" s="3" t="n">
-        <v>173675</v>
-      </c>
-      <c r="B168" s="3" t="n">
-        <v>1768889</v>
-      </c>
-      <c r="C168" s="3" t="n">
-        <v>3</v>
-      </c>
+      <c r="A168" s="5"/>
+      <c r="B168" s="5"/>
+      <c r="C168" s="5"/>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A169" s="3" t="n">
-        <v>173676</v>
-      </c>
-      <c r="B169" s="3" t="n">
-        <v>1768910</v>
-      </c>
-      <c r="C169" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A169" s="5"/>
+      <c r="B169" s="5"/>
+      <c r="C169" s="5"/>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A170" s="3" t="n">
-        <v>173676</v>
-      </c>
-      <c r="B170" s="3" t="n">
-        <v>1768916</v>
-      </c>
-      <c r="C170" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A170" s="5"/>
+      <c r="B170" s="5"/>
+      <c r="C170" s="5"/>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A171" s="3" t="n">
-        <v>173676</v>
-      </c>
-      <c r="B171" s="3" t="n">
-        <v>1768917</v>
-      </c>
-      <c r="C171" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A171" s="5"/>
+      <c r="B171" s="5"/>
+      <c r="C171" s="5"/>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A172" s="3" t="n">
-        <v>173676</v>
-      </c>
-      <c r="B172" s="3" t="n">
-        <v>1768919</v>
-      </c>
-      <c r="C172" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A172" s="5"/>
+      <c r="B172" s="5"/>
+      <c r="C172" s="5"/>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A173" s="3" t="n">
-        <v>173683</v>
-      </c>
-      <c r="B173" s="3" t="n">
-        <v>1744539</v>
-      </c>
-      <c r="C173" s="3" t="n">
-        <v>2</v>
-      </c>
+      <c r="A173" s="5"/>
+      <c r="B173" s="5"/>
+      <c r="C173" s="5"/>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A174" s="3" t="n">
-        <v>173684</v>
-      </c>
-      <c r="B174" s="3" t="n">
-        <v>1744372</v>
-      </c>
-      <c r="C174" s="3" t="n">
-        <v>2</v>
-      </c>
+      <c r="A174" s="5"/>
+      <c r="B174" s="5"/>
+      <c r="C174" s="5"/>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A175" s="3" t="n">
-        <v>173684</v>
-      </c>
-      <c r="B175" s="3" t="n">
-        <v>1744375</v>
-      </c>
-      <c r="C175" s="3" t="n">
-        <v>2</v>
-      </c>
+      <c r="A175" s="5"/>
+      <c r="B175" s="5"/>
+      <c r="C175" s="5"/>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A176" s="3" t="n">
-        <v>173684</v>
-      </c>
-      <c r="B176" s="3" t="n">
-        <v>2169949</v>
-      </c>
-      <c r="C176" s="3" t="n">
-        <v>2</v>
-      </c>
+      <c r="A176" s="5"/>
+      <c r="B176" s="5"/>
+      <c r="C176" s="5"/>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A177" s="3" t="n">
-        <v>173684</v>
-      </c>
-      <c r="B177" s="3" t="n">
-        <v>1744387</v>
-      </c>
-      <c r="C177" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A177" s="5"/>
+      <c r="B177" s="5"/>
+      <c r="C177" s="5"/>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A178" s="3" t="n">
-        <v>173684</v>
-      </c>
-      <c r="B178" s="3" t="n">
-        <v>1913578</v>
-      </c>
-      <c r="C178" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A178" s="5"/>
+      <c r="B178" s="5"/>
+      <c r="C178" s="5"/>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A179" s="3" t="n">
-        <v>173684</v>
-      </c>
-      <c r="B179" s="3" t="n">
-        <v>1913579</v>
-      </c>
-      <c r="C179" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A179" s="5"/>
+      <c r="B179" s="5"/>
+      <c r="C179" s="5"/>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A180" s="3" t="n">
-        <v>173698</v>
-      </c>
-      <c r="B180" s="3" t="n">
-        <v>1766141</v>
-      </c>
-      <c r="C180" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A180" s="5"/>
+      <c r="B180" s="5"/>
+      <c r="C180" s="5"/>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A181" s="3" t="n">
-        <v>173698</v>
-      </c>
-      <c r="B181" s="3" t="n">
-        <v>1766147</v>
-      </c>
-      <c r="C181" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A181" s="5"/>
+      <c r="B181" s="5"/>
+      <c r="C181" s="5"/>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A182" s="3" t="n">
-        <v>173698</v>
-      </c>
-      <c r="B182" s="3" t="n">
-        <v>1766156</v>
-      </c>
-      <c r="C182" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A182" s="5"/>
+      <c r="B182" s="5"/>
+      <c r="C182" s="5"/>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A183" s="3" t="n">
-        <v>173698</v>
-      </c>
-      <c r="B183" s="3" t="n">
-        <v>2103024</v>
-      </c>
-      <c r="C183" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A183" s="5"/>
+      <c r="B183" s="5"/>
+      <c r="C183" s="5"/>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A184" s="3" t="n">
-        <v>173698</v>
-      </c>
-      <c r="B184" s="3" t="n">
-        <v>2194865</v>
-      </c>
-      <c r="C184" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A184" s="5"/>
+      <c r="B184" s="5"/>
+      <c r="C184" s="5"/>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A185" s="3" t="n">
-        <v>173700</v>
-      </c>
-      <c r="B185" s="3" t="n">
-        <v>1969712</v>
-      </c>
-      <c r="C185" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A185" s="5"/>
+      <c r="B185" s="5"/>
+      <c r="C185" s="5"/>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A186" s="3" t="n">
-        <v>173703</v>
-      </c>
-      <c r="B186" s="3" t="n">
-        <v>1769006</v>
-      </c>
-      <c r="C186" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A186" s="5"/>
+      <c r="B186" s="5"/>
+      <c r="C186" s="5"/>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A187" s="3" t="n">
-        <v>173704</v>
-      </c>
-      <c r="B187" s="3" t="n">
-        <v>1744513</v>
-      </c>
-      <c r="C187" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A187" s="5"/>
+      <c r="B187" s="5"/>
+      <c r="C187" s="5"/>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A188" s="3" t="n">
-        <v>173704</v>
-      </c>
-      <c r="B188" s="3" t="n">
-        <v>1744514</v>
-      </c>
-      <c r="C188" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A188" s="5"/>
+      <c r="B188" s="5"/>
+      <c r="C188" s="5"/>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A189" s="3" t="n">
-        <v>173704</v>
-      </c>
-      <c r="B189" s="3" t="n">
-        <v>1744515</v>
-      </c>
-      <c r="C189" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A189" s="5"/>
+      <c r="B189" s="5"/>
+      <c r="C189" s="5"/>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A190" s="3" t="n">
-        <v>173706</v>
-      </c>
-      <c r="B190" s="3" t="n">
-        <v>1955582</v>
-      </c>
-      <c r="C190" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A190" s="5"/>
+      <c r="B190" s="5"/>
+      <c r="C190" s="5"/>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A191" s="3" t="n">
-        <v>173706</v>
-      </c>
-      <c r="B191" s="3" t="n">
-        <v>1768965</v>
-      </c>
-      <c r="C191" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A191" s="5"/>
+      <c r="B191" s="5"/>
+      <c r="C191" s="5"/>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A192" s="3" t="n">
-        <v>173706</v>
-      </c>
-      <c r="B192" s="3" t="n">
-        <v>1768966</v>
-      </c>
-      <c r="C192" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A192" s="5"/>
+      <c r="B192" s="5"/>
+      <c r="C192" s="5"/>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A193" s="3" t="n">
-        <v>173706</v>
-      </c>
-      <c r="B193" s="3" t="n">
-        <v>1768969</v>
-      </c>
-      <c r="C193" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A193" s="5"/>
+      <c r="B193" s="5"/>
+      <c r="C193" s="5"/>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A194" s="3" t="n">
-        <v>173706</v>
-      </c>
-      <c r="B194" s="3" t="n">
-        <v>1768972</v>
-      </c>
-      <c r="C194" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A194" s="5"/>
+      <c r="B194" s="5"/>
+      <c r="C194" s="5"/>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A195" s="3" t="n">
-        <v>173706</v>
-      </c>
-      <c r="B195" s="3" t="n">
-        <v>1768976</v>
-      </c>
-      <c r="C195" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A195" s="5"/>
+      <c r="B195" s="5"/>
+      <c r="C195" s="5"/>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A196" s="3" t="n">
-        <v>173706</v>
-      </c>
-      <c r="B196" s="3" t="n">
-        <v>1768977</v>
-      </c>
-      <c r="C196" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A196" s="5"/>
+      <c r="B196" s="5"/>
+      <c r="C196" s="5"/>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A197" s="3" t="n">
-        <v>178003</v>
-      </c>
-      <c r="B197" s="3" t="n">
-        <v>1823290</v>
-      </c>
-      <c r="C197" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A197" s="5"/>
+      <c r="B197" s="5"/>
+      <c r="C197" s="5"/>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A198" s="3" t="n">
-        <v>178003</v>
-      </c>
-      <c r="B198" s="3" t="n">
-        <v>1823291</v>
-      </c>
-      <c r="C198" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A198" s="5"/>
+      <c r="B198" s="5"/>
+      <c r="C198" s="5"/>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A199" s="3" t="n">
-        <v>178004</v>
-      </c>
-      <c r="B199" s="3" t="n">
-        <v>1823292</v>
-      </c>
-      <c r="C199" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A199" s="5"/>
+      <c r="B199" s="5"/>
+      <c r="C199" s="5"/>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A200" s="3" t="n">
-        <v>178005</v>
-      </c>
-      <c r="B200" s="3" t="n">
-        <v>1823298</v>
-      </c>
-      <c r="C200" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A200" s="5"/>
+      <c r="B200" s="5"/>
+      <c r="C200" s="5"/>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A201" s="3" t="n">
-        <v>178005</v>
-      </c>
-      <c r="B201" s="3" t="n">
-        <v>1823299</v>
-      </c>
-      <c r="C201" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A201" s="5"/>
+      <c r="B201" s="5"/>
+      <c r="C201" s="5"/>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A202" s="3" t="n">
-        <v>178006</v>
-      </c>
-      <c r="B202" s="3" t="n">
-        <v>1823277</v>
-      </c>
-      <c r="C202" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A202" s="5"/>
+      <c r="B202" s="5"/>
+      <c r="C202" s="5"/>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A203" s="3" t="n">
-        <v>178008</v>
-      </c>
-      <c r="B203" s="3" t="n">
-        <v>1823266</v>
-      </c>
-      <c r="C203" s="3" t="n">
-        <v>3</v>
-      </c>
+      <c r="A203" s="5"/>
+      <c r="B203" s="5"/>
+      <c r="C203" s="5"/>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A204" s="3" t="n">
-        <v>178008</v>
-      </c>
-      <c r="B204" s="3" t="n">
-        <v>1823267</v>
-      </c>
-      <c r="C204" s="3" t="n">
-        <v>3</v>
-      </c>
+      <c r="A204" s="5"/>
+      <c r="B204" s="5"/>
+      <c r="C204" s="5"/>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A205" s="3" t="n">
-        <v>178008</v>
-      </c>
-      <c r="B205" s="3" t="n">
-        <v>1823270</v>
-      </c>
-      <c r="C205" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A205" s="5"/>
+      <c r="B205" s="5"/>
+      <c r="C205" s="5"/>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A206" s="3" t="n">
-        <v>178008</v>
-      </c>
-      <c r="B206" s="3" t="n">
-        <v>1823271</v>
-      </c>
-      <c r="C206" s="3" t="n">
-        <v>3</v>
-      </c>
+      <c r="A206" s="5"/>
+      <c r="B206" s="5"/>
+      <c r="C206" s="5"/>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A207" s="3" t="n">
-        <v>178008</v>
-      </c>
-      <c r="B207" s="3" t="n">
-        <v>1823272</v>
-      </c>
-      <c r="C207" s="3" t="n">
-        <v>3</v>
-      </c>
+      <c r="A207" s="5"/>
+      <c r="B207" s="5"/>
+      <c r="C207" s="5"/>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A208" s="3" t="n">
-        <v>178008</v>
-      </c>
-      <c r="B208" s="3" t="n">
-        <v>1823275</v>
-      </c>
-      <c r="C208" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A208" s="5"/>
+      <c r="B208" s="5"/>
+      <c r="C208" s="5"/>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A209" s="3" t="n">
-        <v>178011</v>
-      </c>
-      <c r="B209" s="3" t="n">
-        <v>1823237</v>
-      </c>
-      <c r="C209" s="3" t="n">
-        <v>3</v>
-      </c>
+      <c r="A209" s="5"/>
+      <c r="B209" s="5"/>
+      <c r="C209" s="5"/>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A210" s="3" t="n">
-        <v>178011</v>
-      </c>
-      <c r="B210" s="3" t="n">
-        <v>1823238</v>
-      </c>
-      <c r="C210" s="3" t="n">
-        <v>3</v>
-      </c>
+      <c r="A210" s="5"/>
+      <c r="B210" s="5"/>
+      <c r="C210" s="5"/>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A211" s="3" t="n">
-        <v>178011</v>
-      </c>
-      <c r="B211" s="3" t="n">
-        <v>1823239</v>
-      </c>
-      <c r="C211" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A211" s="5"/>
+      <c r="B211" s="5"/>
+      <c r="C211" s="5"/>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A212" s="3" t="n">
-        <v>178011</v>
-      </c>
-      <c r="B212" s="3" t="n">
-        <v>1823240</v>
-      </c>
-      <c r="C212" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A212" s="5"/>
+      <c r="B212" s="5"/>
+      <c r="C212" s="5"/>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A213" s="3" t="n">
-        <v>178011</v>
-      </c>
-      <c r="B213" s="3" t="n">
-        <v>1823241</v>
-      </c>
-      <c r="C213" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A213" s="5"/>
+      <c r="B213" s="5"/>
+      <c r="C213" s="5"/>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A214" s="3" t="n">
-        <v>178011</v>
-      </c>
-      <c r="B214" s="3" t="n">
-        <v>1823242</v>
-      </c>
-      <c r="C214" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A214" s="5"/>
+      <c r="B214" s="5"/>
+      <c r="C214" s="5"/>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A215" s="3" t="n">
-        <v>178011</v>
-      </c>
-      <c r="B215" s="3" t="n">
-        <v>1823244</v>
-      </c>
-      <c r="C215" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A215" s="5"/>
+      <c r="B215" s="5"/>
+      <c r="C215" s="5"/>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A216" s="3" t="n">
-        <v>178011</v>
-      </c>
-      <c r="B216" s="3" t="n">
-        <v>1823245</v>
-      </c>
-      <c r="C216" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A216" s="5"/>
+      <c r="B216" s="5"/>
+      <c r="C216" s="5"/>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A217" s="3" t="n">
-        <v>178011</v>
-      </c>
-      <c r="B217" s="3" t="n">
-        <v>1823246</v>
-      </c>
-      <c r="C217" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A217" s="5"/>
+      <c r="B217" s="5"/>
+      <c r="C217" s="5"/>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A218" s="3" t="n">
-        <v>178011</v>
-      </c>
-      <c r="B218" s="3" t="n">
-        <v>1823247</v>
-      </c>
-      <c r="C218" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A218" s="5"/>
+      <c r="B218" s="5"/>
+      <c r="C218" s="5"/>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A219" s="3" t="n">
-        <v>178011</v>
-      </c>
-      <c r="B219" s="3" t="n">
-        <v>2064759</v>
-      </c>
-      <c r="C219" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A219" s="5"/>
+      <c r="B219" s="5"/>
+      <c r="C219" s="5"/>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A220" s="3" t="n">
-        <v>178011</v>
-      </c>
-      <c r="B220" s="3" t="n">
-        <v>2064823</v>
-      </c>
-      <c r="C220" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A220" s="5"/>
+      <c r="B220" s="5"/>
+      <c r="C220" s="5"/>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A221" s="3" t="n">
-        <v>178011</v>
-      </c>
-      <c r="B221" s="3" t="n">
-        <v>2064870</v>
-      </c>
-      <c r="C221" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A221" s="5"/>
+      <c r="B221" s="5"/>
+      <c r="C221" s="5"/>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A222" s="3" t="n">
-        <v>178012</v>
-      </c>
-      <c r="B222" s="3" t="n">
-        <v>1823260</v>
-      </c>
-      <c r="C222" s="3" t="n">
-        <v>3</v>
-      </c>
+      <c r="A222" s="5"/>
+      <c r="B222" s="5"/>
+      <c r="C222" s="5"/>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A223" s="3" t="n">
-        <v>178012</v>
-      </c>
-      <c r="B223" s="3" t="n">
-        <v>1823261</v>
-      </c>
-      <c r="C223" s="3" t="n">
-        <v>3</v>
-      </c>
+      <c r="A223" s="5"/>
+      <c r="B223" s="5"/>
+      <c r="C223" s="5"/>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A224" s="3" t="n">
-        <v>178012</v>
-      </c>
-      <c r="B224" s="3" t="n">
-        <v>1823262</v>
-      </c>
-      <c r="C224" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A224" s="5"/>
+      <c r="B224" s="5"/>
+      <c r="C224" s="5"/>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A225" s="3" t="n">
-        <v>178012</v>
-      </c>
-      <c r="B225" s="3" t="n">
-        <v>1823263</v>
-      </c>
-      <c r="C225" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A225" s="5"/>
+      <c r="B225" s="5"/>
+      <c r="C225" s="5"/>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A226" s="3" t="n">
-        <v>178012</v>
-      </c>
-      <c r="B226" s="3" t="n">
-        <v>1823264</v>
-      </c>
-      <c r="C226" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A226" s="5"/>
+      <c r="B226" s="5"/>
+      <c r="C226" s="5"/>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A227" s="3" t="n">
-        <v>178013</v>
-      </c>
-      <c r="B227" s="3" t="n">
-        <v>1823276</v>
-      </c>
-      <c r="C227" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A227" s="5"/>
+      <c r="B227" s="5"/>
+      <c r="C227" s="5"/>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A228" s="3" t="n">
-        <v>182730</v>
-      </c>
-      <c r="B228" s="3" t="n">
-        <v>1768293</v>
-      </c>
-      <c r="C228" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A228" s="5"/>
+      <c r="B228" s="5"/>
+      <c r="C228" s="5"/>
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A229" s="3" t="n">
-        <v>182730</v>
-      </c>
-      <c r="B229" s="3" t="n">
-        <v>1878559</v>
-      </c>
-      <c r="C229" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A229" s="5"/>
+      <c r="B229" s="5"/>
+      <c r="C229" s="5"/>
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A230" s="3" t="n">
-        <v>182730</v>
-      </c>
-      <c r="B230" s="3" t="n">
-        <v>1878556</v>
-      </c>
-      <c r="C230" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A230" s="5"/>
+      <c r="B230" s="5"/>
+      <c r="C230" s="5"/>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A231" s="3" t="n">
-        <v>182730</v>
-      </c>
-      <c r="B231" s="3" t="n">
-        <v>1878486</v>
-      </c>
-      <c r="C231" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A231" s="5"/>
+      <c r="B231" s="5"/>
+      <c r="C231" s="5"/>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A232" s="3" t="n">
-        <v>182730</v>
-      </c>
-      <c r="B232" s="3" t="n">
-        <v>2054221</v>
-      </c>
-      <c r="C232" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A232" s="5"/>
+      <c r="B232" s="5"/>
+      <c r="C232" s="5"/>
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A233" s="3" t="n">
-        <v>182770</v>
-      </c>
-      <c r="B233" s="3" t="n">
-        <v>1879827</v>
-      </c>
-      <c r="C233" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A233" s="5"/>
+      <c r="B233" s="5"/>
+      <c r="C233" s="5"/>
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A234" s="3" t="n">
-        <v>182771</v>
-      </c>
-      <c r="B234" s="3" t="n">
-        <v>1879829</v>
-      </c>
-      <c r="C234" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A234" s="5"/>
+      <c r="B234" s="5"/>
+      <c r="C234" s="5"/>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A235" s="3" t="n">
-        <v>182771</v>
-      </c>
-      <c r="B235" s="3" t="n">
-        <v>1879830</v>
-      </c>
-      <c r="C235" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A235" s="5"/>
+      <c r="B235" s="5"/>
+      <c r="C235" s="5"/>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A236" s="3" t="n">
-        <v>182771</v>
-      </c>
-      <c r="B236" s="3" t="n">
-        <v>1879832</v>
-      </c>
-      <c r="C236" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A236" s="5"/>
+      <c r="B236" s="5"/>
+      <c r="C236" s="5"/>
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A237" s="3" t="n">
-        <v>182771</v>
-      </c>
-      <c r="B237" s="3" t="n">
-        <v>1879833</v>
-      </c>
-      <c r="C237" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A237" s="5"/>
+      <c r="B237" s="5"/>
+      <c r="C237" s="5"/>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A238" s="3" t="n">
-        <v>182771</v>
-      </c>
-      <c r="B238" s="3" t="n">
-        <v>1879834</v>
-      </c>
-      <c r="C238" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A238" s="5"/>
+      <c r="B238" s="5"/>
+      <c r="C238" s="5"/>
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A239" s="3" t="n">
-        <v>182771</v>
-      </c>
-      <c r="B239" s="3" t="n">
-        <v>1879835</v>
-      </c>
-      <c r="C239" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A239" s="5"/>
+      <c r="B239" s="5"/>
+      <c r="C239" s="5"/>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A240" s="3" t="n">
-        <v>182771</v>
-      </c>
-      <c r="B240" s="3" t="n">
-        <v>1879836</v>
-      </c>
-      <c r="C240" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A240" s="5"/>
+      <c r="B240" s="5"/>
+      <c r="C240" s="5"/>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A241" s="3" t="n">
-        <v>182771</v>
-      </c>
-      <c r="B241" s="3" t="n">
-        <v>1879837</v>
-      </c>
-      <c r="C241" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A241" s="5"/>
+      <c r="B241" s="5"/>
+      <c r="C241" s="5"/>
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A242" s="3" t="n">
-        <v>182783</v>
-      </c>
-      <c r="B242" s="3" t="n">
-        <v>1879869</v>
-      </c>
-      <c r="C242" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A242" s="5"/>
+      <c r="B242" s="5"/>
+      <c r="C242" s="5"/>
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A243" s="3" t="n">
-        <v>182783</v>
-      </c>
-      <c r="B243" s="3" t="n">
-        <v>1879870</v>
-      </c>
-      <c r="C243" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A243" s="5"/>
+      <c r="B243" s="5"/>
+      <c r="C243" s="5"/>
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A244" s="3" t="n">
-        <v>182783</v>
-      </c>
-      <c r="B244" s="3" t="n">
-        <v>1879871</v>
-      </c>
-      <c r="C244" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A244" s="5"/>
+      <c r="B244" s="5"/>
+      <c r="C244" s="5"/>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A245" s="3" t="n">
-        <v>182783</v>
-      </c>
-      <c r="B245" s="3" t="n">
-        <v>1879872</v>
-      </c>
-      <c r="C245" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A245" s="5"/>
+      <c r="B245" s="5"/>
+      <c r="C245" s="5"/>
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A246" s="3" t="n">
-        <v>182783</v>
-      </c>
-      <c r="B246" s="3" t="n">
-        <v>1879873</v>
-      </c>
-      <c r="C246" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A246" s="5"/>
+      <c r="B246" s="5"/>
+      <c r="C246" s="5"/>
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A247" s="3" t="n">
-        <v>182783</v>
-      </c>
-      <c r="B247" s="3" t="n">
-        <v>1879874</v>
-      </c>
-      <c r="C247" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A247" s="5"/>
+      <c r="B247" s="5"/>
+      <c r="C247" s="5"/>
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A248" s="3" t="n">
-        <v>182795</v>
-      </c>
-      <c r="B248" s="3" t="n">
-        <v>1879951</v>
-      </c>
-      <c r="C248" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A248" s="5"/>
+      <c r="B248" s="5"/>
+      <c r="C248" s="5"/>
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A249" s="3" t="n">
-        <v>182795</v>
-      </c>
-      <c r="B249" s="3" t="n">
-        <v>1879952</v>
-      </c>
-      <c r="C249" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A249" s="5"/>
+      <c r="B249" s="5"/>
+      <c r="C249" s="5"/>
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A250" s="3" t="n">
-        <v>182795</v>
-      </c>
-      <c r="B250" s="3" t="n">
-        <v>1879954</v>
-      </c>
-      <c r="C250" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A250" s="5"/>
+      <c r="B250" s="5"/>
+      <c r="C250" s="5"/>
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A251" s="3" t="n">
-        <v>182795</v>
-      </c>
-      <c r="B251" s="3" t="n">
-        <v>1879956</v>
-      </c>
-      <c r="C251" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A251" s="5"/>
+      <c r="B251" s="5"/>
+      <c r="C251" s="5"/>
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A252" s="3" t="n">
-        <v>182795</v>
-      </c>
-      <c r="B252" s="3" t="n">
-        <v>1879958</v>
-      </c>
-      <c r="C252" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A252" s="5"/>
+      <c r="B252" s="5"/>
+      <c r="C252" s="5"/>
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A253" s="3" t="n">
-        <v>182795</v>
-      </c>
-      <c r="B253" s="3" t="n">
-        <v>1879960</v>
-      </c>
-      <c r="C253" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A253" s="5"/>
+      <c r="B253" s="5"/>
+      <c r="C253" s="5"/>
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A254" s="3" t="n">
-        <v>185225</v>
-      </c>
-      <c r="B254" s="3" t="n">
-        <v>1908832</v>
-      </c>
-      <c r="C254" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A254" s="5"/>
+      <c r="B254" s="5"/>
+      <c r="C254" s="5"/>
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A255" s="3" t="n">
-        <v>185225</v>
-      </c>
-      <c r="B255" s="3" t="n">
-        <v>1909385</v>
-      </c>
-      <c r="C255" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A255" s="5"/>
+      <c r="B255" s="5"/>
+      <c r="C255" s="5"/>
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A256" s="3" t="n">
-        <v>185227</v>
-      </c>
-      <c r="B256" s="3" t="n">
-        <v>1908899</v>
-      </c>
-      <c r="C256" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A256" s="5"/>
+      <c r="B256" s="5"/>
+      <c r="C256" s="5"/>
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A257" s="3" t="n">
-        <v>185227</v>
-      </c>
-      <c r="B257" s="3" t="n">
-        <v>1913252</v>
-      </c>
-      <c r="C257" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A257" s="5"/>
+      <c r="B257" s="5"/>
+      <c r="C257" s="5"/>
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A258" s="3" t="n">
-        <v>185231</v>
-      </c>
-      <c r="B258" s="3" t="n">
-        <v>1909046</v>
-      </c>
-      <c r="C258" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A258" s="5"/>
+      <c r="B258" s="5"/>
+      <c r="C258" s="5"/>
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A259" s="3" t="n">
-        <v>185231</v>
-      </c>
-      <c r="B259" s="3" t="n">
-        <v>1909047</v>
-      </c>
-      <c r="C259" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A259" s="5"/>
+      <c r="B259" s="5"/>
+      <c r="C259" s="5"/>
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A260" s="3" t="n">
-        <v>185231</v>
-      </c>
-      <c r="B260" s="3" t="n">
-        <v>1909559</v>
-      </c>
-      <c r="C260" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A260" s="5"/>
+      <c r="B260" s="5"/>
+      <c r="C260" s="5"/>
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A261" s="3" t="n">
-        <v>185231</v>
-      </c>
-      <c r="B261" s="3" t="n">
-        <v>1909560</v>
-      </c>
-      <c r="C261" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A261" s="5"/>
+      <c r="B261" s="5"/>
+      <c r="C261" s="5"/>
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A262" s="3" t="n">
-        <v>185240</v>
-      </c>
-      <c r="B262" s="3" t="n">
-        <v>1909120</v>
-      </c>
-      <c r="C262" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A262" s="5"/>
+      <c r="B262" s="5"/>
+      <c r="C262" s="5"/>
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A263" s="3" t="n">
-        <v>185240</v>
-      </c>
-      <c r="B263" s="3" t="n">
-        <v>1909793</v>
-      </c>
-      <c r="C263" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A263" s="5"/>
+      <c r="B263" s="5"/>
+      <c r="C263" s="5"/>
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A264" s="3" t="n">
-        <v>185244</v>
-      </c>
-      <c r="B264" s="3" t="n">
-        <v>1909174</v>
-      </c>
-      <c r="C264" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A264" s="5"/>
+      <c r="B264" s="5"/>
+      <c r="C264" s="5"/>
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A265" s="3" t="n">
-        <v>185244</v>
-      </c>
-      <c r="B265" s="3" t="n">
-        <v>1909798</v>
-      </c>
-      <c r="C265" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A265" s="5"/>
+      <c r="B265" s="5"/>
+      <c r="C265" s="5"/>
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A266" s="3" t="n">
-        <v>185604</v>
-      </c>
-      <c r="B266" s="3" t="n">
-        <v>1913563</v>
-      </c>
-      <c r="C266" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A266" s="5"/>
+      <c r="B266" s="5"/>
+      <c r="C266" s="5"/>
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A267" s="3" t="n">
-        <v>185610</v>
-      </c>
-      <c r="B267" s="3" t="n">
-        <v>1913559</v>
-      </c>
-      <c r="C267" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A267" s="5"/>
+      <c r="B267" s="5"/>
+      <c r="C267" s="5"/>
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A268" s="3" t="n">
-        <v>185620</v>
-      </c>
-      <c r="B268" s="3" t="n">
-        <v>1913543</v>
-      </c>
-      <c r="C268" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A268" s="5"/>
+      <c r="B268" s="5"/>
+      <c r="C268" s="5"/>
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A269" s="3" t="n">
-        <v>185623</v>
-      </c>
-      <c r="B269" s="3" t="n">
-        <v>1913545</v>
-      </c>
-      <c r="C269" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A269" s="5"/>
+      <c r="B269" s="5"/>
+      <c r="C269" s="5"/>
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A270" s="3" t="n">
-        <v>185623</v>
-      </c>
-      <c r="B270" s="3" t="n">
-        <v>2046420</v>
-      </c>
-      <c r="C270" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A270" s="5"/>
+      <c r="B270" s="5"/>
+      <c r="C270" s="5"/>
     </row>
     <row r="271" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A271" s="3" t="n">
-        <v>185624</v>
-      </c>
-      <c r="B271" s="3" t="n">
-        <v>1913551</v>
-      </c>
-      <c r="C271" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A271" s="5"/>
+      <c r="B271" s="5"/>
+      <c r="C271" s="5"/>
     </row>
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A272" s="3" t="n">
-        <v>185658</v>
-      </c>
-      <c r="B272" s="3" t="n">
-        <v>1913564</v>
-      </c>
-      <c r="C272" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A272" s="5"/>
+      <c r="B272" s="5"/>
+      <c r="C272" s="5"/>
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A273" s="3" t="n">
-        <v>185661</v>
-      </c>
-      <c r="B273" s="3" t="n">
-        <v>1913567</v>
-      </c>
-      <c r="C273" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A273" s="5"/>
+      <c r="B273" s="5"/>
+      <c r="C273" s="5"/>
     </row>
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A274" s="3" t="n">
-        <v>185662</v>
-      </c>
-      <c r="B274" s="3" t="n">
-        <v>1913558</v>
-      </c>
-      <c r="C274" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A274" s="5"/>
+      <c r="B274" s="5"/>
+      <c r="C274" s="5"/>
     </row>
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A275" s="3" t="n">
-        <v>185664</v>
-      </c>
-      <c r="B275" s="3" t="n">
-        <v>1913565</v>
-      </c>
-      <c r="C275" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A275" s="5"/>
+      <c r="B275" s="5"/>
+      <c r="C275" s="5"/>
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A276" s="3" t="n">
-        <v>185665</v>
-      </c>
-      <c r="B276" s="3" t="n">
-        <v>1913566</v>
-      </c>
-      <c r="C276" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A276" s="5"/>
+      <c r="B276" s="5"/>
+      <c r="C276" s="5"/>
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A277" s="3" t="n">
-        <v>185687</v>
-      </c>
-      <c r="B277" s="3" t="n">
-        <v>1913561</v>
-      </c>
-      <c r="C277" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A277" s="5"/>
+      <c r="B277" s="5"/>
+      <c r="C277" s="5"/>
     </row>
     <row r="278" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A278" s="3" t="n">
-        <v>185687</v>
-      </c>
-      <c r="B278" s="3" t="n">
-        <v>1913562</v>
-      </c>
-      <c r="C278" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A278" s="5"/>
+      <c r="B278" s="5"/>
+      <c r="C278" s="5"/>
     </row>
     <row r="279" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A279" s="3" t="n">
-        <v>186008</v>
-      </c>
-      <c r="B279" s="3" t="n">
-        <v>1913470</v>
-      </c>
-      <c r="C279" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A279" s="5"/>
+      <c r="B279" s="5"/>
+      <c r="C279" s="5"/>
     </row>
     <row r="280" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A280" s="3" t="n">
-        <v>186008</v>
-      </c>
-      <c r="B280" s="3" t="n">
-        <v>1913471</v>
-      </c>
-      <c r="C280" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A280" s="5"/>
+      <c r="B280" s="5"/>
+      <c r="C280" s="5"/>
     </row>
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A281" s="3" t="n">
-        <v>189626</v>
-      </c>
-      <c r="B281" s="3" t="n">
-        <v>1965524</v>
-      </c>
-      <c r="C281" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A281" s="5"/>
+      <c r="B281" s="5"/>
+      <c r="C281" s="5"/>
     </row>
     <row r="282" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A282" s="3" t="n">
-        <v>189627</v>
-      </c>
-      <c r="B282" s="3" t="n">
-        <v>1965513</v>
-      </c>
-      <c r="C282" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A282" s="5"/>
+      <c r="B282" s="5"/>
+      <c r="C282" s="5"/>
     </row>
     <row r="283" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A283" s="3" t="n">
-        <v>189628</v>
-      </c>
-      <c r="B283" s="3" t="n">
-        <v>1965509</v>
-      </c>
-      <c r="C283" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A283" s="5"/>
+      <c r="B283" s="5"/>
+      <c r="C283" s="5"/>
     </row>
     <row r="284" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A284" s="3" t="n">
-        <v>189630</v>
-      </c>
-      <c r="B284" s="3" t="n">
-        <v>1965519</v>
-      </c>
-      <c r="C284" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A284" s="5"/>
+      <c r="B284" s="5"/>
+      <c r="C284" s="5"/>
     </row>
     <row r="285" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A285" s="3" t="n">
-        <v>189649</v>
-      </c>
-      <c r="B285" s="3" t="n">
-        <v>1965515</v>
-      </c>
-      <c r="C285" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A285" s="5"/>
+      <c r="B285" s="5"/>
+      <c r="C285" s="5"/>
     </row>
     <row r="286" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A286" s="3" t="n">
-        <v>189650</v>
-      </c>
-      <c r="B286" s="3" t="n">
-        <v>1965517</v>
-      </c>
-      <c r="C286" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="287" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A287" s="3" t="n">
-        <v>189651</v>
-      </c>
-      <c r="B287" s="3" t="n">
-        <v>1965520</v>
-      </c>
-      <c r="C287" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="288" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A288" s="3" t="n">
-        <v>189652</v>
-      </c>
-      <c r="B288" s="3" t="n">
-        <v>1965522</v>
-      </c>
-      <c r="C288" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="289" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A289" s="3" t="n">
-        <v>171781</v>
-      </c>
-      <c r="B289" s="3" t="n">
-        <v>1744301</v>
-      </c>
-      <c r="C289" s="3" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="290" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A290" s="3" t="n">
-        <v>171783</v>
-      </c>
-      <c r="B290" s="3" t="n">
-        <v>1744303</v>
-      </c>
-      <c r="C290" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="291" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A291" s="3" t="n">
-        <v>171783</v>
-      </c>
-      <c r="B291" s="3" t="n">
-        <v>1744305</v>
-      </c>
-      <c r="C291" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="292" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A292" s="3" t="n">
-        <v>171785</v>
-      </c>
-      <c r="B292" s="3" t="n">
-        <v>1968324</v>
-      </c>
-      <c r="C292" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="293" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A293" s="3" t="n">
-        <v>171785</v>
-      </c>
-      <c r="B293" s="3" t="n">
-        <v>1744312</v>
-      </c>
-      <c r="C293" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="294" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A294" s="3" t="n">
-        <v>171775</v>
-      </c>
-      <c r="B294" s="3" t="n">
-        <v>1979762</v>
-      </c>
-      <c r="C294" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="295" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A295" s="3" t="n">
-        <v>171775</v>
-      </c>
-      <c r="B295" s="3" t="n">
-        <v>1744264</v>
-      </c>
-      <c r="C295" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="296" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A296" s="3" t="n">
-        <v>171771</v>
-      </c>
-      <c r="B296" s="3" t="n">
-        <v>1755472</v>
-      </c>
-      <c r="C296" s="3" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="297" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A297" s="3" t="n">
-        <v>171771</v>
-      </c>
-      <c r="B297" s="3" t="n">
-        <v>1913463</v>
-      </c>
-      <c r="C297" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="298" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A298" s="3" t="n">
-        <v>171771</v>
-      </c>
-      <c r="B298" s="3" t="n">
-        <v>1913464</v>
-      </c>
-      <c r="C298" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="299" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A299" s="5"/>
-      <c r="B299" s="5"/>
-      <c r="C299" s="5"/>
-    </row>
-    <row r="300" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A300" s="5"/>
-      <c r="B300" s="5"/>
-      <c r="C300" s="5"/>
-    </row>
-    <row r="301" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A301" s="5"/>
-      <c r="B301" s="5"/>
-      <c r="C301" s="5"/>
-    </row>
-    <row r="302" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A302" s="5"/>
-      <c r="B302" s="5"/>
-      <c r="C302" s="5"/>
-    </row>
-    <row r="303" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A303" s="5"/>
-      <c r="B303" s="5"/>
-      <c r="C303" s="5"/>
-    </row>
-    <row r="304" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A304" s="5"/>
-      <c r="B304" s="5"/>
-      <c r="C304" s="5"/>
-    </row>
-    <row r="305" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A305" s="5"/>
-      <c r="B305" s="5"/>
-      <c r="C305" s="5"/>
-    </row>
-    <row r="306" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A306" s="5"/>
-      <c r="B306" s="5"/>
-      <c r="C306" s="5"/>
-    </row>
-    <row r="307" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A307" s="5"/>
-      <c r="B307" s="5"/>
-      <c r="C307" s="5"/>
-    </row>
-    <row r="308" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A308" s="5"/>
-      <c r="B308" s="5"/>
-      <c r="C308" s="5"/>
-    </row>
-    <row r="309" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A309" s="5"/>
-      <c r="B309" s="5"/>
-      <c r="C309" s="5"/>
-    </row>
-    <row r="310" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A310" s="5"/>
-      <c r="B310" s="5"/>
-      <c r="C310" s="5"/>
-    </row>
-    <row r="311" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A311" s="5"/>
-      <c r="B311" s="5"/>
-      <c r="C311" s="5"/>
-    </row>
-    <row r="312" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A312" s="5"/>
-      <c r="B312" s="5"/>
-      <c r="C312" s="5"/>
-    </row>
-    <row r="313" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A313" s="5"/>
-      <c r="B313" s="5"/>
-      <c r="C313" s="5"/>
-    </row>
-    <row r="314" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A314" s="5"/>
-      <c r="B314" s="5"/>
-      <c r="C314" s="5"/>
-    </row>
-    <row r="315" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A315" s="5"/>
-      <c r="B315" s="5"/>
-      <c r="C315" s="5"/>
-    </row>
-    <row r="316" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A316" s="5"/>
-      <c r="B316" s="5"/>
-      <c r="C316" s="5"/>
-    </row>
-    <row r="317" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A317" s="5"/>
-      <c r="B317" s="5"/>
-      <c r="C317" s="5"/>
-    </row>
-    <row r="318" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A318" s="5"/>
-      <c r="B318" s="5"/>
-      <c r="C318" s="5"/>
-    </row>
-    <row r="319" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A319" s="5"/>
-      <c r="B319" s="5"/>
-      <c r="C319" s="5"/>
-    </row>
-    <row r="320" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A320" s="5"/>
-      <c r="B320" s="5"/>
-      <c r="C320" s="5"/>
-    </row>
-    <row r="321" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A321" s="5"/>
-      <c r="B321" s="5"/>
-      <c r="C321" s="5"/>
-    </row>
-    <row r="322" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A322" s="5"/>
-      <c r="B322" s="5"/>
-      <c r="C322" s="5"/>
-    </row>
-    <row r="323" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A323" s="5"/>
-      <c r="B323" s="5"/>
-      <c r="C323" s="5"/>
-    </row>
-    <row r="324" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A324" s="5"/>
-      <c r="B324" s="5"/>
-      <c r="C324" s="5"/>
-    </row>
-    <row r="325" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A325" s="5"/>
-      <c r="B325" s="5"/>
-      <c r="C325" s="5"/>
-    </row>
-    <row r="326" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A326" s="5"/>
-      <c r="B326" s="5"/>
-      <c r="C326" s="5"/>
-    </row>
-    <row r="327" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A327" s="5"/>
-      <c r="B327" s="5"/>
-      <c r="C327" s="5"/>
-    </row>
-    <row r="328" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A328" s="5"/>
-      <c r="B328" s="5"/>
-      <c r="C328" s="5"/>
-    </row>
-    <row r="329" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A329" s="5"/>
-      <c r="B329" s="5"/>
-      <c r="C329" s="5"/>
-    </row>
-    <row r="330" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A330" s="5"/>
-      <c r="B330" s="5"/>
-      <c r="C330" s="5"/>
-    </row>
-    <row r="331" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A331" s="5"/>
-      <c r="B331" s="5"/>
-      <c r="C331" s="5"/>
-    </row>
-    <row r="332" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A332" s="5"/>
-      <c r="B332" s="5"/>
-      <c r="C332" s="5"/>
-    </row>
-    <row r="333" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A333" s="5"/>
-      <c r="B333" s="5"/>
-      <c r="C333" s="5"/>
-    </row>
-    <row r="334" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A334" s="5"/>
-      <c r="B334" s="5"/>
-      <c r="C334" s="5"/>
-    </row>
-    <row r="335" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A335" s="5"/>
-      <c r="B335" s="5"/>
-      <c r="C335" s="5"/>
-    </row>
-    <row r="336" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A336" s="5"/>
-      <c r="B336" s="5"/>
-      <c r="C336" s="5"/>
-    </row>
-    <row r="337" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A337" s="5"/>
-      <c r="B337" s="5"/>
-      <c r="C337" s="5"/>
-    </row>
-    <row r="338" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A338" s="5"/>
-      <c r="B338" s="5"/>
-      <c r="C338" s="5"/>
-    </row>
-    <row r="339" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A339" s="5"/>
-      <c r="B339" s="5"/>
-      <c r="C339" s="5"/>
-    </row>
-    <row r="340" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A340" s="5"/>
-      <c r="B340" s="5"/>
-      <c r="C340" s="5"/>
-    </row>
-    <row r="341" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A341" s="5"/>
-      <c r="B341" s="5"/>
-      <c r="C341" s="5"/>
-    </row>
-    <row r="342" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A342" s="5"/>
-      <c r="B342" s="5"/>
-      <c r="C342" s="5"/>
-    </row>
-    <row r="343" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A343" s="5"/>
-      <c r="B343" s="5"/>
-      <c r="C343" s="5"/>
-    </row>
-    <row r="344" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A344" s="5"/>
-      <c r="B344" s="5"/>
-      <c r="C344" s="5"/>
-    </row>
-    <row r="345" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A345" s="5"/>
-      <c r="B345" s="5"/>
-      <c r="C345" s="5"/>
-    </row>
-    <row r="346" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A346" s="5"/>
-      <c r="B346" s="5"/>
-      <c r="C346" s="5"/>
-    </row>
-    <row r="347" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A347" s="5"/>
-      <c r="B347" s="5"/>
-      <c r="C347" s="5"/>
-    </row>
-    <row r="348" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A348" s="5"/>
-      <c r="B348" s="5"/>
-      <c r="C348" s="5"/>
-    </row>
-    <row r="349" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A349" s="5"/>
-      <c r="B349" s="5"/>
-      <c r="C349" s="5"/>
-    </row>
-    <row r="350" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A350" s="5"/>
-      <c r="B350" s="5"/>
-      <c r="C350" s="5"/>
-    </row>
-    <row r="351" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A351" s="5"/>
-      <c r="B351" s="5"/>
-      <c r="C351" s="5"/>
-    </row>
-    <row r="352" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A352" s="5"/>
-      <c r="B352" s="5"/>
-      <c r="C352" s="5"/>
-    </row>
-    <row r="353" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A353" s="5"/>
-      <c r="B353" s="5"/>
-      <c r="C353" s="5"/>
-    </row>
-    <row r="354" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A354" s="5"/>
-      <c r="B354" s="5"/>
-      <c r="C354" s="5"/>
-    </row>
-    <row r="355" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A355" s="5"/>
-      <c r="B355" s="5"/>
-      <c r="C355" s="5"/>
-    </row>
-    <row r="356" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A356" s="5"/>
-      <c r="B356" s="5"/>
-      <c r="C356" s="5"/>
-    </row>
-    <row r="357" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A357" s="5"/>
-      <c r="B357" s="5"/>
-      <c r="C357" s="5"/>
-    </row>
-    <row r="358" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A358" s="5"/>
-      <c r="B358" s="5"/>
-      <c r="C358" s="5"/>
-    </row>
-    <row r="359" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A359" s="5"/>
-      <c r="B359" s="5"/>
-      <c r="C359" s="5"/>
-    </row>
-    <row r="360" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A360" s="5"/>
-      <c r="B360" s="5"/>
-      <c r="C360" s="5"/>
-    </row>
-    <row r="361" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A361" s="5"/>
-      <c r="B361" s="5"/>
-      <c r="C361" s="5"/>
-    </row>
-    <row r="362" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A362" s="5"/>
-      <c r="B362" s="5"/>
-      <c r="C362" s="5"/>
-    </row>
-    <row r="363" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A363" s="5"/>
-      <c r="B363" s="5"/>
-      <c r="C363" s="5"/>
-    </row>
-    <row r="364" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A364" s="5"/>
-      <c r="B364" s="5"/>
-      <c r="C364" s="5"/>
-    </row>
-    <row r="365" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A365" s="5"/>
-      <c r="B365" s="5"/>
-      <c r="C365" s="5"/>
-    </row>
-    <row r="366" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A366" s="5"/>
-      <c r="B366" s="5"/>
-      <c r="C366" s="5"/>
-    </row>
-    <row r="367" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A367" s="5"/>
-      <c r="B367" s="5"/>
-      <c r="C367" s="5"/>
-    </row>
-    <row r="368" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A368" s="5"/>
-      <c r="B368" s="5"/>
-      <c r="C368" s="5"/>
-    </row>
-    <row r="369" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A369" s="5"/>
-      <c r="B369" s="5"/>
-      <c r="C369" s="5"/>
-    </row>
-    <row r="370" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A370" s="5"/>
-      <c r="B370" s="5"/>
-      <c r="C370" s="5"/>
-    </row>
-    <row r="371" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A371" s="5"/>
-      <c r="B371" s="5"/>
-      <c r="C371" s="5"/>
-    </row>
-    <row r="372" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A372" s="5"/>
-      <c r="B372" s="5"/>
-      <c r="C372" s="5"/>
-    </row>
-    <row r="373" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A373" s="5"/>
-      <c r="B373" s="5"/>
-      <c r="C373" s="5"/>
-    </row>
-    <row r="374" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A374" s="5"/>
-      <c r="B374" s="5"/>
-      <c r="C374" s="5"/>
-    </row>
-    <row r="375" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A375" s="5"/>
-      <c r="B375" s="5"/>
-      <c r="C375" s="5"/>
-    </row>
-    <row r="376" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A376" s="5"/>
-      <c r="B376" s="5"/>
-      <c r="C376" s="5"/>
-    </row>
-    <row r="377" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A377" s="5"/>
-      <c r="B377" s="5"/>
-      <c r="C377" s="5"/>
-    </row>
-    <row r="378" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A378" s="5"/>
-      <c r="B378" s="5"/>
-      <c r="C378" s="5"/>
-    </row>
-    <row r="379" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A379" s="5"/>
-      <c r="B379" s="5"/>
-      <c r="C379" s="5"/>
-    </row>
-    <row r="380" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A380" s="5"/>
-      <c r="B380" s="5"/>
-      <c r="C380" s="5"/>
-    </row>
-    <row r="381" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A381" s="5"/>
-      <c r="B381" s="5"/>
-      <c r="C381" s="5"/>
-    </row>
-    <row r="382" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A382" s="5"/>
-      <c r="B382" s="5"/>
-      <c r="C382" s="5"/>
-    </row>
-    <row r="383" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A383" s="5"/>
-      <c r="B383" s="5"/>
-      <c r="C383" s="5"/>
-    </row>
-    <row r="384" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A384" s="5"/>
-      <c r="B384" s="5"/>
-      <c r="C384" s="5"/>
-    </row>
-    <row r="385" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A385" s="5"/>
-      <c r="B385" s="5"/>
-      <c r="C385" s="5"/>
-    </row>
-    <row r="386" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A386" s="5"/>
-      <c r="B386" s="5"/>
-      <c r="C386" s="5"/>
-    </row>
-    <row r="387" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A387" s="5"/>
-      <c r="B387" s="5"/>
-      <c r="C387" s="5"/>
-    </row>
-    <row r="388" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A388" s="5"/>
-      <c r="B388" s="5"/>
-      <c r="C388" s="5"/>
-    </row>
-    <row r="389" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A389" s="5"/>
-      <c r="B389" s="5"/>
-      <c r="C389" s="5"/>
-    </row>
-    <row r="390" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A390" s="5"/>
-      <c r="B390" s="5"/>
-      <c r="C390" s="5"/>
-    </row>
-    <row r="391" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A391" s="5"/>
-      <c r="B391" s="5"/>
-      <c r="C391" s="5"/>
-    </row>
-    <row r="392" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A392" s="5"/>
-      <c r="B392" s="5"/>
-      <c r="C392" s="5"/>
-    </row>
-    <row r="393" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A393" s="5"/>
-      <c r="B393" s="5"/>
-      <c r="C393" s="5"/>
-    </row>
-    <row r="394" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A394" s="5"/>
-      <c r="B394" s="5"/>
-      <c r="C394" s="5"/>
-    </row>
-    <row r="395" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A395" s="5"/>
-      <c r="B395" s="5"/>
-      <c r="C395" s="5"/>
-    </row>
-    <row r="396" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A396" s="5"/>
-      <c r="B396" s="5"/>
-      <c r="C396" s="5"/>
-    </row>
-    <row r="397" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A397" s="5"/>
-      <c r="B397" s="5"/>
-      <c r="C397" s="5"/>
-    </row>
-    <row r="398" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A398" s="5"/>
-      <c r="B398" s="5"/>
-      <c r="C398" s="5"/>
-    </row>
-    <row r="399" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A399" s="5"/>
-      <c r="B399" s="5"/>
-      <c r="C399" s="5"/>
-    </row>
-    <row r="400" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A400" s="5"/>
-      <c r="B400" s="5"/>
-      <c r="C400" s="5"/>
-    </row>
-    <row r="401" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A401" s="5"/>
-      <c r="B401" s="5"/>
-      <c r="C401" s="5"/>
-    </row>
-    <row r="402" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A402" s="5"/>
-      <c r="B402" s="5"/>
-      <c r="C402" s="5"/>
-    </row>
-    <row r="403" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A403" s="5"/>
-      <c r="B403" s="5"/>
-      <c r="C403" s="5"/>
-    </row>
-    <row r="404" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A404" s="5"/>
-      <c r="B404" s="5"/>
-      <c r="C404" s="5"/>
-    </row>
-    <row r="405" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A405" s="5"/>
-      <c r="B405" s="5"/>
-      <c r="C405" s="5"/>
-    </row>
-    <row r="406" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A406" s="5"/>
-      <c r="B406" s="5"/>
-      <c r="C406" s="5"/>
-    </row>
-    <row r="407" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A407" s="5"/>
-      <c r="B407" s="5"/>
-      <c r="C407" s="5"/>
-    </row>
-    <row r="408" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A408" s="5"/>
-      <c r="B408" s="5"/>
-      <c r="C408" s="5"/>
-    </row>
-    <row r="409" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A409" s="5"/>
-      <c r="B409" s="5"/>
-      <c r="C409" s="5"/>
-    </row>
-    <row r="410" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A410" s="5"/>
-      <c r="B410" s="5"/>
-      <c r="C410" s="5"/>
-    </row>
-    <row r="411" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A411" s="5"/>
-      <c r="B411" s="5"/>
-      <c r="C411" s="5"/>
-    </row>
-    <row r="412" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A412" s="5"/>
-      <c r="B412" s="5"/>
-      <c r="C412" s="5"/>
-    </row>
-    <row r="413" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A413" s="5"/>
-      <c r="B413" s="5"/>
-      <c r="C413" s="5"/>
-    </row>
-    <row r="414" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A414" s="5"/>
-      <c r="B414" s="5"/>
-      <c r="C414" s="5"/>
-    </row>
-    <row r="415" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A415" s="5"/>
-      <c r="B415" s="5"/>
-      <c r="C415" s="5"/>
-    </row>
-    <row r="416" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A416" s="5"/>
-      <c r="B416" s="5"/>
-      <c r="C416" s="5"/>
-    </row>
-    <row r="417" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A417" s="5"/>
-      <c r="B417" s="5"/>
-      <c r="C417" s="5"/>
-    </row>
-    <row r="418" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A418" s="5"/>
-      <c r="B418" s="5"/>
-      <c r="C418" s="5"/>
-    </row>
-    <row r="419" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A419" s="5"/>
-      <c r="B419" s="5"/>
-      <c r="C419" s="5"/>
-    </row>
-    <row r="420" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A420" s="5"/>
-      <c r="B420" s="5"/>
-      <c r="C420" s="5"/>
-    </row>
-    <row r="421" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A421" s="5"/>
-      <c r="B421" s="5"/>
-      <c r="C421" s="5"/>
-    </row>
-    <row r="422" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A422" s="5"/>
-      <c r="B422" s="5"/>
-      <c r="C422" s="5"/>
-    </row>
-    <row r="423" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A423" s="5"/>
-      <c r="B423" s="5"/>
-      <c r="C423" s="5"/>
-    </row>
-    <row r="424" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A424" s="5"/>
-      <c r="B424" s="5"/>
-      <c r="C424" s="5"/>
-    </row>
-    <row r="425" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A425" s="5"/>
-      <c r="B425" s="5"/>
-      <c r="C425" s="5"/>
-    </row>
-    <row r="426" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A426" s="5"/>
-      <c r="B426" s="5"/>
-      <c r="C426" s="5"/>
-    </row>
-    <row r="427" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A427" s="5"/>
-      <c r="B427" s="5"/>
-      <c r="C427" s="5"/>
-    </row>
-    <row r="428" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A428" s="5"/>
-      <c r="B428" s="5"/>
-      <c r="C428" s="5"/>
-    </row>
-    <row r="429" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A429" s="5"/>
-      <c r="B429" s="5"/>
-      <c r="C429" s="5"/>
-    </row>
-    <row r="430" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A430" s="5"/>
-      <c r="B430" s="5"/>
-      <c r="C430" s="5"/>
-    </row>
-    <row r="431" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A431" s="5"/>
-      <c r="B431" s="5"/>
-      <c r="C431" s="5"/>
-    </row>
-    <row r="432" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A432" s="5"/>
-      <c r="B432" s="5"/>
-      <c r="C432" s="5"/>
-    </row>
-    <row r="433" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A433" s="5"/>
-      <c r="B433" s="5"/>
-      <c r="C433" s="5"/>
-    </row>
-    <row r="434" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A434" s="5"/>
-      <c r="B434" s="5"/>
-      <c r="C434" s="5"/>
-    </row>
-    <row r="435" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A435" s="5"/>
-      <c r="B435" s="5"/>
-      <c r="C435" s="5"/>
-    </row>
-    <row r="436" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A436" s="5"/>
-      <c r="B436" s="5"/>
-      <c r="C436" s="5"/>
-    </row>
-    <row r="437" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A437" s="5"/>
-      <c r="B437" s="5"/>
-      <c r="C437" s="5"/>
-    </row>
-    <row r="438" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A438" s="5"/>
-      <c r="B438" s="5"/>
-      <c r="C438" s="5"/>
-    </row>
-    <row r="439" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A439" s="5"/>
-      <c r="B439" s="5"/>
-      <c r="C439" s="5"/>
-    </row>
-    <row r="440" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A440" s="5"/>
-      <c r="B440" s="5"/>
-      <c r="C440" s="5"/>
-    </row>
-    <row r="441" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A441" s="5"/>
-      <c r="B441" s="5"/>
-      <c r="C441" s="5"/>
-    </row>
-    <row r="442" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A442" s="5"/>
-      <c r="B442" s="5"/>
-      <c r="C442" s="5"/>
-    </row>
-    <row r="443" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A443" s="5"/>
-      <c r="B443" s="5"/>
-      <c r="C443" s="5"/>
-    </row>
-    <row r="444" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A444" s="5"/>
-      <c r="B444" s="5"/>
-      <c r="C444" s="5"/>
-    </row>
-    <row r="445" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A445" s="5"/>
-      <c r="B445" s="5"/>
-      <c r="C445" s="5"/>
-    </row>
-    <row r="446" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A446" s="5"/>
-      <c r="B446" s="5"/>
-      <c r="C446" s="5"/>
-    </row>
-    <row r="447" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A447" s="5"/>
-      <c r="B447" s="5"/>
-      <c r="C447" s="5"/>
-    </row>
-    <row r="448" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A448" s="5"/>
-      <c r="B448" s="5"/>
-      <c r="C448" s="5"/>
-    </row>
-    <row r="449" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A449" s="5"/>
-      <c r="B449" s="5"/>
-      <c r="C449" s="5"/>
-    </row>
-    <row r="450" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A450" s="5"/>
-      <c r="B450" s="5"/>
-      <c r="C450" s="5"/>
-    </row>
-    <row r="451" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A451" s="5"/>
-      <c r="B451" s="5"/>
-      <c r="C451" s="5"/>
-    </row>
-    <row r="452" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A452" s="5"/>
-      <c r="B452" s="5"/>
-      <c r="C452" s="5"/>
-    </row>
-    <row r="453" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A453" s="5"/>
-      <c r="B453" s="5"/>
-      <c r="C453" s="5"/>
-    </row>
-    <row r="454" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A454" s="5"/>
-      <c r="B454" s="5"/>
-      <c r="C454" s="5"/>
-    </row>
-    <row r="455" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A455" s="5"/>
-      <c r="B455" s="5"/>
-      <c r="C455" s="5"/>
-    </row>
-    <row r="456" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A456" s="5"/>
-      <c r="B456" s="5"/>
-      <c r="C456" s="5"/>
-    </row>
-    <row r="457" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A457" s="5"/>
-      <c r="B457" s="5"/>
-      <c r="C457" s="5"/>
-    </row>
-    <row r="458" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A458" s="5"/>
-      <c r="B458" s="5"/>
-      <c r="C458" s="5"/>
-    </row>
-    <row r="459" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A459" s="5"/>
-      <c r="B459" s="5"/>
-      <c r="C459" s="5"/>
-    </row>
-    <row r="460" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A460" s="5"/>
-      <c r="B460" s="5"/>
-      <c r="C460" s="5"/>
-    </row>
-    <row r="461" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A461" s="5"/>
-      <c r="B461" s="5"/>
-      <c r="C461" s="5"/>
-    </row>
-    <row r="462" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A462" s="5"/>
-      <c r="B462" s="5"/>
-      <c r="C462" s="5"/>
-    </row>
-    <row r="463" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A463" s="5"/>
-      <c r="B463" s="5"/>
-      <c r="C463" s="5"/>
-    </row>
-    <row r="464" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A464" s="5"/>
-      <c r="B464" s="5"/>
-      <c r="C464" s="5"/>
-    </row>
-    <row r="465" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A465" s="5"/>
-      <c r="B465" s="5"/>
-      <c r="C465" s="5"/>
-    </row>
-    <row r="466" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A466" s="5"/>
-      <c r="B466" s="5"/>
-      <c r="C466" s="5"/>
-    </row>
-    <row r="467" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A467" s="5"/>
-      <c r="B467" s="5"/>
-      <c r="C467" s="5"/>
-    </row>
-    <row r="468" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A468" s="5"/>
-      <c r="B468" s="5"/>
-      <c r="C468" s="5"/>
-    </row>
-    <row r="469" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A469" s="5"/>
-      <c r="B469" s="5"/>
-      <c r="C469" s="5"/>
-    </row>
-    <row r="470" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A470" s="5"/>
-      <c r="B470" s="5"/>
-      <c r="C470" s="5"/>
-    </row>
-    <row r="471" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A471" s="5"/>
-      <c r="B471" s="5"/>
-      <c r="C471" s="5"/>
-    </row>
-    <row r="472" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A472" s="5"/>
-      <c r="B472" s="5"/>
-      <c r="C472" s="5"/>
-    </row>
-    <row r="473" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A473" s="5"/>
-      <c r="B473" s="5"/>
-      <c r="C473" s="5"/>
-    </row>
-    <row r="474" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A474" s="5"/>
-      <c r="B474" s="5"/>
-      <c r="C474" s="5"/>
-    </row>
-    <row r="475" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A475" s="5"/>
-      <c r="B475" s="5"/>
-      <c r="C475" s="5"/>
-    </row>
-    <row r="476" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A476" s="5"/>
-      <c r="B476" s="5"/>
-      <c r="C476" s="5"/>
-    </row>
-    <row r="477" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A477" s="5"/>
-      <c r="B477" s="5"/>
-      <c r="C477" s="5"/>
-    </row>
-    <row r="478" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A478" s="5"/>
-      <c r="B478" s="5"/>
-      <c r="C478" s="5"/>
-    </row>
-    <row r="479" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A479" s="5"/>
-      <c r="B479" s="5"/>
-      <c r="C479" s="5"/>
-    </row>
-    <row r="480" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A480" s="5"/>
-      <c r="B480" s="5"/>
-      <c r="C480" s="5"/>
-    </row>
-    <row r="481" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A481" s="5"/>
-      <c r="B481" s="5"/>
-      <c r="C481" s="5"/>
-    </row>
-    <row r="482" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A482" s="5"/>
-      <c r="B482" s="5"/>
-      <c r="C482" s="5"/>
-    </row>
-    <row r="483" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A483" s="5"/>
-      <c r="B483" s="5"/>
-      <c r="C483" s="5"/>
-    </row>
-    <row r="484" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A484" s="5"/>
-      <c r="B484" s="5"/>
-      <c r="C484" s="5"/>
-    </row>
-    <row r="485" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A485" s="5"/>
-      <c r="B485" s="5"/>
-      <c r="C485" s="5"/>
-    </row>
-    <row r="486" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A486" s="5"/>
-      <c r="B486" s="5"/>
-      <c r="C486" s="5"/>
-    </row>
-    <row r="487" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A487" s="5"/>
-      <c r="B487" s="5"/>
-      <c r="C487" s="5"/>
-    </row>
-    <row r="488" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A488" s="5"/>
-      <c r="B488" s="5"/>
-      <c r="C488" s="5"/>
-    </row>
-    <row r="489" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A489" s="5"/>
-      <c r="B489" s="5"/>
-      <c r="C489" s="5"/>
-    </row>
-    <row r="490" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A490" s="5"/>
-      <c r="B490" s="5"/>
-      <c r="C490" s="5"/>
-    </row>
-    <row r="491" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A491" s="5"/>
-      <c r="B491" s="5"/>
-      <c r="C491" s="5"/>
-    </row>
-    <row r="492" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A492" s="5"/>
-      <c r="B492" s="5"/>
-      <c r="C492" s="5"/>
-    </row>
-    <row r="493" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A493" s="5"/>
-      <c r="B493" s="5"/>
-      <c r="C493" s="5"/>
-    </row>
-    <row r="494" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A494" s="5"/>
-      <c r="B494" s="5"/>
-      <c r="C494" s="5"/>
-    </row>
-    <row r="495" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A495" s="5"/>
-      <c r="B495" s="5"/>
-      <c r="C495" s="5"/>
-    </row>
-    <row r="496" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A496" s="5"/>
-      <c r="B496" s="5"/>
-      <c r="C496" s="5"/>
-    </row>
-    <row r="497" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A497" s="5"/>
-      <c r="B497" s="5"/>
-      <c r="C497" s="5"/>
-    </row>
-    <row r="498" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A498" s="5"/>
-      <c r="B498" s="5"/>
-      <c r="C498" s="5"/>
-    </row>
-    <row r="499" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A499" s="5"/>
-      <c r="B499" s="5"/>
-      <c r="C499" s="5"/>
-    </row>
-    <row r="500" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A500" s="5"/>
-      <c r="B500" s="5"/>
-      <c r="C500" s="5"/>
-    </row>
-    <row r="501" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A501" s="5"/>
-      <c r="B501" s="5"/>
-      <c r="C501" s="5"/>
-    </row>
-    <row r="502" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A502" s="5"/>
-      <c r="B502" s="5"/>
-      <c r="C502" s="5"/>
-    </row>
-    <row r="503" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A503" s="5"/>
-      <c r="B503" s="5"/>
-      <c r="C503" s="5"/>
-    </row>
-    <row r="504" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A504" s="5"/>
-      <c r="B504" s="5"/>
-      <c r="C504" s="5"/>
-    </row>
-    <row r="505" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A505" s="5"/>
-      <c r="B505" s="5"/>
-      <c r="C505" s="5"/>
-    </row>
-    <row r="506" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A506" s="5"/>
-      <c r="B506" s="5"/>
-      <c r="C506" s="5"/>
-    </row>
-    <row r="507" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A507" s="5"/>
-      <c r="B507" s="5"/>
-      <c r="C507" s="5"/>
-    </row>
-    <row r="508" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A508" s="5"/>
-      <c r="B508" s="5"/>
-      <c r="C508" s="5"/>
-    </row>
-    <row r="509" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A509" s="5"/>
-      <c r="B509" s="5"/>
-      <c r="C509" s="5"/>
-    </row>
-    <row r="510" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A510" s="5"/>
-      <c r="B510" s="5"/>
-      <c r="C510" s="5"/>
-    </row>
-    <row r="511" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A511" s="5"/>
-      <c r="B511" s="5"/>
-      <c r="C511" s="5"/>
-    </row>
-    <row r="512" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A512" s="5"/>
-      <c r="B512" s="5"/>
-      <c r="C512" s="5"/>
-    </row>
-    <row r="513" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A513" s="5"/>
-      <c r="B513" s="5"/>
-      <c r="C513" s="5"/>
-    </row>
-    <row r="514" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A514" s="5"/>
-      <c r="B514" s="5"/>
-      <c r="C514" s="5"/>
-    </row>
-    <row r="515" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A515" s="5"/>
-      <c r="B515" s="5"/>
-      <c r="C515" s="5"/>
-    </row>
-    <row r="516" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A516" s="5"/>
-      <c r="B516" s="5"/>
-      <c r="C516" s="5"/>
-    </row>
-    <row r="517" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A517" s="5"/>
-      <c r="B517" s="5"/>
-      <c r="C517" s="5"/>
-    </row>
-    <row r="518" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A518" s="5"/>
-      <c r="B518" s="5"/>
-      <c r="C518" s="5"/>
-    </row>
-    <row r="519" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A519" s="5"/>
-      <c r="B519" s="5"/>
-      <c r="C519" s="5"/>
-    </row>
-    <row r="520" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A520" s="5"/>
-      <c r="B520" s="5"/>
-      <c r="C520" s="5"/>
-    </row>
-    <row r="521" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A521" s="5"/>
-      <c r="B521" s="5"/>
-      <c r="C521" s="5"/>
-    </row>
-    <row r="522" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A522" s="5"/>
-      <c r="B522" s="5"/>
-      <c r="C522" s="5"/>
-    </row>
-    <row r="523" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A523" s="5"/>
-      <c r="B523" s="5"/>
-      <c r="C523" s="5"/>
-    </row>
-    <row r="524" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A524" s="5"/>
-      <c r="B524" s="5"/>
-      <c r="C524" s="5"/>
-    </row>
-    <row r="525" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A525" s="5"/>
-      <c r="B525" s="5"/>
-      <c r="C525" s="5"/>
-    </row>
-    <row r="526" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A526" s="5"/>
-      <c r="B526" s="5"/>
-      <c r="C526" s="5"/>
-    </row>
-    <row r="527" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A527" s="5"/>
-      <c r="B527" s="5"/>
-      <c r="C527" s="5"/>
-    </row>
-    <row r="528" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A528" s="5"/>
-      <c r="B528" s="5"/>
-      <c r="C528" s="5"/>
-    </row>
-    <row r="529" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A529" s="5"/>
-      <c r="B529" s="5"/>
-      <c r="C529" s="5"/>
-    </row>
-    <row r="530" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A530" s="5"/>
-      <c r="B530" s="5"/>
-      <c r="C530" s="5"/>
-    </row>
-    <row r="531" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A531" s="5"/>
-      <c r="B531" s="5"/>
-      <c r="C531" s="5"/>
-    </row>
-    <row r="532" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A532" s="5"/>
-      <c r="B532" s="5"/>
-      <c r="C532" s="5"/>
-    </row>
-    <row r="533" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A533" s="5"/>
-      <c r="B533" s="5"/>
-      <c r="C533" s="5"/>
-    </row>
-    <row r="534" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A534" s="5"/>
-      <c r="B534" s="5"/>
-      <c r="C534" s="5"/>
-    </row>
-    <row r="535" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A535" s="5"/>
-      <c r="B535" s="5"/>
-      <c r="C535" s="5"/>
-    </row>
-    <row r="536" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A536" s="5"/>
-      <c r="B536" s="5"/>
-      <c r="C536" s="5"/>
-    </row>
-    <row r="537" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A537" s="5"/>
-      <c r="B537" s="5"/>
-      <c r="C537" s="5"/>
-    </row>
-    <row r="538" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A538" s="5"/>
-      <c r="B538" s="5"/>
-      <c r="C538" s="5"/>
-    </row>
-    <row r="539" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A539" s="5"/>
-      <c r="B539" s="5"/>
-      <c r="C539" s="5"/>
-    </row>
-    <row r="540" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A540" s="5"/>
-      <c r="B540" s="5"/>
-      <c r="C540" s="5"/>
-    </row>
-    <row r="541" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A541" s="5"/>
-      <c r="B541" s="5"/>
-      <c r="C541" s="5"/>
-    </row>
-    <row r="542" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A542" s="5"/>
-      <c r="B542" s="5"/>
-      <c r="C542" s="5"/>
-    </row>
-    <row r="543" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A543" s="5"/>
-      <c r="B543" s="5"/>
-      <c r="C543" s="5"/>
-    </row>
-    <row r="544" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A544" s="5"/>
-      <c r="B544" s="5"/>
-      <c r="C544" s="5"/>
-    </row>
-    <row r="545" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A545" s="5"/>
-      <c r="B545" s="5"/>
-      <c r="C545" s="5"/>
-    </row>
-    <row r="546" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A546" s="5"/>
-      <c r="B546" s="5"/>
-      <c r="C546" s="5"/>
-    </row>
-    <row r="547" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A547" s="5"/>
-      <c r="B547" s="5"/>
-      <c r="C547" s="5"/>
-    </row>
-    <row r="548" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A548" s="5"/>
-      <c r="B548" s="5"/>
-      <c r="C548" s="5"/>
-    </row>
-    <row r="549" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A549" s="5"/>
-      <c r="B549" s="5"/>
-      <c r="C549" s="5"/>
-    </row>
-    <row r="550" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A550" s="5"/>
-      <c r="B550" s="5"/>
-      <c r="C550" s="5"/>
-    </row>
-    <row r="551" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A551" s="5"/>
-      <c r="B551" s="5"/>
-      <c r="C551" s="5"/>
-    </row>
-    <row r="552" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A552" s="5"/>
-      <c r="B552" s="5"/>
-      <c r="C552" s="5"/>
-    </row>
-    <row r="553" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A553" s="5"/>
-      <c r="B553" s="5"/>
-      <c r="C553" s="5"/>
-    </row>
-    <row r="554" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A554" s="5"/>
-      <c r="B554" s="5"/>
-      <c r="C554" s="5"/>
-    </row>
-    <row r="555" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A555" s="5"/>
-      <c r="B555" s="5"/>
-      <c r="C555" s="5"/>
-    </row>
-    <row r="556" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A556" s="5"/>
-      <c r="B556" s="5"/>
-      <c r="C556" s="5"/>
-    </row>
-    <row r="557" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A557" s="5"/>
-      <c r="B557" s="5"/>
-      <c r="C557" s="5"/>
-    </row>
-    <row r="558" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A558" s="5"/>
-      <c r="B558" s="5"/>
-      <c r="C558" s="5"/>
-    </row>
-    <row r="559" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A559" s="5"/>
-      <c r="B559" s="5"/>
-      <c r="C559" s="5"/>
-    </row>
-    <row r="560" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A560" s="5"/>
-      <c r="B560" s="5"/>
-      <c r="C560" s="5"/>
-    </row>
-    <row r="561" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A561" s="5"/>
-      <c r="B561" s="5"/>
-      <c r="C561" s="5"/>
-    </row>
-    <row r="562" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A562" s="5"/>
-      <c r="B562" s="5"/>
-      <c r="C562" s="5"/>
-    </row>
-    <row r="563" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A563" s="5"/>
-      <c r="B563" s="5"/>
-      <c r="C563" s="5"/>
-    </row>
-    <row r="564" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A564" s="5"/>
-      <c r="B564" s="5"/>
-      <c r="C564" s="5"/>
-    </row>
-    <row r="565" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A565" s="5"/>
-      <c r="B565" s="5"/>
-      <c r="C565" s="5"/>
-    </row>
-    <row r="566" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A566" s="5"/>
-      <c r="B566" s="5"/>
-      <c r="C566" s="5"/>
-    </row>
-    <row r="567" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A567" s="5"/>
-      <c r="B567" s="5"/>
-      <c r="C567" s="5"/>
-    </row>
-    <row r="568" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A568" s="5"/>
-      <c r="B568" s="5"/>
-      <c r="C568" s="5"/>
-    </row>
-    <row r="569" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A569" s="5"/>
-      <c r="B569" s="5"/>
-      <c r="C569" s="5"/>
-    </row>
-    <row r="570" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A570" s="5"/>
-      <c r="B570" s="5"/>
-      <c r="C570" s="5"/>
-    </row>
-    <row r="571" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A571" s="5"/>
-      <c r="B571" s="5"/>
-      <c r="C571" s="5"/>
-    </row>
-    <row r="572" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A572" s="5"/>
-      <c r="B572" s="5"/>
-      <c r="C572" s="5"/>
-    </row>
-    <row r="573" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A573" s="5"/>
-      <c r="B573" s="5"/>
-      <c r="C573" s="5"/>
-    </row>
-    <row r="574" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A574" s="5"/>
-      <c r="B574" s="5"/>
-      <c r="C574" s="5"/>
-    </row>
-    <row r="575" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A575" s="5"/>
-      <c r="B575" s="5"/>
-      <c r="C575" s="5"/>
-    </row>
-    <row r="576" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A576" s="5"/>
-      <c r="B576" s="5"/>
-      <c r="C576" s="5"/>
-    </row>
-    <row r="577" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A577" s="5"/>
-      <c r="B577" s="5"/>
-      <c r="C577" s="5"/>
-    </row>
-    <row r="578" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A578" s="5"/>
-      <c r="B578" s="5"/>
-      <c r="C578" s="5"/>
-    </row>
-    <row r="579" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A579" s="5"/>
-      <c r="B579" s="5"/>
-      <c r="C579" s="5"/>
-    </row>
-    <row r="580" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A580" s="5"/>
-      <c r="B580" s="5"/>
-      <c r="C580" s="5"/>
-    </row>
-    <row r="581" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A581" s="5"/>
-      <c r="B581" s="5"/>
-      <c r="C581" s="5"/>
-    </row>
-    <row r="582" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A582" s="5"/>
-      <c r="B582" s="5"/>
-      <c r="C582" s="5"/>
-    </row>
-    <row r="583" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A583" s="5"/>
-      <c r="B583" s="5"/>
-      <c r="C583" s="5"/>
-    </row>
-    <row r="584" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A584" s="5"/>
-      <c r="B584" s="5"/>
-      <c r="C584" s="5"/>
-    </row>
+      <c r="A286" s="5"/>
+      <c r="B286" s="5"/>
+      <c r="C286" s="5"/>
+    </row>
+    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/Copia Envases/ListaEntrada.xlsx
+++ b/Copia Envases/ListaEntrada.xlsx
@@ -11,6 +11,9 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Hoja1" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Sheet1!$A$1:$F$13</definedName>
+  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -21,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="12">
   <si>
     <t xml:space="preserve">ID COTI</t>
   </si>
@@ -41,7 +44,13 @@
     <t xml:space="preserve">AGRUPACIÓN</t>
   </si>
   <si>
+    <t xml:space="preserve">1Q</t>
+  </si>
+  <si>
     <t xml:space="preserve">NO3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2Q</t>
   </si>
   <si>
     <t xml:space="preserve">N° de cotización (si aplica)</t>
@@ -174,11 +183,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -195,7 +204,28 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -384,8 +414,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="17.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13.28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="14.92"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="2" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16377" style="2" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -422,7 +451,9 @@
         <v>46054</v>
       </c>
       <c r="E2" s="2"/>
-      <c r="F2" s="6"/>
+      <c r="F2" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="n">
@@ -438,1983 +469,2005 @@
         <v>46054</v>
       </c>
       <c r="E3" s="2"/>
-      <c r="F3" s="6"/>
+      <c r="F3" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="n">
+      <c r="A4" s="6" t="n">
         <v>220903</v>
       </c>
-      <c r="B4" s="7" t="n">
+      <c r="B4" s="6" t="n">
         <v>1933296</v>
       </c>
-      <c r="C4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="6" t="n">
+      <c r="C4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="7" t="n">
         <v>46054</v>
       </c>
-      <c r="E4" s="7"/>
-      <c r="F4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="n">
+      <c r="A5" s="6" t="n">
         <v>220903</v>
       </c>
-      <c r="B5" s="7" t="n">
+      <c r="B5" s="6" t="n">
         <v>1933300</v>
       </c>
-      <c r="C5" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="6" t="n">
+      <c r="C5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="7" t="n">
         <v>46054</v>
       </c>
-      <c r="E5" s="7"/>
-      <c r="F5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="n">
+      <c r="A6" s="6" t="n">
         <v>221009</v>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B6" s="6" t="n">
         <v>1969781</v>
       </c>
-      <c r="C6" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="6" t="n">
+      <c r="C6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="7" t="n">
         <v>46054</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="n">
+      <c r="A7" s="6" t="n">
         <v>221009</v>
       </c>
-      <c r="B7" s="7" t="n">
+      <c r="B7" s="6" t="n">
         <v>1969792</v>
       </c>
-      <c r="C7" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="6" t="n">
+      <c r="C7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="7" t="n">
         <v>46054</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="n">
+      <c r="A8" s="6" t="n">
         <v>220892</v>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="B8" s="6" t="n">
         <v>1933042</v>
       </c>
-      <c r="C8" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>46055</v>
-      </c>
-      <c r="E8" s="7"/>
-      <c r="F8" s="6"/>
+      <c r="C8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>46056</v>
+      </c>
+      <c r="E8" s="6"/>
+      <c r="F8" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="n">
+      <c r="A9" s="6" t="n">
         <v>220892</v>
       </c>
-      <c r="B9" s="7" t="n">
+      <c r="B9" s="6" t="n">
         <v>1933089</v>
       </c>
-      <c r="C9" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>46055</v>
+      <c r="C9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>46056</v>
       </c>
       <c r="E9" s="2"/>
-      <c r="F9" s="6"/>
+      <c r="F9" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="n">
+      <c r="A10" s="6" t="n">
         <v>220903</v>
       </c>
-      <c r="B10" s="7" t="n">
+      <c r="B10" s="6" t="n">
         <v>1933292</v>
       </c>
-      <c r="C10" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>46055</v>
-      </c>
-      <c r="E10" s="7"/>
-      <c r="F10" s="6"/>
+      <c r="C10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>46056</v>
+      </c>
+      <c r="E10" s="6"/>
+      <c r="F10" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="n">
+      <c r="A11" s="6" t="n">
         <v>220903</v>
       </c>
-      <c r="B11" s="7" t="n">
+      <c r="B11" s="6" t="n">
         <v>1933299</v>
       </c>
-      <c r="C11" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>46055</v>
-      </c>
-      <c r="E11" s="7"/>
-      <c r="F11" s="6"/>
+      <c r="C11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>46056</v>
+      </c>
+      <c r="E11" s="6"/>
+      <c r="F11" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="n">
+      <c r="A12" s="6" t="n">
         <v>221009</v>
       </c>
-      <c r="B12" s="7" t="n">
+      <c r="B12" s="6" t="n">
         <v>1969781</v>
       </c>
-      <c r="C12" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="6" t="n">
-        <v>46055</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" s="6"/>
+      <c r="C12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>46056</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="n">
+      <c r="A13" s="6" t="n">
         <v>221009</v>
       </c>
-      <c r="B13" s="7" t="n">
+      <c r="B13" s="6" t="n">
         <v>1969792</v>
       </c>
-      <c r="C13" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>46055</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" s="6"/>
+      <c r="C13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>46056</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
+      <c r="A23" s="6"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
+      <c r="A25" s="6"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
+      <c r="A26" s="6"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
+      <c r="A27" s="6"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
+      <c r="A29" s="6"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
+      <c r="A30" s="6"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="7"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
+      <c r="A31" s="6"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="7"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
+      <c r="A32" s="6"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="7"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
+      <c r="A33" s="6"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="7"/>
-      <c r="B34" s="7"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
+      <c r="A34" s="6"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="7"/>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
+      <c r="A35" s="6"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="7"/>
-      <c r="B36" s="7"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="7"/>
+      <c r="A36" s="6"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="7"/>
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
+      <c r="A37" s="6"/>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="7"/>
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
+      <c r="A38" s="6"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="7"/>
-      <c r="B39" s="7"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
+      <c r="A39" s="6"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="7"/>
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
+      <c r="A40" s="6"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="7"/>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="7"/>
+      <c r="A41" s="6"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="7"/>
-      <c r="B42" s="7"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="7"/>
-      <c r="F42" s="7"/>
+      <c r="A42" s="6"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="7"/>
-      <c r="B43" s="7"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="7"/>
+      <c r="A43" s="6"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="7"/>
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
+      <c r="A44" s="6"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="7"/>
-      <c r="B45" s="7"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
-      <c r="F45" s="7"/>
+      <c r="A45" s="6"/>
+      <c r="B45" s="6"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="6"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="7"/>
-      <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="7"/>
+      <c r="A46" s="6"/>
+      <c r="B46" s="6"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="6"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="7"/>
-      <c r="B47" s="7"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="7"/>
+      <c r="A47" s="6"/>
+      <c r="B47" s="6"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="6"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="7"/>
-      <c r="B48" s="7"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="7"/>
+      <c r="A48" s="6"/>
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="7"/>
-      <c r="B49" s="7"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="7"/>
-      <c r="E49" s="7"/>
-      <c r="F49" s="7"/>
+      <c r="A49" s="6"/>
+      <c r="B49" s="6"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="6"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="7"/>
-      <c r="B50" s="7"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="7"/>
+      <c r="A50" s="6"/>
+      <c r="B50" s="6"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="7"/>
-      <c r="B51" s="7"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="7"/>
+      <c r="A51" s="6"/>
+      <c r="B51" s="6"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="6"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="7"/>
-      <c r="B52" s="7"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="7"/>
-      <c r="F52" s="7"/>
+      <c r="A52" s="6"/>
+      <c r="B52" s="6"/>
+      <c r="C52" s="6"/>
+      <c r="D52" s="6"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="6"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="7"/>
-      <c r="B53" s="7"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="7"/>
-      <c r="E53" s="7"/>
-      <c r="F53" s="7"/>
+      <c r="A53" s="6"/>
+      <c r="B53" s="6"/>
+      <c r="C53" s="6"/>
+      <c r="D53" s="6"/>
+      <c r="E53" s="6"/>
+      <c r="F53" s="6"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="7"/>
-      <c r="B54" s="7"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
+      <c r="A54" s="6"/>
+      <c r="B54" s="6"/>
+      <c r="C54" s="6"/>
+      <c r="D54" s="6"/>
+      <c r="E54" s="6"/>
+      <c r="F54" s="6"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="7"/>
-      <c r="B55" s="7"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="7"/>
-      <c r="E55" s="7"/>
-      <c r="F55" s="7"/>
+      <c r="A55" s="6"/>
+      <c r="B55" s="6"/>
+      <c r="C55" s="6"/>
+      <c r="D55" s="6"/>
+      <c r="E55" s="6"/>
+      <c r="F55" s="6"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="7"/>
-      <c r="B56" s="7"/>
-      <c r="C56" s="7"/>
-      <c r="D56" s="7"/>
-      <c r="E56" s="7"/>
-      <c r="F56" s="7"/>
+      <c r="A56" s="6"/>
+      <c r="B56" s="6"/>
+      <c r="C56" s="6"/>
+      <c r="D56" s="6"/>
+      <c r="E56" s="6"/>
+      <c r="F56" s="6"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="7"/>
-      <c r="B57" s="7"/>
-      <c r="C57" s="7"/>
-      <c r="D57" s="7"/>
-      <c r="E57" s="7"/>
-      <c r="F57" s="7"/>
+      <c r="A57" s="6"/>
+      <c r="B57" s="6"/>
+      <c r="C57" s="6"/>
+      <c r="D57" s="6"/>
+      <c r="E57" s="6"/>
+      <c r="F57" s="6"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="7"/>
-      <c r="B58" s="7"/>
-      <c r="C58" s="7"/>
-      <c r="D58" s="7"/>
-      <c r="E58" s="7"/>
-      <c r="F58" s="7"/>
+      <c r="A58" s="6"/>
+      <c r="B58" s="6"/>
+      <c r="C58" s="6"/>
+      <c r="D58" s="6"/>
+      <c r="E58" s="6"/>
+      <c r="F58" s="6"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="7"/>
-      <c r="B59" s="7"/>
-      <c r="C59" s="7"/>
-      <c r="D59" s="7"/>
-      <c r="E59" s="7"/>
-      <c r="F59" s="7"/>
+      <c r="A59" s="6"/>
+      <c r="B59" s="6"/>
+      <c r="C59" s="6"/>
+      <c r="D59" s="6"/>
+      <c r="E59" s="6"/>
+      <c r="F59" s="6"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="7"/>
-      <c r="B60" s="7"/>
-      <c r="C60" s="7"/>
-      <c r="D60" s="7"/>
-      <c r="E60" s="7"/>
-      <c r="F60" s="7"/>
+      <c r="A60" s="6"/>
+      <c r="B60" s="6"/>
+      <c r="C60" s="6"/>
+      <c r="D60" s="6"/>
+      <c r="E60" s="6"/>
+      <c r="F60" s="6"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="7"/>
-      <c r="B61" s="7"/>
-      <c r="C61" s="7"/>
-      <c r="D61" s="7"/>
-      <c r="E61" s="7"/>
-      <c r="F61" s="7"/>
+      <c r="A61" s="6"/>
+      <c r="B61" s="6"/>
+      <c r="C61" s="6"/>
+      <c r="D61" s="6"/>
+      <c r="E61" s="6"/>
+      <c r="F61" s="6"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="7"/>
-      <c r="B62" s="7"/>
-      <c r="C62" s="7"/>
-      <c r="D62" s="7"/>
-      <c r="E62" s="7"/>
-      <c r="F62" s="7"/>
+      <c r="A62" s="6"/>
+      <c r="B62" s="6"/>
+      <c r="C62" s="6"/>
+      <c r="D62" s="6"/>
+      <c r="E62" s="6"/>
+      <c r="F62" s="6"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="7"/>
-      <c r="B63" s="7"/>
-      <c r="C63" s="7"/>
-      <c r="D63" s="7"/>
-      <c r="E63" s="7"/>
-      <c r="F63" s="7"/>
+      <c r="A63" s="6"/>
+      <c r="B63" s="6"/>
+      <c r="C63" s="6"/>
+      <c r="D63" s="6"/>
+      <c r="E63" s="6"/>
+      <c r="F63" s="6"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="7"/>
-      <c r="B64" s="7"/>
-      <c r="C64" s="7"/>
-      <c r="D64" s="7"/>
-      <c r="E64" s="7"/>
-      <c r="F64" s="7"/>
+      <c r="A64" s="6"/>
+      <c r="B64" s="6"/>
+      <c r="C64" s="6"/>
+      <c r="D64" s="6"/>
+      <c r="E64" s="6"/>
+      <c r="F64" s="6"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="7"/>
-      <c r="B65" s="7"/>
-      <c r="C65" s="7"/>
-      <c r="D65" s="7"/>
-      <c r="E65" s="7"/>
-      <c r="F65" s="7"/>
+      <c r="A65" s="6"/>
+      <c r="B65" s="6"/>
+      <c r="C65" s="6"/>
+      <c r="D65" s="6"/>
+      <c r="E65" s="6"/>
+      <c r="F65" s="6"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="7"/>
-      <c r="B66" s="7"/>
-      <c r="C66" s="7"/>
-      <c r="D66" s="7"/>
-      <c r="E66" s="7"/>
-      <c r="F66" s="7"/>
+      <c r="A66" s="6"/>
+      <c r="B66" s="6"/>
+      <c r="C66" s="6"/>
+      <c r="D66" s="6"/>
+      <c r="E66" s="6"/>
+      <c r="F66" s="6"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="7"/>
-      <c r="B67" s="7"/>
-      <c r="C67" s="7"/>
-      <c r="D67" s="7"/>
-      <c r="E67" s="7"/>
-      <c r="F67" s="7"/>
+      <c r="A67" s="6"/>
+      <c r="B67" s="6"/>
+      <c r="C67" s="6"/>
+      <c r="D67" s="6"/>
+      <c r="E67" s="6"/>
+      <c r="F67" s="6"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="7"/>
-      <c r="B68" s="7"/>
-      <c r="C68" s="7"/>
-      <c r="D68" s="7"/>
-      <c r="E68" s="7"/>
-      <c r="F68" s="7"/>
+      <c r="A68" s="6"/>
+      <c r="B68" s="6"/>
+      <c r="C68" s="6"/>
+      <c r="D68" s="6"/>
+      <c r="E68" s="6"/>
+      <c r="F68" s="6"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="7"/>
-      <c r="B69" s="7"/>
-      <c r="C69" s="7"/>
-      <c r="D69" s="7"/>
-      <c r="E69" s="7"/>
-      <c r="F69" s="7"/>
+      <c r="A69" s="6"/>
+      <c r="B69" s="6"/>
+      <c r="C69" s="6"/>
+      <c r="D69" s="6"/>
+      <c r="E69" s="6"/>
+      <c r="F69" s="6"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="7"/>
-      <c r="B70" s="7"/>
-      <c r="C70" s="7"/>
-      <c r="D70" s="7"/>
-      <c r="E70" s="7"/>
-      <c r="F70" s="7"/>
+      <c r="A70" s="6"/>
+      <c r="B70" s="6"/>
+      <c r="C70" s="6"/>
+      <c r="D70" s="6"/>
+      <c r="E70" s="6"/>
+      <c r="F70" s="6"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="7"/>
-      <c r="B71" s="7"/>
-      <c r="C71" s="7"/>
-      <c r="D71" s="7"/>
-      <c r="E71" s="7"/>
-      <c r="F71" s="7"/>
+      <c r="A71" s="6"/>
+      <c r="B71" s="6"/>
+      <c r="C71" s="6"/>
+      <c r="D71" s="6"/>
+      <c r="E71" s="6"/>
+      <c r="F71" s="6"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="7"/>
-      <c r="B72" s="7"/>
-      <c r="C72" s="7"/>
-      <c r="D72" s="7"/>
-      <c r="E72" s="7"/>
-      <c r="F72" s="7"/>
+      <c r="A72" s="6"/>
+      <c r="B72" s="6"/>
+      <c r="C72" s="6"/>
+      <c r="D72" s="6"/>
+      <c r="E72" s="6"/>
+      <c r="F72" s="6"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="7"/>
-      <c r="B73" s="7"/>
-      <c r="C73" s="7"/>
-      <c r="D73" s="7"/>
-      <c r="E73" s="7"/>
-      <c r="F73" s="7"/>
+      <c r="A73" s="6"/>
+      <c r="B73" s="6"/>
+      <c r="C73" s="6"/>
+      <c r="D73" s="6"/>
+      <c r="E73" s="6"/>
+      <c r="F73" s="6"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="7"/>
-      <c r="B74" s="7"/>
-      <c r="C74" s="7"/>
-      <c r="D74" s="7"/>
-      <c r="E74" s="7"/>
-      <c r="F74" s="7"/>
+      <c r="A74" s="6"/>
+      <c r="B74" s="6"/>
+      <c r="C74" s="6"/>
+      <c r="D74" s="6"/>
+      <c r="E74" s="6"/>
+      <c r="F74" s="6"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="7"/>
-      <c r="B75" s="7"/>
-      <c r="C75" s="7"/>
-      <c r="D75" s="7"/>
-      <c r="E75" s="7"/>
-      <c r="F75" s="7"/>
+      <c r="A75" s="6"/>
+      <c r="B75" s="6"/>
+      <c r="C75" s="6"/>
+      <c r="D75" s="6"/>
+      <c r="E75" s="6"/>
+      <c r="F75" s="6"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="7"/>
-      <c r="B76" s="7"/>
-      <c r="C76" s="7"/>
-      <c r="D76" s="7"/>
-      <c r="E76" s="7"/>
-      <c r="F76" s="7"/>
+      <c r="A76" s="6"/>
+      <c r="B76" s="6"/>
+      <c r="C76" s="6"/>
+      <c r="D76" s="6"/>
+      <c r="E76" s="6"/>
+      <c r="F76" s="6"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="7"/>
-      <c r="B77" s="7"/>
-      <c r="C77" s="7"/>
-      <c r="D77" s="7"/>
-      <c r="E77" s="7"/>
-      <c r="F77" s="7"/>
+      <c r="A77" s="6"/>
+      <c r="B77" s="6"/>
+      <c r="C77" s="6"/>
+      <c r="D77" s="6"/>
+      <c r="E77" s="6"/>
+      <c r="F77" s="6"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="7"/>
-      <c r="B78" s="7"/>
-      <c r="C78" s="7"/>
-      <c r="D78" s="7"/>
-      <c r="E78" s="7"/>
-      <c r="F78" s="7"/>
+      <c r="A78" s="6"/>
+      <c r="B78" s="6"/>
+      <c r="C78" s="6"/>
+      <c r="D78" s="6"/>
+      <c r="E78" s="6"/>
+      <c r="F78" s="6"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="7"/>
-      <c r="B79" s="7"/>
-      <c r="C79" s="7"/>
-      <c r="D79" s="7"/>
-      <c r="E79" s="7"/>
-      <c r="F79" s="7"/>
+      <c r="A79" s="6"/>
+      <c r="B79" s="6"/>
+      <c r="C79" s="6"/>
+      <c r="D79" s="6"/>
+      <c r="E79" s="6"/>
+      <c r="F79" s="6"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="7"/>
-      <c r="B80" s="7"/>
-      <c r="C80" s="7"/>
-      <c r="D80" s="7"/>
-      <c r="E80" s="7"/>
-      <c r="F80" s="7"/>
+      <c r="A80" s="6"/>
+      <c r="B80" s="6"/>
+      <c r="C80" s="6"/>
+      <c r="D80" s="6"/>
+      <c r="E80" s="6"/>
+      <c r="F80" s="6"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="7"/>
-      <c r="B81" s="7"/>
-      <c r="C81" s="7"/>
-      <c r="D81" s="7"/>
-      <c r="E81" s="7"/>
-      <c r="F81" s="7"/>
+      <c r="A81" s="6"/>
+      <c r="B81" s="6"/>
+      <c r="C81" s="6"/>
+      <c r="D81" s="6"/>
+      <c r="E81" s="6"/>
+      <c r="F81" s="6"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="7"/>
-      <c r="B82" s="7"/>
-      <c r="C82" s="7"/>
-      <c r="D82" s="7"/>
-      <c r="E82" s="7"/>
-      <c r="F82" s="7"/>
+      <c r="A82" s="6"/>
+      <c r="B82" s="6"/>
+      <c r="C82" s="6"/>
+      <c r="D82" s="6"/>
+      <c r="E82" s="6"/>
+      <c r="F82" s="6"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="7"/>
-      <c r="B83" s="7"/>
-      <c r="C83" s="7"/>
-      <c r="D83" s="7"/>
-      <c r="E83" s="7"/>
-      <c r="F83" s="7"/>
+      <c r="A83" s="6"/>
+      <c r="B83" s="6"/>
+      <c r="C83" s="6"/>
+      <c r="D83" s="6"/>
+      <c r="E83" s="6"/>
+      <c r="F83" s="6"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="7"/>
-      <c r="B84" s="7"/>
-      <c r="C84" s="7"/>
-      <c r="D84" s="7"/>
-      <c r="E84" s="7"/>
-      <c r="F84" s="7"/>
+      <c r="A84" s="6"/>
+      <c r="B84" s="6"/>
+      <c r="C84" s="6"/>
+      <c r="D84" s="6"/>
+      <c r="E84" s="6"/>
+      <c r="F84" s="6"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="7"/>
-      <c r="B85" s="7"/>
-      <c r="C85" s="7"/>
-      <c r="D85" s="7"/>
-      <c r="E85" s="7"/>
-      <c r="F85" s="7"/>
+      <c r="A85" s="6"/>
+      <c r="B85" s="6"/>
+      <c r="C85" s="6"/>
+      <c r="D85" s="6"/>
+      <c r="E85" s="6"/>
+      <c r="F85" s="6"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="7"/>
-      <c r="B86" s="7"/>
-      <c r="C86" s="7"/>
-      <c r="D86" s="7"/>
-      <c r="E86" s="7"/>
-      <c r="F86" s="7"/>
+      <c r="A86" s="6"/>
+      <c r="B86" s="6"/>
+      <c r="C86" s="6"/>
+      <c r="D86" s="6"/>
+      <c r="E86" s="6"/>
+      <c r="F86" s="6"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="7"/>
-      <c r="B87" s="7"/>
-      <c r="C87" s="7"/>
-      <c r="D87" s="7"/>
-      <c r="E87" s="7"/>
-      <c r="F87" s="7"/>
+      <c r="A87" s="6"/>
+      <c r="B87" s="6"/>
+      <c r="C87" s="6"/>
+      <c r="D87" s="6"/>
+      <c r="E87" s="6"/>
+      <c r="F87" s="6"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="7"/>
-      <c r="B88" s="7"/>
-      <c r="C88" s="7"/>
-      <c r="D88" s="7"/>
-      <c r="E88" s="7"/>
-      <c r="F88" s="7"/>
+      <c r="A88" s="6"/>
+      <c r="B88" s="6"/>
+      <c r="C88" s="6"/>
+      <c r="D88" s="6"/>
+      <c r="E88" s="6"/>
+      <c r="F88" s="6"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="7"/>
-      <c r="B89" s="7"/>
-      <c r="C89" s="7"/>
-      <c r="D89" s="7"/>
-      <c r="E89" s="7"/>
-      <c r="F89" s="7"/>
+      <c r="A89" s="6"/>
+      <c r="B89" s="6"/>
+      <c r="C89" s="6"/>
+      <c r="D89" s="6"/>
+      <c r="E89" s="6"/>
+      <c r="F89" s="6"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="7"/>
-      <c r="B90" s="7"/>
-      <c r="C90" s="7"/>
-      <c r="D90" s="7"/>
-      <c r="E90" s="7"/>
-      <c r="F90" s="7"/>
+      <c r="A90" s="6"/>
+      <c r="B90" s="6"/>
+      <c r="C90" s="6"/>
+      <c r="D90" s="6"/>
+      <c r="E90" s="6"/>
+      <c r="F90" s="6"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="7"/>
-      <c r="B91" s="7"/>
-      <c r="C91" s="7"/>
-      <c r="D91" s="7"/>
-      <c r="E91" s="7"/>
-      <c r="F91" s="7"/>
+      <c r="A91" s="6"/>
+      <c r="B91" s="6"/>
+      <c r="C91" s="6"/>
+      <c r="D91" s="6"/>
+      <c r="E91" s="6"/>
+      <c r="F91" s="6"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="7"/>
-      <c r="B92" s="7"/>
-      <c r="C92" s="7"/>
-      <c r="D92" s="7"/>
-      <c r="E92" s="7"/>
-      <c r="F92" s="7"/>
+      <c r="A92" s="6"/>
+      <c r="B92" s="6"/>
+      <c r="C92" s="6"/>
+      <c r="D92" s="6"/>
+      <c r="E92" s="6"/>
+      <c r="F92" s="6"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="7"/>
-      <c r="B93" s="7"/>
-      <c r="C93" s="7"/>
-      <c r="D93" s="7"/>
-      <c r="E93" s="7"/>
-      <c r="F93" s="7"/>
+      <c r="A93" s="6"/>
+      <c r="B93" s="6"/>
+      <c r="C93" s="6"/>
+      <c r="D93" s="6"/>
+      <c r="E93" s="6"/>
+      <c r="F93" s="6"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="7"/>
-      <c r="B94" s="7"/>
-      <c r="C94" s="7"/>
-      <c r="D94" s="7"/>
-      <c r="E94" s="7"/>
-      <c r="F94" s="7"/>
+      <c r="A94" s="6"/>
+      <c r="B94" s="6"/>
+      <c r="C94" s="6"/>
+      <c r="D94" s="6"/>
+      <c r="E94" s="6"/>
+      <c r="F94" s="6"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="7"/>
-      <c r="B95" s="7"/>
-      <c r="C95" s="7"/>
-      <c r="D95" s="7"/>
-      <c r="E95" s="7"/>
-      <c r="F95" s="7"/>
+      <c r="A95" s="6"/>
+      <c r="B95" s="6"/>
+      <c r="C95" s="6"/>
+      <c r="D95" s="6"/>
+      <c r="E95" s="6"/>
+      <c r="F95" s="6"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="7"/>
-      <c r="B96" s="7"/>
-      <c r="C96" s="7"/>
-      <c r="D96" s="7"/>
-      <c r="E96" s="7"/>
-      <c r="F96" s="7"/>
+      <c r="A96" s="6"/>
+      <c r="B96" s="6"/>
+      <c r="C96" s="6"/>
+      <c r="D96" s="6"/>
+      <c r="E96" s="6"/>
+      <c r="F96" s="6"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="7"/>
-      <c r="B97" s="7"/>
-      <c r="C97" s="7"/>
-      <c r="D97" s="7"/>
-      <c r="E97" s="7"/>
-      <c r="F97" s="7"/>
+      <c r="A97" s="6"/>
+      <c r="B97" s="6"/>
+      <c r="C97" s="6"/>
+      <c r="D97" s="6"/>
+      <c r="E97" s="6"/>
+      <c r="F97" s="6"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="7"/>
-      <c r="B98" s="7"/>
-      <c r="C98" s="7"/>
-      <c r="D98" s="7"/>
-      <c r="E98" s="7"/>
-      <c r="F98" s="7"/>
+      <c r="A98" s="6"/>
+      <c r="B98" s="6"/>
+      <c r="C98" s="6"/>
+      <c r="D98" s="6"/>
+      <c r="E98" s="6"/>
+      <c r="F98" s="6"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="7"/>
-      <c r="B99" s="7"/>
-      <c r="C99" s="7"/>
-      <c r="D99" s="7"/>
-      <c r="E99" s="7"/>
-      <c r="F99" s="7"/>
+      <c r="A99" s="6"/>
+      <c r="B99" s="6"/>
+      <c r="C99" s="6"/>
+      <c r="D99" s="6"/>
+      <c r="E99" s="6"/>
+      <c r="F99" s="6"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="7"/>
-      <c r="B100" s="7"/>
-      <c r="C100" s="7"/>
-      <c r="D100" s="7"/>
-      <c r="E100" s="7"/>
-      <c r="F100" s="7"/>
+      <c r="A100" s="6"/>
+      <c r="B100" s="6"/>
+      <c r="C100" s="6"/>
+      <c r="D100" s="6"/>
+      <c r="E100" s="6"/>
+      <c r="F100" s="6"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="7"/>
-      <c r="B101" s="7"/>
-      <c r="C101" s="7"/>
-      <c r="D101" s="7"/>
-      <c r="E101" s="7"/>
-      <c r="F101" s="7"/>
+      <c r="A101" s="6"/>
+      <c r="B101" s="6"/>
+      <c r="C101" s="6"/>
+      <c r="D101" s="6"/>
+      <c r="E101" s="6"/>
+      <c r="F101" s="6"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="7"/>
-      <c r="B102" s="7"/>
-      <c r="C102" s="7"/>
-      <c r="D102" s="7"/>
-      <c r="E102" s="7"/>
-      <c r="F102" s="7"/>
+      <c r="A102" s="6"/>
+      <c r="B102" s="6"/>
+      <c r="C102" s="6"/>
+      <c r="D102" s="6"/>
+      <c r="E102" s="6"/>
+      <c r="F102" s="6"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="7"/>
-      <c r="B103" s="7"/>
-      <c r="C103" s="7"/>
-      <c r="D103" s="7"/>
-      <c r="E103" s="7"/>
-      <c r="F103" s="7"/>
+      <c r="A103" s="6"/>
+      <c r="B103" s="6"/>
+      <c r="C103" s="6"/>
+      <c r="D103" s="6"/>
+      <c r="E103" s="6"/>
+      <c r="F103" s="6"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="7"/>
-      <c r="B104" s="7"/>
-      <c r="C104" s="7"/>
-      <c r="D104" s="7"/>
-      <c r="E104" s="7"/>
-      <c r="F104" s="7"/>
+      <c r="A104" s="6"/>
+      <c r="B104" s="6"/>
+      <c r="C104" s="6"/>
+      <c r="D104" s="6"/>
+      <c r="E104" s="6"/>
+      <c r="F104" s="6"/>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A105" s="7"/>
-      <c r="B105" s="7"/>
-      <c r="C105" s="7"/>
-      <c r="D105" s="7"/>
-      <c r="E105" s="7"/>
-      <c r="F105" s="7"/>
+      <c r="A105" s="6"/>
+      <c r="B105" s="6"/>
+      <c r="C105" s="6"/>
+      <c r="D105" s="6"/>
+      <c r="E105" s="6"/>
+      <c r="F105" s="6"/>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A106" s="7"/>
-      <c r="B106" s="7"/>
-      <c r="C106" s="7"/>
-      <c r="D106" s="7"/>
-      <c r="E106" s="7"/>
-      <c r="F106" s="7"/>
+      <c r="A106" s="6"/>
+      <c r="B106" s="6"/>
+      <c r="C106" s="6"/>
+      <c r="D106" s="6"/>
+      <c r="E106" s="6"/>
+      <c r="F106" s="6"/>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A107" s="7"/>
-      <c r="B107" s="7"/>
-      <c r="C107" s="7"/>
-      <c r="D107" s="7"/>
-      <c r="E107" s="7"/>
-      <c r="F107" s="7"/>
+      <c r="A107" s="6"/>
+      <c r="B107" s="6"/>
+      <c r="C107" s="6"/>
+      <c r="D107" s="6"/>
+      <c r="E107" s="6"/>
+      <c r="F107" s="6"/>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A108" s="7"/>
-      <c r="B108" s="7"/>
-      <c r="C108" s="7"/>
-      <c r="D108" s="7"/>
-      <c r="E108" s="7"/>
-      <c r="F108" s="7"/>
+      <c r="A108" s="6"/>
+      <c r="B108" s="6"/>
+      <c r="C108" s="6"/>
+      <c r="D108" s="6"/>
+      <c r="E108" s="6"/>
+      <c r="F108" s="6"/>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A109" s="7"/>
-      <c r="B109" s="7"/>
-      <c r="C109" s="7"/>
-      <c r="D109" s="7"/>
-      <c r="E109" s="7"/>
-      <c r="F109" s="7"/>
+      <c r="A109" s="6"/>
+      <c r="B109" s="6"/>
+      <c r="C109" s="6"/>
+      <c r="D109" s="6"/>
+      <c r="E109" s="6"/>
+      <c r="F109" s="6"/>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A110" s="7"/>
-      <c r="B110" s="7"/>
-      <c r="C110" s="7"/>
-      <c r="D110" s="7"/>
-      <c r="E110" s="7"/>
-      <c r="F110" s="7"/>
+      <c r="A110" s="6"/>
+      <c r="B110" s="6"/>
+      <c r="C110" s="6"/>
+      <c r="D110" s="6"/>
+      <c r="E110" s="6"/>
+      <c r="F110" s="6"/>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A111" s="7"/>
-      <c r="B111" s="7"/>
-      <c r="C111" s="7"/>
-      <c r="D111" s="7"/>
-      <c r="E111" s="7"/>
-      <c r="F111" s="7"/>
+      <c r="A111" s="6"/>
+      <c r="B111" s="6"/>
+      <c r="C111" s="6"/>
+      <c r="D111" s="6"/>
+      <c r="E111" s="6"/>
+      <c r="F111" s="6"/>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A112" s="7"/>
-      <c r="B112" s="7"/>
-      <c r="C112" s="7"/>
-      <c r="D112" s="7"/>
-      <c r="E112" s="7"/>
-      <c r="F112" s="7"/>
+      <c r="A112" s="6"/>
+      <c r="B112" s="6"/>
+      <c r="C112" s="6"/>
+      <c r="D112" s="6"/>
+      <c r="E112" s="6"/>
+      <c r="F112" s="6"/>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A113" s="7"/>
-      <c r="B113" s="7"/>
-      <c r="C113" s="7"/>
-      <c r="D113" s="7"/>
-      <c r="E113" s="7"/>
-      <c r="F113" s="7"/>
+      <c r="A113" s="6"/>
+      <c r="B113" s="6"/>
+      <c r="C113" s="6"/>
+      <c r="D113" s="6"/>
+      <c r="E113" s="6"/>
+      <c r="F113" s="6"/>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A114" s="7"/>
-      <c r="B114" s="7"/>
-      <c r="C114" s="7"/>
-      <c r="D114" s="7"/>
-      <c r="E114" s="7"/>
-      <c r="F114" s="7"/>
+      <c r="A114" s="6"/>
+      <c r="B114" s="6"/>
+      <c r="C114" s="6"/>
+      <c r="D114" s="6"/>
+      <c r="E114" s="6"/>
+      <c r="F114" s="6"/>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A115" s="7"/>
-      <c r="B115" s="7"/>
-      <c r="C115" s="7"/>
-      <c r="D115" s="7"/>
-      <c r="E115" s="7"/>
-      <c r="F115" s="7"/>
+      <c r="A115" s="6"/>
+      <c r="B115" s="6"/>
+      <c r="C115" s="6"/>
+      <c r="D115" s="6"/>
+      <c r="E115" s="6"/>
+      <c r="F115" s="6"/>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A116" s="7"/>
-      <c r="B116" s="7"/>
-      <c r="C116" s="7"/>
-      <c r="D116" s="7"/>
-      <c r="E116" s="7"/>
-      <c r="F116" s="7"/>
+      <c r="A116" s="6"/>
+      <c r="B116" s="6"/>
+      <c r="C116" s="6"/>
+      <c r="D116" s="6"/>
+      <c r="E116" s="6"/>
+      <c r="F116" s="6"/>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A117" s="7"/>
-      <c r="B117" s="7"/>
-      <c r="C117" s="7"/>
-      <c r="D117" s="7"/>
-      <c r="E117" s="7"/>
-      <c r="F117" s="7"/>
+      <c r="A117" s="6"/>
+      <c r="B117" s="6"/>
+      <c r="C117" s="6"/>
+      <c r="D117" s="6"/>
+      <c r="E117" s="6"/>
+      <c r="F117" s="6"/>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A118" s="7"/>
-      <c r="B118" s="7"/>
-      <c r="C118" s="7"/>
-      <c r="D118" s="7"/>
-      <c r="E118" s="7"/>
-      <c r="F118" s="7"/>
+      <c r="A118" s="6"/>
+      <c r="B118" s="6"/>
+      <c r="C118" s="6"/>
+      <c r="D118" s="6"/>
+      <c r="E118" s="6"/>
+      <c r="F118" s="6"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A119" s="7"/>
-      <c r="B119" s="7"/>
-      <c r="C119" s="7"/>
-      <c r="D119" s="7"/>
-      <c r="E119" s="7"/>
-      <c r="F119" s="7"/>
+      <c r="A119" s="6"/>
+      <c r="B119" s="6"/>
+      <c r="C119" s="6"/>
+      <c r="D119" s="6"/>
+      <c r="E119" s="6"/>
+      <c r="F119" s="6"/>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A120" s="7"/>
-      <c r="B120" s="7"/>
-      <c r="C120" s="7"/>
-      <c r="D120" s="7"/>
-      <c r="E120" s="7"/>
-      <c r="F120" s="7"/>
+      <c r="A120" s="6"/>
+      <c r="B120" s="6"/>
+      <c r="C120" s="6"/>
+      <c r="D120" s="6"/>
+      <c r="E120" s="6"/>
+      <c r="F120" s="6"/>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A121" s="7"/>
-      <c r="B121" s="7"/>
-      <c r="C121" s="7"/>
-      <c r="D121" s="7"/>
-      <c r="E121" s="7"/>
-      <c r="F121" s="7"/>
+      <c r="A121" s="6"/>
+      <c r="B121" s="6"/>
+      <c r="C121" s="6"/>
+      <c r="D121" s="6"/>
+      <c r="E121" s="6"/>
+      <c r="F121" s="6"/>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A122" s="7"/>
-      <c r="B122" s="7"/>
-      <c r="C122" s="7"/>
-      <c r="D122" s="7"/>
-      <c r="E122" s="7"/>
-      <c r="F122" s="7"/>
+      <c r="A122" s="6"/>
+      <c r="B122" s="6"/>
+      <c r="C122" s="6"/>
+      <c r="D122" s="6"/>
+      <c r="E122" s="6"/>
+      <c r="F122" s="6"/>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A123" s="7"/>
-      <c r="B123" s="7"/>
-      <c r="C123" s="7"/>
-      <c r="D123" s="7"/>
-      <c r="E123" s="7"/>
-      <c r="F123" s="7"/>
+      <c r="A123" s="6"/>
+      <c r="B123" s="6"/>
+      <c r="C123" s="6"/>
+      <c r="D123" s="6"/>
+      <c r="E123" s="6"/>
+      <c r="F123" s="6"/>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A124" s="7"/>
-      <c r="B124" s="7"/>
-      <c r="C124" s="7"/>
-      <c r="D124" s="7"/>
-      <c r="E124" s="7"/>
-      <c r="F124" s="7"/>
+      <c r="A124" s="6"/>
+      <c r="B124" s="6"/>
+      <c r="C124" s="6"/>
+      <c r="D124" s="6"/>
+      <c r="E124" s="6"/>
+      <c r="F124" s="6"/>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A125" s="7"/>
-      <c r="B125" s="7"/>
-      <c r="C125" s="7"/>
-      <c r="D125" s="7"/>
-      <c r="E125" s="7"/>
-      <c r="F125" s="7"/>
+      <c r="A125" s="6"/>
+      <c r="B125" s="6"/>
+      <c r="C125" s="6"/>
+      <c r="D125" s="6"/>
+      <c r="E125" s="6"/>
+      <c r="F125" s="6"/>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A126" s="7"/>
-      <c r="B126" s="7"/>
-      <c r="C126" s="7"/>
-      <c r="D126" s="7"/>
-      <c r="E126" s="7"/>
-      <c r="F126" s="7"/>
+      <c r="A126" s="6"/>
+      <c r="B126" s="6"/>
+      <c r="C126" s="6"/>
+      <c r="D126" s="6"/>
+      <c r="E126" s="6"/>
+      <c r="F126" s="6"/>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A127" s="7"/>
-      <c r="B127" s="7"/>
-      <c r="C127" s="7"/>
-      <c r="D127" s="7"/>
-      <c r="E127" s="7"/>
-      <c r="F127" s="7"/>
+      <c r="A127" s="6"/>
+      <c r="B127" s="6"/>
+      <c r="C127" s="6"/>
+      <c r="D127" s="6"/>
+      <c r="E127" s="6"/>
+      <c r="F127" s="6"/>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A128" s="7"/>
-      <c r="B128" s="7"/>
-      <c r="C128" s="7"/>
-      <c r="D128" s="7"/>
-      <c r="E128" s="7"/>
-      <c r="F128" s="7"/>
+      <c r="A128" s="6"/>
+      <c r="B128" s="6"/>
+      <c r="C128" s="6"/>
+      <c r="D128" s="6"/>
+      <c r="E128" s="6"/>
+      <c r="F128" s="6"/>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A129" s="7"/>
-      <c r="B129" s="7"/>
-      <c r="C129" s="7"/>
-      <c r="D129" s="7"/>
-      <c r="E129" s="7"/>
-      <c r="F129" s="7"/>
+      <c r="A129" s="6"/>
+      <c r="B129" s="6"/>
+      <c r="C129" s="6"/>
+      <c r="D129" s="6"/>
+      <c r="E129" s="6"/>
+      <c r="F129" s="6"/>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A130" s="7"/>
-      <c r="B130" s="7"/>
-      <c r="C130" s="7"/>
-      <c r="D130" s="7"/>
-      <c r="E130" s="7"/>
-      <c r="F130" s="7"/>
+      <c r="A130" s="6"/>
+      <c r="B130" s="6"/>
+      <c r="C130" s="6"/>
+      <c r="D130" s="6"/>
+      <c r="E130" s="6"/>
+      <c r="F130" s="6"/>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A131" s="7"/>
-      <c r="B131" s="7"/>
-      <c r="C131" s="7"/>
-      <c r="D131" s="7"/>
-      <c r="E131" s="7"/>
-      <c r="F131" s="7"/>
+      <c r="A131" s="6"/>
+      <c r="B131" s="6"/>
+      <c r="C131" s="6"/>
+      <c r="D131" s="6"/>
+      <c r="E131" s="6"/>
+      <c r="F131" s="6"/>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A132" s="7"/>
-      <c r="B132" s="7"/>
-      <c r="C132" s="7"/>
-      <c r="D132" s="7"/>
-      <c r="E132" s="7"/>
-      <c r="F132" s="7"/>
+      <c r="A132" s="6"/>
+      <c r="B132" s="6"/>
+      <c r="C132" s="6"/>
+      <c r="D132" s="6"/>
+      <c r="E132" s="6"/>
+      <c r="F132" s="6"/>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A133" s="7"/>
-      <c r="B133" s="7"/>
-      <c r="C133" s="7"/>
-      <c r="D133" s="7"/>
-      <c r="E133" s="7"/>
-      <c r="F133" s="7"/>
+      <c r="A133" s="6"/>
+      <c r="B133" s="6"/>
+      <c r="C133" s="6"/>
+      <c r="D133" s="6"/>
+      <c r="E133" s="6"/>
+      <c r="F133" s="6"/>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A134" s="7"/>
-      <c r="B134" s="7"/>
-      <c r="C134" s="7"/>
-      <c r="D134" s="7"/>
-      <c r="E134" s="7"/>
-      <c r="F134" s="7"/>
+      <c r="A134" s="6"/>
+      <c r="B134" s="6"/>
+      <c r="C134" s="6"/>
+      <c r="D134" s="6"/>
+      <c r="E134" s="6"/>
+      <c r="F134" s="6"/>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A135" s="7"/>
-      <c r="B135" s="7"/>
-      <c r="C135" s="7"/>
-      <c r="D135" s="7"/>
-      <c r="E135" s="7"/>
-      <c r="F135" s="7"/>
+      <c r="A135" s="6"/>
+      <c r="B135" s="6"/>
+      <c r="C135" s="6"/>
+      <c r="D135" s="6"/>
+      <c r="E135" s="6"/>
+      <c r="F135" s="6"/>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A136" s="7"/>
-      <c r="B136" s="7"/>
-      <c r="C136" s="7"/>
-      <c r="D136" s="7"/>
-      <c r="E136" s="7"/>
-      <c r="F136" s="7"/>
+      <c r="A136" s="6"/>
+      <c r="B136" s="6"/>
+      <c r="C136" s="6"/>
+      <c r="D136" s="6"/>
+      <c r="E136" s="6"/>
+      <c r="F136" s="6"/>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A137" s="7"/>
-      <c r="B137" s="7"/>
-      <c r="C137" s="7"/>
-      <c r="D137" s="7"/>
-      <c r="E137" s="7"/>
-      <c r="F137" s="7"/>
+      <c r="A137" s="6"/>
+      <c r="B137" s="6"/>
+      <c r="C137" s="6"/>
+      <c r="D137" s="6"/>
+      <c r="E137" s="6"/>
+      <c r="F137" s="6"/>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A138" s="7"/>
-      <c r="B138" s="7"/>
-      <c r="C138" s="7"/>
-      <c r="D138" s="7"/>
-      <c r="E138" s="7"/>
-      <c r="F138" s="7"/>
+      <c r="A138" s="6"/>
+      <c r="B138" s="6"/>
+      <c r="C138" s="6"/>
+      <c r="D138" s="6"/>
+      <c r="E138" s="6"/>
+      <c r="F138" s="6"/>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A139" s="7"/>
-      <c r="B139" s="7"/>
-      <c r="C139" s="7"/>
-      <c r="D139" s="7"/>
-      <c r="E139" s="7"/>
-      <c r="F139" s="7"/>
+      <c r="A139" s="6"/>
+      <c r="B139" s="6"/>
+      <c r="C139" s="6"/>
+      <c r="D139" s="6"/>
+      <c r="E139" s="6"/>
+      <c r="F139" s="6"/>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A140" s="7"/>
-      <c r="B140" s="7"/>
-      <c r="C140" s="7"/>
-      <c r="D140" s="7"/>
-      <c r="E140" s="7"/>
-      <c r="F140" s="7"/>
+      <c r="A140" s="6"/>
+      <c r="B140" s="6"/>
+      <c r="C140" s="6"/>
+      <c r="D140" s="6"/>
+      <c r="E140" s="6"/>
+      <c r="F140" s="6"/>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A141" s="7"/>
-      <c r="B141" s="7"/>
-      <c r="C141" s="7"/>
-      <c r="D141" s="7"/>
-      <c r="E141" s="7"/>
-      <c r="F141" s="7"/>
+      <c r="A141" s="6"/>
+      <c r="B141" s="6"/>
+      <c r="C141" s="6"/>
+      <c r="D141" s="6"/>
+      <c r="E141" s="6"/>
+      <c r="F141" s="6"/>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A142" s="7"/>
-      <c r="B142" s="7"/>
-      <c r="C142" s="7"/>
-      <c r="D142" s="7"/>
-      <c r="E142" s="7"/>
-      <c r="F142" s="7"/>
+      <c r="A142" s="6"/>
+      <c r="B142" s="6"/>
+      <c r="C142" s="6"/>
+      <c r="D142" s="6"/>
+      <c r="E142" s="6"/>
+      <c r="F142" s="6"/>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A143" s="7"/>
-      <c r="B143" s="7"/>
-      <c r="C143" s="7"/>
-      <c r="D143" s="7"/>
-      <c r="E143" s="7"/>
-      <c r="F143" s="7"/>
+      <c r="A143" s="6"/>
+      <c r="B143" s="6"/>
+      <c r="C143" s="6"/>
+      <c r="D143" s="6"/>
+      <c r="E143" s="6"/>
+      <c r="F143" s="6"/>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A144" s="7"/>
-      <c r="B144" s="7"/>
-      <c r="C144" s="7"/>
-      <c r="D144" s="7"/>
-      <c r="E144" s="7"/>
-      <c r="F144" s="7"/>
+      <c r="A144" s="6"/>
+      <c r="B144" s="6"/>
+      <c r="C144" s="6"/>
+      <c r="D144" s="6"/>
+      <c r="E144" s="6"/>
+      <c r="F144" s="6"/>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A145" s="7"/>
-      <c r="B145" s="7"/>
-      <c r="C145" s="7"/>
-      <c r="D145" s="7"/>
-      <c r="E145" s="7"/>
-      <c r="F145" s="7"/>
+      <c r="A145" s="6"/>
+      <c r="B145" s="6"/>
+      <c r="C145" s="6"/>
+      <c r="D145" s="6"/>
+      <c r="E145" s="6"/>
+      <c r="F145" s="6"/>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A146" s="7"/>
-      <c r="B146" s="7"/>
-      <c r="C146" s="7"/>
-      <c r="D146" s="7"/>
-      <c r="E146" s="7"/>
-      <c r="F146" s="7"/>
+      <c r="A146" s="6"/>
+      <c r="B146" s="6"/>
+      <c r="C146" s="6"/>
+      <c r="D146" s="6"/>
+      <c r="E146" s="6"/>
+      <c r="F146" s="6"/>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A147" s="7"/>
-      <c r="B147" s="7"/>
-      <c r="C147" s="7"/>
-      <c r="D147" s="7"/>
-      <c r="E147" s="7"/>
-      <c r="F147" s="7"/>
+      <c r="A147" s="6"/>
+      <c r="B147" s="6"/>
+      <c r="C147" s="6"/>
+      <c r="D147" s="6"/>
+      <c r="E147" s="6"/>
+      <c r="F147" s="6"/>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A148" s="7"/>
-      <c r="B148" s="7"/>
-      <c r="C148" s="7"/>
-      <c r="D148" s="7"/>
-      <c r="E148" s="7"/>
-      <c r="F148" s="7"/>
+      <c r="A148" s="6"/>
+      <c r="B148" s="6"/>
+      <c r="C148" s="6"/>
+      <c r="D148" s="6"/>
+      <c r="E148" s="6"/>
+      <c r="F148" s="6"/>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A149" s="7"/>
-      <c r="B149" s="7"/>
-      <c r="C149" s="7"/>
-      <c r="D149" s="7"/>
-      <c r="E149" s="7"/>
-      <c r="F149" s="7"/>
+      <c r="A149" s="6"/>
+      <c r="B149" s="6"/>
+      <c r="C149" s="6"/>
+      <c r="D149" s="6"/>
+      <c r="E149" s="6"/>
+      <c r="F149" s="6"/>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A150" s="7"/>
-      <c r="B150" s="7"/>
-      <c r="C150" s="7"/>
-      <c r="D150" s="7"/>
-      <c r="E150" s="7"/>
-      <c r="F150" s="7"/>
+      <c r="A150" s="6"/>
+      <c r="B150" s="6"/>
+      <c r="C150" s="6"/>
+      <c r="D150" s="6"/>
+      <c r="E150" s="6"/>
+      <c r="F150" s="6"/>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A151" s="7"/>
-      <c r="B151" s="7"/>
-      <c r="C151" s="7"/>
-      <c r="D151" s="7"/>
-      <c r="E151" s="7"/>
-      <c r="F151" s="7"/>
+      <c r="A151" s="6"/>
+      <c r="B151" s="6"/>
+      <c r="C151" s="6"/>
+      <c r="D151" s="6"/>
+      <c r="E151" s="6"/>
+      <c r="F151" s="6"/>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A152" s="7"/>
-      <c r="B152" s="7"/>
-      <c r="C152" s="7"/>
-      <c r="D152" s="7"/>
-      <c r="E152" s="7"/>
-      <c r="F152" s="7"/>
+      <c r="A152" s="6"/>
+      <c r="B152" s="6"/>
+      <c r="C152" s="6"/>
+      <c r="D152" s="6"/>
+      <c r="E152" s="6"/>
+      <c r="F152" s="6"/>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A153" s="7"/>
-      <c r="B153" s="7"/>
-      <c r="C153" s="7"/>
-      <c r="D153" s="7"/>
-      <c r="E153" s="7"/>
-      <c r="F153" s="7"/>
+      <c r="A153" s="6"/>
+      <c r="B153" s="6"/>
+      <c r="C153" s="6"/>
+      <c r="D153" s="6"/>
+      <c r="E153" s="6"/>
+      <c r="F153" s="6"/>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A154" s="7"/>
-      <c r="B154" s="7"/>
-      <c r="C154" s="7"/>
-      <c r="D154" s="7"/>
-      <c r="E154" s="7"/>
-      <c r="F154" s="7"/>
+      <c r="A154" s="6"/>
+      <c r="B154" s="6"/>
+      <c r="C154" s="6"/>
+      <c r="D154" s="6"/>
+      <c r="E154" s="6"/>
+      <c r="F154" s="6"/>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A155" s="7"/>
-      <c r="B155" s="7"/>
-      <c r="C155" s="7"/>
-      <c r="D155" s="7"/>
-      <c r="E155" s="7"/>
-      <c r="F155" s="7"/>
+      <c r="A155" s="6"/>
+      <c r="B155" s="6"/>
+      <c r="C155" s="6"/>
+      <c r="D155" s="6"/>
+      <c r="E155" s="6"/>
+      <c r="F155" s="6"/>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A156" s="7"/>
-      <c r="B156" s="7"/>
-      <c r="C156" s="7"/>
-      <c r="D156" s="7"/>
-      <c r="E156" s="7"/>
-      <c r="F156" s="7"/>
+      <c r="A156" s="6"/>
+      <c r="B156" s="6"/>
+      <c r="C156" s="6"/>
+      <c r="D156" s="6"/>
+      <c r="E156" s="6"/>
+      <c r="F156" s="6"/>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A157" s="7"/>
-      <c r="B157" s="7"/>
-      <c r="C157" s="7"/>
-      <c r="D157" s="7"/>
-      <c r="E157" s="7"/>
-      <c r="F157" s="7"/>
+      <c r="A157" s="6"/>
+      <c r="B157" s="6"/>
+      <c r="C157" s="6"/>
+      <c r="D157" s="6"/>
+      <c r="E157" s="6"/>
+      <c r="F157" s="6"/>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A158" s="7"/>
-      <c r="B158" s="7"/>
-      <c r="C158" s="7"/>
-      <c r="D158" s="7"/>
-      <c r="E158" s="7"/>
-      <c r="F158" s="7"/>
+      <c r="A158" s="6"/>
+      <c r="B158" s="6"/>
+      <c r="C158" s="6"/>
+      <c r="D158" s="6"/>
+      <c r="E158" s="6"/>
+      <c r="F158" s="6"/>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A159" s="7"/>
-      <c r="B159" s="7"/>
-      <c r="C159" s="7"/>
-      <c r="D159" s="7"/>
-      <c r="E159" s="7"/>
-      <c r="F159" s="7"/>
+      <c r="A159" s="6"/>
+      <c r="B159" s="6"/>
+      <c r="C159" s="6"/>
+      <c r="D159" s="6"/>
+      <c r="E159" s="6"/>
+      <c r="F159" s="6"/>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A160" s="7"/>
-      <c r="B160" s="7"/>
-      <c r="C160" s="7"/>
-      <c r="D160" s="7"/>
-      <c r="E160" s="7"/>
-      <c r="F160" s="7"/>
+      <c r="A160" s="6"/>
+      <c r="B160" s="6"/>
+      <c r="C160" s="6"/>
+      <c r="D160" s="6"/>
+      <c r="E160" s="6"/>
+      <c r="F160" s="6"/>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A161" s="7"/>
-      <c r="B161" s="7"/>
-      <c r="C161" s="7"/>
-      <c r="D161" s="7"/>
-      <c r="E161" s="7"/>
-      <c r="F161" s="7"/>
+      <c r="A161" s="6"/>
+      <c r="B161" s="6"/>
+      <c r="C161" s="6"/>
+      <c r="D161" s="6"/>
+      <c r="E161" s="6"/>
+      <c r="F161" s="6"/>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A162" s="7"/>
-      <c r="B162" s="7"/>
-      <c r="C162" s="7"/>
-      <c r="D162" s="7"/>
-      <c r="E162" s="7"/>
-      <c r="F162" s="7"/>
+      <c r="A162" s="6"/>
+      <c r="B162" s="6"/>
+      <c r="C162" s="6"/>
+      <c r="D162" s="6"/>
+      <c r="E162" s="6"/>
+      <c r="F162" s="6"/>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A163" s="7"/>
-      <c r="B163" s="7"/>
-      <c r="C163" s="7"/>
-      <c r="D163" s="7"/>
-      <c r="E163" s="7"/>
-      <c r="F163" s="7"/>
+      <c r="A163" s="6"/>
+      <c r="B163" s="6"/>
+      <c r="C163" s="6"/>
+      <c r="D163" s="6"/>
+      <c r="E163" s="6"/>
+      <c r="F163" s="6"/>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A164" s="7"/>
-      <c r="B164" s="7"/>
-      <c r="C164" s="7"/>
-      <c r="D164" s="7"/>
-      <c r="E164" s="7"/>
-      <c r="F164" s="7"/>
+      <c r="A164" s="6"/>
+      <c r="B164" s="6"/>
+      <c r="C164" s="6"/>
+      <c r="D164" s="6"/>
+      <c r="E164" s="6"/>
+      <c r="F164" s="6"/>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A165" s="7"/>
-      <c r="B165" s="7"/>
-      <c r="C165" s="7"/>
-      <c r="D165" s="7"/>
-      <c r="E165" s="7"/>
-      <c r="F165" s="7"/>
+      <c r="A165" s="6"/>
+      <c r="B165" s="6"/>
+      <c r="C165" s="6"/>
+      <c r="D165" s="6"/>
+      <c r="E165" s="6"/>
+      <c r="F165" s="6"/>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A166" s="7"/>
-      <c r="B166" s="7"/>
-      <c r="C166" s="7"/>
-      <c r="D166" s="7"/>
-      <c r="E166" s="7"/>
-      <c r="F166" s="7"/>
+      <c r="A166" s="6"/>
+      <c r="B166" s="6"/>
+      <c r="C166" s="6"/>
+      <c r="D166" s="6"/>
+      <c r="E166" s="6"/>
+      <c r="F166" s="6"/>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A167" s="7"/>
-      <c r="B167" s="7"/>
-      <c r="C167" s="7"/>
-      <c r="D167" s="7"/>
-      <c r="E167" s="7"/>
-      <c r="F167" s="7"/>
+      <c r="A167" s="6"/>
+      <c r="B167" s="6"/>
+      <c r="C167" s="6"/>
+      <c r="D167" s="6"/>
+      <c r="E167" s="6"/>
+      <c r="F167" s="6"/>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A168" s="7"/>
-      <c r="B168" s="7"/>
-      <c r="C168" s="7"/>
-      <c r="D168" s="7"/>
-      <c r="E168" s="7"/>
-      <c r="F168" s="7"/>
+      <c r="A168" s="6"/>
+      <c r="B168" s="6"/>
+      <c r="C168" s="6"/>
+      <c r="D168" s="6"/>
+      <c r="E168" s="6"/>
+      <c r="F168" s="6"/>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A169" s="7"/>
-      <c r="B169" s="7"/>
-      <c r="C169" s="7"/>
-      <c r="D169" s="7"/>
-      <c r="E169" s="7"/>
-      <c r="F169" s="7"/>
+      <c r="A169" s="6"/>
+      <c r="B169" s="6"/>
+      <c r="C169" s="6"/>
+      <c r="D169" s="6"/>
+      <c r="E169" s="6"/>
+      <c r="F169" s="6"/>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A170" s="7"/>
-      <c r="B170" s="7"/>
-      <c r="C170" s="7"/>
-      <c r="D170" s="7"/>
-      <c r="E170" s="7"/>
-      <c r="F170" s="7"/>
+      <c r="A170" s="6"/>
+      <c r="B170" s="6"/>
+      <c r="C170" s="6"/>
+      <c r="D170" s="6"/>
+      <c r="E170" s="6"/>
+      <c r="F170" s="6"/>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A171" s="7"/>
-      <c r="B171" s="7"/>
-      <c r="C171" s="7"/>
-      <c r="D171" s="7"/>
-      <c r="E171" s="7"/>
-      <c r="F171" s="7"/>
+      <c r="A171" s="6"/>
+      <c r="B171" s="6"/>
+      <c r="C171" s="6"/>
+      <c r="D171" s="6"/>
+      <c r="E171" s="6"/>
+      <c r="F171" s="6"/>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A172" s="7"/>
-      <c r="B172" s="7"/>
-      <c r="C172" s="7"/>
-      <c r="D172" s="7"/>
-      <c r="E172" s="7"/>
-      <c r="F172" s="7"/>
+      <c r="A172" s="6"/>
+      <c r="B172" s="6"/>
+      <c r="C172" s="6"/>
+      <c r="D172" s="6"/>
+      <c r="E172" s="6"/>
+      <c r="F172" s="6"/>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A173" s="7"/>
-      <c r="B173" s="7"/>
-      <c r="C173" s="7"/>
-      <c r="D173" s="7"/>
-      <c r="E173" s="7"/>
-      <c r="F173" s="7"/>
+      <c r="A173" s="6"/>
+      <c r="B173" s="6"/>
+      <c r="C173" s="6"/>
+      <c r="D173" s="6"/>
+      <c r="E173" s="6"/>
+      <c r="F173" s="6"/>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A174" s="7"/>
-      <c r="B174" s="7"/>
-      <c r="C174" s="7"/>
-      <c r="D174" s="7"/>
-      <c r="E174" s="7"/>
-      <c r="F174" s="7"/>
+      <c r="A174" s="6"/>
+      <c r="B174" s="6"/>
+      <c r="C174" s="6"/>
+      <c r="D174" s="6"/>
+      <c r="E174" s="6"/>
+      <c r="F174" s="6"/>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A175" s="7"/>
-      <c r="B175" s="7"/>
-      <c r="C175" s="7"/>
-      <c r="D175" s="7"/>
-      <c r="E175" s="7"/>
-      <c r="F175" s="7"/>
+      <c r="A175" s="6"/>
+      <c r="B175" s="6"/>
+      <c r="C175" s="6"/>
+      <c r="D175" s="6"/>
+      <c r="E175" s="6"/>
+      <c r="F175" s="6"/>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A176" s="7"/>
-      <c r="B176" s="7"/>
-      <c r="C176" s="7"/>
-      <c r="D176" s="7"/>
-      <c r="E176" s="7"/>
-      <c r="F176" s="7"/>
+      <c r="A176" s="6"/>
+      <c r="B176" s="6"/>
+      <c r="C176" s="6"/>
+      <c r="D176" s="6"/>
+      <c r="E176" s="6"/>
+      <c r="F176" s="6"/>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A177" s="7"/>
-      <c r="B177" s="7"/>
-      <c r="C177" s="7"/>
-      <c r="D177" s="7"/>
-      <c r="E177" s="7"/>
-      <c r="F177" s="7"/>
+      <c r="A177" s="6"/>
+      <c r="B177" s="6"/>
+      <c r="C177" s="6"/>
+      <c r="D177" s="6"/>
+      <c r="E177" s="6"/>
+      <c r="F177" s="6"/>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A178" s="7"/>
-      <c r="B178" s="7"/>
-      <c r="C178" s="7"/>
-      <c r="D178" s="7"/>
-      <c r="E178" s="7"/>
-      <c r="F178" s="7"/>
+      <c r="A178" s="6"/>
+      <c r="B178" s="6"/>
+      <c r="C178" s="6"/>
+      <c r="D178" s="6"/>
+      <c r="E178" s="6"/>
+      <c r="F178" s="6"/>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A179" s="7"/>
-      <c r="B179" s="7"/>
-      <c r="C179" s="7"/>
-      <c r="D179" s="7"/>
-      <c r="E179" s="7"/>
-      <c r="F179" s="7"/>
+      <c r="A179" s="6"/>
+      <c r="B179" s="6"/>
+      <c r="C179" s="6"/>
+      <c r="D179" s="6"/>
+      <c r="E179" s="6"/>
+      <c r="F179" s="6"/>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A180" s="7"/>
-      <c r="B180" s="7"/>
-      <c r="C180" s="7"/>
-      <c r="D180" s="7"/>
-      <c r="E180" s="7"/>
-      <c r="F180" s="7"/>
+      <c r="A180" s="6"/>
+      <c r="B180" s="6"/>
+      <c r="C180" s="6"/>
+      <c r="D180" s="6"/>
+      <c r="E180" s="6"/>
+      <c r="F180" s="6"/>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A181" s="7"/>
-      <c r="B181" s="7"/>
-      <c r="C181" s="7"/>
-      <c r="D181" s="7"/>
-      <c r="E181" s="7"/>
-      <c r="F181" s="7"/>
+      <c r="A181" s="6"/>
+      <c r="B181" s="6"/>
+      <c r="C181" s="6"/>
+      <c r="D181" s="6"/>
+      <c r="E181" s="6"/>
+      <c r="F181" s="6"/>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A182" s="7"/>
-      <c r="B182" s="7"/>
-      <c r="C182" s="7"/>
-      <c r="D182" s="7"/>
-      <c r="E182" s="7"/>
-      <c r="F182" s="7"/>
+      <c r="A182" s="6"/>
+      <c r="B182" s="6"/>
+      <c r="C182" s="6"/>
+      <c r="D182" s="6"/>
+      <c r="E182" s="6"/>
+      <c r="F182" s="6"/>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A183" s="7"/>
-      <c r="B183" s="7"/>
-      <c r="C183" s="7"/>
-      <c r="D183" s="7"/>
-      <c r="E183" s="7"/>
-      <c r="F183" s="7"/>
+      <c r="A183" s="6"/>
+      <c r="B183" s="6"/>
+      <c r="C183" s="6"/>
+      <c r="D183" s="6"/>
+      <c r="E183" s="6"/>
+      <c r="F183" s="6"/>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A184" s="7"/>
-      <c r="B184" s="7"/>
-      <c r="C184" s="7"/>
-      <c r="D184" s="7"/>
-      <c r="E184" s="7"/>
-      <c r="F184" s="7"/>
+      <c r="A184" s="6"/>
+      <c r="B184" s="6"/>
+      <c r="C184" s="6"/>
+      <c r="D184" s="6"/>
+      <c r="E184" s="6"/>
+      <c r="F184" s="6"/>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A185" s="7"/>
-      <c r="B185" s="7"/>
-      <c r="C185" s="7"/>
-      <c r="D185" s="7"/>
-      <c r="E185" s="7"/>
-      <c r="F185" s="7"/>
+      <c r="A185" s="6"/>
+      <c r="B185" s="6"/>
+      <c r="C185" s="6"/>
+      <c r="D185" s="6"/>
+      <c r="E185" s="6"/>
+      <c r="F185" s="6"/>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A186" s="7"/>
-      <c r="B186" s="7"/>
-      <c r="C186" s="7"/>
-      <c r="D186" s="7"/>
-      <c r="E186" s="7"/>
-      <c r="F186" s="7"/>
+      <c r="A186" s="6"/>
+      <c r="B186" s="6"/>
+      <c r="C186" s="6"/>
+      <c r="D186" s="6"/>
+      <c r="E186" s="6"/>
+      <c r="F186" s="6"/>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A187" s="7"/>
-      <c r="B187" s="7"/>
-      <c r="C187" s="7"/>
-      <c r="D187" s="7"/>
-      <c r="E187" s="7"/>
-      <c r="F187" s="7"/>
+      <c r="A187" s="6"/>
+      <c r="B187" s="6"/>
+      <c r="C187" s="6"/>
+      <c r="D187" s="6"/>
+      <c r="E187" s="6"/>
+      <c r="F187" s="6"/>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A188" s="7"/>
-      <c r="B188" s="7"/>
-      <c r="C188" s="7"/>
-      <c r="D188" s="7"/>
-      <c r="E188" s="7"/>
-      <c r="F188" s="7"/>
+      <c r="A188" s="6"/>
+      <c r="B188" s="6"/>
+      <c r="C188" s="6"/>
+      <c r="D188" s="6"/>
+      <c r="E188" s="6"/>
+      <c r="F188" s="6"/>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A189" s="7"/>
-      <c r="B189" s="7"/>
-      <c r="C189" s="7"/>
-      <c r="D189" s="7"/>
-      <c r="E189" s="7"/>
-      <c r="F189" s="7"/>
+      <c r="A189" s="6"/>
+      <c r="B189" s="6"/>
+      <c r="C189" s="6"/>
+      <c r="D189" s="6"/>
+      <c r="E189" s="6"/>
+      <c r="F189" s="6"/>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A190" s="7"/>
-      <c r="B190" s="7"/>
-      <c r="C190" s="7"/>
-      <c r="D190" s="7"/>
-      <c r="E190" s="7"/>
-      <c r="F190" s="7"/>
+      <c r="A190" s="6"/>
+      <c r="B190" s="6"/>
+      <c r="C190" s="6"/>
+      <c r="D190" s="6"/>
+      <c r="E190" s="6"/>
+      <c r="F190" s="6"/>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A191" s="7"/>
-      <c r="B191" s="7"/>
-      <c r="C191" s="7"/>
-      <c r="D191" s="7"/>
-      <c r="E191" s="7"/>
-      <c r="F191" s="7"/>
+      <c r="A191" s="6"/>
+      <c r="B191" s="6"/>
+      <c r="C191" s="6"/>
+      <c r="D191" s="6"/>
+      <c r="E191" s="6"/>
+      <c r="F191" s="6"/>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A192" s="7"/>
-      <c r="B192" s="7"/>
-      <c r="C192" s="7"/>
-      <c r="D192" s="7"/>
-      <c r="E192" s="7"/>
-      <c r="F192" s="7"/>
+      <c r="A192" s="6"/>
+      <c r="B192" s="6"/>
+      <c r="C192" s="6"/>
+      <c r="D192" s="6"/>
+      <c r="E192" s="6"/>
+      <c r="F192" s="6"/>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A193" s="7"/>
-      <c r="B193" s="7"/>
-      <c r="C193" s="7"/>
-      <c r="D193" s="7"/>
-      <c r="E193" s="7"/>
-      <c r="F193" s="7"/>
+      <c r="A193" s="6"/>
+      <c r="B193" s="6"/>
+      <c r="C193" s="6"/>
+      <c r="D193" s="6"/>
+      <c r="E193" s="6"/>
+      <c r="F193" s="6"/>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A194" s="7"/>
-      <c r="B194" s="7"/>
-      <c r="C194" s="7"/>
-      <c r="D194" s="7"/>
-      <c r="E194" s="7"/>
-      <c r="F194" s="7"/>
+      <c r="A194" s="6"/>
+      <c r="B194" s="6"/>
+      <c r="C194" s="6"/>
+      <c r="D194" s="6"/>
+      <c r="E194" s="6"/>
+      <c r="F194" s="6"/>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A195" s="7"/>
-      <c r="B195" s="7"/>
-      <c r="C195" s="7"/>
-      <c r="D195" s="7"/>
-      <c r="E195" s="7"/>
-      <c r="F195" s="7"/>
+      <c r="A195" s="6"/>
+      <c r="B195" s="6"/>
+      <c r="C195" s="6"/>
+      <c r="D195" s="6"/>
+      <c r="E195" s="6"/>
+      <c r="F195" s="6"/>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A196" s="7"/>
-      <c r="B196" s="7"/>
-      <c r="C196" s="7"/>
-      <c r="D196" s="7"/>
-      <c r="E196" s="7"/>
-      <c r="F196" s="7"/>
+      <c r="A196" s="6"/>
+      <c r="B196" s="6"/>
+      <c r="C196" s="6"/>
+      <c r="D196" s="6"/>
+      <c r="E196" s="6"/>
+      <c r="F196" s="6"/>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A197" s="7"/>
-      <c r="B197" s="7"/>
-      <c r="C197" s="7"/>
-      <c r="D197" s="7"/>
-      <c r="E197" s="7"/>
-      <c r="F197" s="7"/>
+      <c r="A197" s="6"/>
+      <c r="B197" s="6"/>
+      <c r="C197" s="6"/>
+      <c r="D197" s="6"/>
+      <c r="E197" s="6"/>
+      <c r="F197" s="6"/>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A198" s="7"/>
-      <c r="B198" s="7"/>
-      <c r="C198" s="7"/>
-      <c r="D198" s="7"/>
-      <c r="E198" s="7"/>
-      <c r="F198" s="7"/>
+      <c r="A198" s="6"/>
+      <c r="B198" s="6"/>
+      <c r="C198" s="6"/>
+      <c r="D198" s="6"/>
+      <c r="E198" s="6"/>
+      <c r="F198" s="6"/>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A199" s="7"/>
-      <c r="B199" s="7"/>
-      <c r="C199" s="7"/>
-      <c r="D199" s="7"/>
-      <c r="E199" s="7"/>
-      <c r="F199" s="7"/>
+      <c r="A199" s="6"/>
+      <c r="B199" s="6"/>
+      <c r="C199" s="6"/>
+      <c r="D199" s="6"/>
+      <c r="E199" s="6"/>
+      <c r="F199" s="6"/>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A200" s="7"/>
-      <c r="B200" s="7"/>
-      <c r="C200" s="7"/>
-      <c r="D200" s="7"/>
-      <c r="E200" s="7"/>
-      <c r="F200" s="7"/>
+      <c r="A200" s="6"/>
+      <c r="B200" s="6"/>
+      <c r="C200" s="6"/>
+      <c r="D200" s="6"/>
+      <c r="E200" s="6"/>
+      <c r="F200" s="6"/>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A201" s="7"/>
-      <c r="B201" s="7"/>
-      <c r="C201" s="7"/>
-      <c r="D201" s="7"/>
-      <c r="E201" s="7"/>
-      <c r="F201" s="7"/>
+      <c r="A201" s="6"/>
+      <c r="B201" s="6"/>
+      <c r="C201" s="6"/>
+      <c r="D201" s="6"/>
+      <c r="E201" s="6"/>
+      <c r="F201" s="6"/>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A202" s="7"/>
-      <c r="B202" s="7"/>
-      <c r="C202" s="7"/>
-      <c r="D202" s="7"/>
-      <c r="E202" s="7"/>
-      <c r="F202" s="7"/>
+      <c r="A202" s="6"/>
+      <c r="B202" s="6"/>
+      <c r="C202" s="6"/>
+      <c r="D202" s="6"/>
+      <c r="E202" s="6"/>
+      <c r="F202" s="6"/>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A203" s="7"/>
-      <c r="B203" s="7"/>
-      <c r="C203" s="7"/>
-      <c r="D203" s="7"/>
-      <c r="E203" s="7"/>
-      <c r="F203" s="7"/>
+      <c r="A203" s="6"/>
+      <c r="B203" s="6"/>
+      <c r="C203" s="6"/>
+      <c r="D203" s="6"/>
+      <c r="E203" s="6"/>
+      <c r="F203" s="6"/>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A204" s="7"/>
-      <c r="B204" s="7"/>
-      <c r="C204" s="7"/>
-      <c r="D204" s="7"/>
-      <c r="E204" s="7"/>
-      <c r="F204" s="7"/>
+      <c r="A204" s="6"/>
+      <c r="B204" s="6"/>
+      <c r="C204" s="6"/>
+      <c r="D204" s="6"/>
+      <c r="E204" s="6"/>
+      <c r="F204" s="6"/>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A205" s="7"/>
-      <c r="B205" s="7"/>
-      <c r="C205" s="7"/>
-      <c r="D205" s="7"/>
-      <c r="E205" s="7"/>
-      <c r="F205" s="7"/>
+      <c r="A205" s="6"/>
+      <c r="B205" s="6"/>
+      <c r="C205" s="6"/>
+      <c r="D205" s="6"/>
+      <c r="E205" s="6"/>
+      <c r="F205" s="6"/>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A206" s="7"/>
-      <c r="B206" s="7"/>
-      <c r="C206" s="7"/>
-      <c r="D206" s="7"/>
-      <c r="E206" s="7"/>
-      <c r="F206" s="7"/>
+      <c r="A206" s="6"/>
+      <c r="B206" s="6"/>
+      <c r="C206" s="6"/>
+      <c r="D206" s="6"/>
+      <c r="E206" s="6"/>
+      <c r="F206" s="6"/>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A207" s="7"/>
-      <c r="B207" s="7"/>
-      <c r="C207" s="7"/>
-      <c r="D207" s="7"/>
-      <c r="E207" s="7"/>
-      <c r="F207" s="7"/>
+      <c r="A207" s="6"/>
+      <c r="B207" s="6"/>
+      <c r="C207" s="6"/>
+      <c r="D207" s="6"/>
+      <c r="E207" s="6"/>
+      <c r="F207" s="6"/>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A208" s="7"/>
-      <c r="B208" s="7"/>
-      <c r="C208" s="7"/>
-      <c r="D208" s="7"/>
-      <c r="E208" s="7"/>
-      <c r="F208" s="7"/>
+      <c r="A208" s="6"/>
+      <c r="B208" s="6"/>
+      <c r="C208" s="6"/>
+      <c r="D208" s="6"/>
+      <c r="E208" s="6"/>
+      <c r="F208" s="6"/>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A209" s="7"/>
-      <c r="B209" s="7"/>
-      <c r="C209" s="7"/>
-      <c r="D209" s="7"/>
-      <c r="E209" s="7"/>
-      <c r="F209" s="7"/>
+      <c r="A209" s="6"/>
+      <c r="B209" s="6"/>
+      <c r="C209" s="6"/>
+      <c r="D209" s="6"/>
+      <c r="E209" s="6"/>
+      <c r="F209" s="6"/>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A210" s="7"/>
-      <c r="B210" s="7"/>
-      <c r="C210" s="7"/>
-      <c r="D210" s="7"/>
-      <c r="E210" s="7"/>
-      <c r="F210" s="7"/>
+      <c r="A210" s="6"/>
+      <c r="B210" s="6"/>
+      <c r="C210" s="6"/>
+      <c r="D210" s="6"/>
+      <c r="E210" s="6"/>
+      <c r="F210" s="6"/>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A211" s="7"/>
-      <c r="B211" s="7"/>
-      <c r="C211" s="7"/>
-      <c r="D211" s="7"/>
-      <c r="E211" s="7"/>
-      <c r="F211" s="7"/>
+      <c r="A211" s="6"/>
+      <c r="B211" s="6"/>
+      <c r="C211" s="6"/>
+      <c r="D211" s="6"/>
+      <c r="E211" s="6"/>
+      <c r="F211" s="6"/>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A212" s="7"/>
-      <c r="B212" s="7"/>
-      <c r="C212" s="7"/>
-      <c r="D212" s="7"/>
-      <c r="E212" s="7"/>
-      <c r="F212" s="7"/>
+      <c r="A212" s="6"/>
+      <c r="B212" s="6"/>
+      <c r="C212" s="6"/>
+      <c r="D212" s="6"/>
+      <c r="E212" s="6"/>
+      <c r="F212" s="6"/>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A213" s="7"/>
-      <c r="B213" s="7"/>
-      <c r="C213" s="7"/>
-      <c r="D213" s="7"/>
-      <c r="E213" s="7"/>
-      <c r="F213" s="7"/>
+      <c r="A213" s="6"/>
+      <c r="B213" s="6"/>
+      <c r="C213" s="6"/>
+      <c r="D213" s="6"/>
+      <c r="E213" s="6"/>
+      <c r="F213" s="6"/>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A214" s="7"/>
-      <c r="B214" s="7"/>
-      <c r="C214" s="7"/>
-      <c r="D214" s="7"/>
-      <c r="E214" s="7"/>
-      <c r="F214" s="7"/>
+      <c r="A214" s="6"/>
+      <c r="B214" s="6"/>
+      <c r="C214" s="6"/>
+      <c r="D214" s="6"/>
+      <c r="E214" s="6"/>
+      <c r="F214" s="6"/>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A215" s="7"/>
-      <c r="B215" s="7"/>
-      <c r="C215" s="7"/>
-      <c r="D215" s="7"/>
-      <c r="E215" s="7"/>
-      <c r="F215" s="7"/>
+      <c r="A215" s="6"/>
+      <c r="B215" s="6"/>
+      <c r="C215" s="6"/>
+      <c r="D215" s="6"/>
+      <c r="E215" s="6"/>
+      <c r="F215" s="6"/>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A216" s="7"/>
-      <c r="B216" s="7"/>
-      <c r="C216" s="7"/>
-      <c r="D216" s="7"/>
-      <c r="E216" s="7"/>
-      <c r="F216" s="7"/>
+      <c r="A216" s="6"/>
+      <c r="B216" s="6"/>
+      <c r="C216" s="6"/>
+      <c r="D216" s="6"/>
+      <c r="E216" s="6"/>
+      <c r="F216" s="6"/>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A217" s="7"/>
-      <c r="B217" s="7"/>
-      <c r="C217" s="7"/>
-      <c r="D217" s="7"/>
-      <c r="E217" s="7"/>
-      <c r="F217" s="7"/>
+      <c r="A217" s="6"/>
+      <c r="B217" s="6"/>
+      <c r="C217" s="6"/>
+      <c r="D217" s="6"/>
+      <c r="E217" s="6"/>
+      <c r="F217" s="6"/>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A218" s="7"/>
-      <c r="B218" s="7"/>
-      <c r="C218" s="7"/>
-      <c r="D218" s="7"/>
-      <c r="E218" s="7"/>
-      <c r="F218" s="7"/>
+      <c r="A218" s="6"/>
+      <c r="B218" s="6"/>
+      <c r="C218" s="6"/>
+      <c r="D218" s="6"/>
+      <c r="E218" s="6"/>
+      <c r="F218" s="6"/>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A219" s="7"/>
-      <c r="B219" s="7"/>
-      <c r="C219" s="7"/>
-      <c r="D219" s="7"/>
-      <c r="E219" s="7"/>
-      <c r="F219" s="7"/>
+      <c r="A219" s="6"/>
+      <c r="B219" s="6"/>
+      <c r="C219" s="6"/>
+      <c r="D219" s="6"/>
+      <c r="E219" s="6"/>
+      <c r="F219" s="6"/>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A220" s="7"/>
-      <c r="B220" s="7"/>
-      <c r="C220" s="7"/>
-      <c r="D220" s="7"/>
-      <c r="E220" s="7"/>
-      <c r="F220" s="7"/>
+      <c r="A220" s="6"/>
+      <c r="B220" s="6"/>
+      <c r="C220" s="6"/>
+      <c r="D220" s="6"/>
+      <c r="E220" s="6"/>
+      <c r="F220" s="6"/>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A221" s="7"/>
-      <c r="B221" s="7"/>
-      <c r="C221" s="7"/>
-      <c r="D221" s="7"/>
-      <c r="E221" s="7"/>
-      <c r="F221" s="7"/>
+      <c r="A221" s="6"/>
+      <c r="B221" s="6"/>
+      <c r="C221" s="6"/>
+      <c r="D221" s="6"/>
+      <c r="E221" s="6"/>
+      <c r="F221" s="6"/>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A222" s="7"/>
-      <c r="B222" s="7"/>
-      <c r="C222" s="7"/>
-      <c r="D222" s="7"/>
-      <c r="E222" s="7"/>
-      <c r="F222" s="7"/>
+      <c r="A222" s="6"/>
+      <c r="B222" s="6"/>
+      <c r="C222" s="6"/>
+      <c r="D222" s="6"/>
+      <c r="E222" s="6"/>
+      <c r="F222" s="6"/>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A223" s="7"/>
-      <c r="B223" s="7"/>
-      <c r="C223" s="7"/>
-      <c r="D223" s="7"/>
-      <c r="E223" s="7"/>
-      <c r="F223" s="7"/>
+      <c r="A223" s="6"/>
+      <c r="B223" s="6"/>
+      <c r="C223" s="6"/>
+      <c r="D223" s="6"/>
+      <c r="E223" s="6"/>
+      <c r="F223" s="6"/>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A224" s="7"/>
-      <c r="B224" s="7"/>
-      <c r="C224" s="7"/>
-      <c r="D224" s="7"/>
-      <c r="E224" s="7"/>
-      <c r="F224" s="7"/>
+      <c r="A224" s="6"/>
+      <c r="B224" s="6"/>
+      <c r="C224" s="6"/>
+      <c r="D224" s="6"/>
+      <c r="E224" s="6"/>
+      <c r="F224" s="6"/>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A225" s="7"/>
-      <c r="B225" s="7"/>
-      <c r="C225" s="7"/>
-      <c r="D225" s="7"/>
-      <c r="E225" s="7"/>
-      <c r="F225" s="7"/>
+      <c r="A225" s="6"/>
+      <c r="B225" s="6"/>
+      <c r="C225" s="6"/>
+      <c r="D225" s="6"/>
+      <c r="E225" s="6"/>
+      <c r="F225" s="6"/>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A226" s="7"/>
-      <c r="B226" s="7"/>
-      <c r="C226" s="7"/>
-      <c r="D226" s="7"/>
-      <c r="E226" s="7"/>
-      <c r="F226" s="7"/>
+      <c r="A226" s="6"/>
+      <c r="B226" s="6"/>
+      <c r="C226" s="6"/>
+      <c r="D226" s="6"/>
+      <c r="E226" s="6"/>
+      <c r="F226" s="6"/>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A227" s="7"/>
-      <c r="B227" s="7"/>
-      <c r="C227" s="7"/>
-      <c r="D227" s="7"/>
-      <c r="E227" s="7"/>
-      <c r="F227" s="7"/>
+      <c r="A227" s="6"/>
+      <c r="B227" s="6"/>
+      <c r="C227" s="6"/>
+      <c r="D227" s="6"/>
+      <c r="E227" s="6"/>
+      <c r="F227" s="6"/>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A228" s="7"/>
-      <c r="B228" s="7"/>
-      <c r="C228" s="7"/>
-      <c r="D228" s="7"/>
-      <c r="E228" s="7"/>
-      <c r="F228" s="7"/>
+      <c r="A228" s="6"/>
+      <c r="B228" s="6"/>
+      <c r="C228" s="6"/>
+      <c r="D228" s="6"/>
+      <c r="E228" s="6"/>
+      <c r="F228" s="6"/>
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A229" s="7"/>
-      <c r="B229" s="7"/>
-      <c r="C229" s="7"/>
-      <c r="D229" s="7"/>
-      <c r="E229" s="7"/>
-      <c r="F229" s="7"/>
+      <c r="A229" s="6"/>
+      <c r="B229" s="6"/>
+      <c r="C229" s="6"/>
+      <c r="D229" s="6"/>
+      <c r="E229" s="6"/>
+      <c r="F229" s="6"/>
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A230" s="7"/>
-      <c r="B230" s="7"/>
-      <c r="C230" s="7"/>
-      <c r="D230" s="7"/>
-      <c r="E230" s="7"/>
-      <c r="F230" s="7"/>
+      <c r="A230" s="6"/>
+      <c r="B230" s="6"/>
+      <c r="C230" s="6"/>
+      <c r="D230" s="6"/>
+      <c r="E230" s="6"/>
+      <c r="F230" s="6"/>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A231" s="7"/>
-      <c r="B231" s="7"/>
-      <c r="C231" s="7"/>
-      <c r="D231" s="7"/>
-      <c r="E231" s="7"/>
-      <c r="F231" s="7"/>
+      <c r="A231" s="6"/>
+      <c r="B231" s="6"/>
+      <c r="C231" s="6"/>
+      <c r="D231" s="6"/>
+      <c r="E231" s="6"/>
+      <c r="F231" s="6"/>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A232" s="7"/>
-      <c r="B232" s="7"/>
-      <c r="C232" s="7"/>
-      <c r="D232" s="7"/>
-      <c r="E232" s="7"/>
-      <c r="F232" s="7"/>
+      <c r="A232" s="6"/>
+      <c r="B232" s="6"/>
+      <c r="C232" s="6"/>
+      <c r="D232" s="6"/>
+      <c r="E232" s="6"/>
+      <c r="F232" s="6"/>
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A233" s="7"/>
-      <c r="B233" s="7"/>
-      <c r="C233" s="7"/>
-      <c r="D233" s="7"/>
-      <c r="E233" s="7"/>
-      <c r="F233" s="7"/>
+      <c r="A233" s="6"/>
+      <c r="B233" s="6"/>
+      <c r="C233" s="6"/>
+      <c r="D233" s="6"/>
+      <c r="E233" s="6"/>
+      <c r="F233" s="6"/>
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A234" s="7"/>
-      <c r="B234" s="7"/>
-      <c r="C234" s="7"/>
-      <c r="D234" s="7"/>
-      <c r="E234" s="7"/>
-      <c r="F234" s="7"/>
+      <c r="A234" s="6"/>
+      <c r="B234" s="6"/>
+      <c r="C234" s="6"/>
+      <c r="D234" s="6"/>
+      <c r="E234" s="6"/>
+      <c r="F234" s="6"/>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A235" s="7"/>
-      <c r="B235" s="7"/>
-      <c r="C235" s="7"/>
-      <c r="D235" s="7"/>
-      <c r="E235" s="7"/>
-      <c r="F235" s="7"/>
+      <c r="A235" s="6"/>
+      <c r="B235" s="6"/>
+      <c r="C235" s="6"/>
+      <c r="D235" s="6"/>
+      <c r="E235" s="6"/>
+      <c r="F235" s="6"/>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A236" s="7"/>
-      <c r="B236" s="7"/>
-      <c r="C236" s="7"/>
-      <c r="D236" s="7"/>
-      <c r="E236" s="7"/>
-      <c r="F236" s="7"/>
+      <c r="A236" s="6"/>
+      <c r="B236" s="6"/>
+      <c r="C236" s="6"/>
+      <c r="D236" s="6"/>
+      <c r="E236" s="6"/>
+      <c r="F236" s="6"/>
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A237" s="7"/>
-      <c r="B237" s="7"/>
-      <c r="C237" s="7"/>
-      <c r="D237" s="7"/>
-      <c r="E237" s="7"/>
-      <c r="F237" s="7"/>
+      <c r="A237" s="6"/>
+      <c r="B237" s="6"/>
+      <c r="C237" s="6"/>
+      <c r="D237" s="6"/>
+      <c r="E237" s="6"/>
+      <c r="F237" s="6"/>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A238" s="7"/>
-      <c r="B238" s="7"/>
-      <c r="C238" s="7"/>
-      <c r="D238" s="7"/>
-      <c r="E238" s="7"/>
-      <c r="F238" s="7"/>
+      <c r="A238" s="6"/>
+      <c r="B238" s="6"/>
+      <c r="C238" s="6"/>
+      <c r="D238" s="6"/>
+      <c r="E238" s="6"/>
+      <c r="F238" s="6"/>
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A239" s="7"/>
-      <c r="B239" s="7"/>
-      <c r="C239" s="7"/>
-      <c r="D239" s="7"/>
-      <c r="E239" s="7"/>
-      <c r="F239" s="7"/>
+      <c r="A239" s="6"/>
+      <c r="B239" s="6"/>
+      <c r="C239" s="6"/>
+      <c r="D239" s="6"/>
+      <c r="E239" s="6"/>
+      <c r="F239" s="6"/>
     </row>
     <row r="1048520" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048521" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2474,6 +2527,7 @@
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
+  <autoFilter ref="A1:F13"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -2481,6 +2535,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2498,13 +2553,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
